--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8169,6 +8169,9807 @@
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128998140</v>
+      </c>
+      <c r="B68" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>583855</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7213081</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128998144</v>
+      </c>
+      <c r="B69" t="n">
+        <v>75192</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>583765</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7212611</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129000128</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>583804</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7212351</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129000140</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>584092</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7211517</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129000136</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>583699</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7212348</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129000179</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>583976</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7212366</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128998142</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>583800</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7212769</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128998122</v>
+      </c>
+      <c r="B75" t="n">
+        <v>105684</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>583934</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7212490</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128997038</v>
+      </c>
+      <c r="B76" t="n">
+        <v>97513</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>583850</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7212515</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129000183</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>584220</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7211664</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128998128</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57880</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>583799</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7212748</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129000152</v>
+      </c>
+      <c r="B79" t="n">
+        <v>80257</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>584338</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7211689</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128998131</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57717</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>584025</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7212370</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128998135</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91877</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>583778</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7212890</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128998124</v>
+      </c>
+      <c r="B82" t="n">
+        <v>91508</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>583784</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7212884</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129000137</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>583784</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7212338</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128998147</v>
+      </c>
+      <c r="B84" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>583732</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7212858</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129000181</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>583824</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7211526</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129000163</v>
+      </c>
+      <c r="B86" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>584005</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7211652</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>129000159</v>
+      </c>
+      <c r="B87" t="n">
+        <v>56901</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>583817</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7212328</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>129000171</v>
+      </c>
+      <c r="B88" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>583882</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7212369</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129000106</v>
+      </c>
+      <c r="B89" t="n">
+        <v>92205</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>583634</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7212397</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>129000141</v>
+      </c>
+      <c r="B90" t="n">
+        <v>97507</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>584301</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7211657</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>129000178</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>583707</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7212347</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128998153</v>
+      </c>
+      <c r="B92" t="n">
+        <v>80264</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>583842</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7212492</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128998133</v>
+      </c>
+      <c r="B93" t="n">
+        <v>80230</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>583743</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7212862</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129000145</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>583826</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7211682</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>129000149</v>
+      </c>
+      <c r="B95" t="n">
+        <v>97513</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>583660</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7212365</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>129000103</v>
+      </c>
+      <c r="B96" t="n">
+        <v>91508</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>583841</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7212355</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>129000115</v>
+      </c>
+      <c r="B97" t="n">
+        <v>80258</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>583856</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7212374</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>129000189</v>
+      </c>
+      <c r="B98" t="n">
+        <v>80264</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>583856</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7212375</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>128998134</v>
+      </c>
+      <c r="B99" t="n">
+        <v>91804</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>658</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>583813</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7212866</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>129000188</v>
+      </c>
+      <c r="B100" t="n">
+        <v>80264</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>583606</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7212484</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>129000110</v>
+      </c>
+      <c r="B101" t="n">
+        <v>57880</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>583842</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7212868</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>129000094</v>
+      </c>
+      <c r="B102" t="n">
+        <v>75209</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>583585</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7212671</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>128998152</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>583744</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7212703</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128998127</v>
+      </c>
+      <c r="B104" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>583792</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7212761</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Färskt bohål som sannolikt är från tretåig hackspett pga storleken på bohålet (ca 5 cm)</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>129000100</v>
+      </c>
+      <c r="B105" t="n">
+        <v>91473</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>583841</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7212873</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>129000096</v>
+      </c>
+      <c r="B106" t="n">
+        <v>75209</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>583980</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7212363</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>128998130</v>
+      </c>
+      <c r="B107" t="n">
+        <v>80258</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>583781</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7212767</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>129000165</v>
+      </c>
+      <c r="B108" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>583888</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7211663</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>129000116</v>
+      </c>
+      <c r="B109" t="n">
+        <v>57717</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>584099</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7211521</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Spillkråkehack på låga</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>129000153</v>
+      </c>
+      <c r="B110" t="n">
+        <v>80229</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>583768</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7212826</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>björktrast</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>129000177</v>
+      </c>
+      <c r="B111" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>583609</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7212495</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>128997035</v>
+      </c>
+      <c r="B112" t="n">
+        <v>57880</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>583868</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7212926</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>128997040</v>
+      </c>
+      <c r="B113" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>583800</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7212621</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>128998155</v>
+      </c>
+      <c r="B114" t="n">
+        <v>80264</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>583778</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7212766</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>128998146</v>
+      </c>
+      <c r="B115" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>583700</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7212870</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>128998150</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>583862</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7212466</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>129000114</v>
+      </c>
+      <c r="B117" t="n">
+        <v>80258</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>583606</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7212483</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>129000175</v>
+      </c>
+      <c r="B118" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>583975</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7211530</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>128998132</v>
+      </c>
+      <c r="B119" t="n">
+        <v>57717</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>583834</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7212585</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>128998136</v>
+      </c>
+      <c r="B120" t="n">
+        <v>80265</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>583838</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7212502</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>129000150</v>
+      </c>
+      <c r="B121" t="n">
+        <v>91877</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>583951</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7211500</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>129000107</v>
+      </c>
+      <c r="B122" t="n">
+        <v>92205</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>583938</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7211643</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>129000104</v>
+      </c>
+      <c r="B123" t="n">
+        <v>91508</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>584023</v>
+      </c>
+      <c r="R123" t="n">
+        <v>7212353</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>128997039</v>
+      </c>
+      <c r="B124" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>583807</v>
+      </c>
+      <c r="R124" t="n">
+        <v>7212750</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>129000147</v>
+      </c>
+      <c r="B125" t="n">
+        <v>97513</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>584141</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7211590</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>129000126</v>
+      </c>
+      <c r="B126" t="n">
+        <v>75214</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>583693</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7211591</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>129000122</v>
+      </c>
+      <c r="B127" t="n">
+        <v>80230</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>583833</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7212856</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>129000170</v>
+      </c>
+      <c r="B128" t="n">
+        <v>91522</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>583844</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7212348</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>129000130</v>
+      </c>
+      <c r="B129" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>584350</v>
+      </c>
+      <c r="R129" t="n">
+        <v>7211690</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128998250</v>
+      </c>
+      <c r="B130" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>583752</v>
+      </c>
+      <c r="R130" t="n">
+        <v>7212679</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>128998126</v>
+      </c>
+      <c r="B131" t="n">
+        <v>92205</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>583748</v>
+      </c>
+      <c r="R131" t="n">
+        <v>7212869</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>128998149</v>
+      </c>
+      <c r="B132" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>584059</v>
+      </c>
+      <c r="R132" t="n">
+        <v>7212428</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>129000176</v>
+      </c>
+      <c r="B133" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>583766</v>
+      </c>
+      <c r="R133" t="n">
+        <v>7212828</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>129000157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>57824</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>583712</v>
+      </c>
+      <c r="R134" t="n">
+        <v>7211576</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>129000146</v>
+      </c>
+      <c r="B135" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>583819</v>
+      </c>
+      <c r="R135" t="n">
+        <v>7211689</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>129000187</v>
+      </c>
+      <c r="B136" t="n">
+        <v>88908</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>510</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>583966</v>
+      </c>
+      <c r="R136" t="n">
+        <v>7211510</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>128998138</v>
+      </c>
+      <c r="B137" t="n">
+        <v>80265</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>583742</v>
+      </c>
+      <c r="R137" t="n">
+        <v>7213116</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>129000124</v>
+      </c>
+      <c r="B138" t="n">
+        <v>75214</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>583770</v>
+      </c>
+      <c r="R138" t="n">
+        <v>7212830</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>129000172</v>
+      </c>
+      <c r="B139" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>583719</v>
+      </c>
+      <c r="R139" t="n">
+        <v>7212791</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>129000173</v>
+      </c>
+      <c r="B140" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>583879</v>
+      </c>
+      <c r="R140" t="n">
+        <v>7211699</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>129000097</v>
+      </c>
+      <c r="B141" t="n">
+        <v>75209</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>584170</v>
+      </c>
+      <c r="R141" t="n">
+        <v>7211600</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>129000135</v>
+      </c>
+      <c r="B142" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>584139</v>
+      </c>
+      <c r="R142" t="n">
+        <v>7211559</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>129000119</v>
+      </c>
+      <c r="B143" t="n">
+        <v>75207</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>6486</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Skuggnål</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Chaenotheca sphaerocephala</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>583763</v>
+      </c>
+      <c r="R143" t="n">
+        <v>7211568</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>129000182</v>
+      </c>
+      <c r="B144" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>584124</v>
+      </c>
+      <c r="R144" t="n">
+        <v>7211556</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>128998151</v>
+      </c>
+      <c r="B145" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>583830</v>
+      </c>
+      <c r="R145" t="n">
+        <v>7212605</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>128998148</v>
+      </c>
+      <c r="B146" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>583764</v>
+      </c>
+      <c r="R146" t="n">
+        <v>7212875</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>128998129</v>
+      </c>
+      <c r="B147" t="n">
+        <v>80258</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>583743</v>
+      </c>
+      <c r="R147" t="n">
+        <v>7212862</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>128998154</v>
+      </c>
+      <c r="B148" t="n">
+        <v>80264</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>583743</v>
+      </c>
+      <c r="R148" t="n">
+        <v>7212862</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>129000169</v>
+      </c>
+      <c r="B149" t="n">
+        <v>75192</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>583695</v>
+      </c>
+      <c r="R149" t="n">
+        <v>7211591</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>129000101</v>
+      </c>
+      <c r="B150" t="n">
+        <v>91508</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>583663</v>
+      </c>
+      <c r="R150" t="n">
+        <v>7212429</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>129000144</v>
+      </c>
+      <c r="B151" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>583832</v>
+      </c>
+      <c r="R151" t="n">
+        <v>7211693</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>129000129</v>
+      </c>
+      <c r="B152" t="n">
+        <v>91804</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>658</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>583810</v>
+      </c>
+      <c r="R152" t="n">
+        <v>7212852</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>128998141</v>
+      </c>
+      <c r="B153" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>583789</v>
+      </c>
+      <c r="R153" t="n">
+        <v>7213129</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>129000180</v>
+      </c>
+      <c r="B154" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>583695</v>
+      </c>
+      <c r="R154" t="n">
+        <v>7211621</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>129000132</v>
+      </c>
+      <c r="B155" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>583968</v>
+      </c>
+      <c r="R155" t="n">
+        <v>7212362</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>129000121</v>
+      </c>
+      <c r="B156" t="n">
+        <v>80230</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>583770</v>
+      </c>
+      <c r="R156" t="n">
+        <v>7212825</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>129000160</v>
+      </c>
+      <c r="B157" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>583674</v>
+      </c>
+      <c r="R157" t="n">
+        <v>7212755</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>129000142</v>
+      </c>
+      <c r="B158" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>583922</v>
+      </c>
+      <c r="R158" t="n">
+        <v>7211662</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>129000168</v>
+      </c>
+      <c r="B159" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>584331</v>
+      </c>
+      <c r="R159" t="n">
+        <v>7211693</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>129000184</v>
+      </c>
+      <c r="B160" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>584333</v>
+      </c>
+      <c r="R160" t="n">
+        <v>7211688</v>
+      </c>
+      <c r="S160" t="n">
+        <v>10</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>129000166</v>
+      </c>
+      <c r="B161" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>583796</v>
+      </c>
+      <c r="R161" t="n">
+        <v>7211546</v>
+      </c>
+      <c r="S161" t="n">
+        <v>10</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>129000185</v>
+      </c>
+      <c r="B162" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>584074</v>
+      </c>
+      <c r="R162" t="n">
+        <v>7211675</v>
+      </c>
+      <c r="S162" t="n">
+        <v>10</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>129000174</v>
+      </c>
+      <c r="B163" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>583934</v>
+      </c>
+      <c r="R163" t="n">
+        <v>7211520</v>
+      </c>
+      <c r="S163" t="n">
+        <v>10</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>129000167</v>
+      </c>
+      <c r="B164" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>584144</v>
+      </c>
+      <c r="R164" t="n">
+        <v>7211566</v>
+      </c>
+      <c r="S164" t="n">
+        <v>10</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>129000162</v>
+      </c>
+      <c r="B165" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>583583</v>
+      </c>
+      <c r="R165" t="n">
+        <v>7212676</v>
+      </c>
+      <c r="S165" t="n">
+        <v>10</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>129000138</v>
+      </c>
+      <c r="B166" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>583805</v>
+      </c>
+      <c r="R166" t="n">
+        <v>7211693</v>
+      </c>
+      <c r="S166" t="n">
+        <v>10</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>129000154</v>
+      </c>
+      <c r="B167" t="n">
+        <v>80265</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Inre Verkanliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>583832</v>
+      </c>
+      <c r="R167" t="n">
+        <v>7212853</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY167"/>
+  <dimension ref="A1:AY170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8171,45 +8171,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128998140</v>
+        <v>129000128</v>
       </c>
       <c r="B68" t="n">
-        <v>91504</v>
+        <v>91967</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583855</v>
+        <v>583804</v>
       </c>
       <c r="R68" t="n">
-        <v>7213081</v>
+        <v>7212351</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8256,57 +8256,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128998144</v>
+        <v>129000179</v>
       </c>
       <c r="B69" t="n">
-        <v>75192</v>
+        <v>79029</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>583765</v>
+        <v>583976</v>
       </c>
       <c r="R69" t="n">
-        <v>7212611</v>
+        <v>7212366</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8353,44 +8353,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129000128</v>
+        <v>129000140</v>
       </c>
       <c r="B70" t="n">
-        <v>91962</v>
+        <v>57723</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583804</v>
+        <v>584092</v>
       </c>
       <c r="R70" t="n">
-        <v>7212351</v>
+        <v>7211517</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8430,12 +8430,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8462,10 +8467,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129000140</v>
+        <v>129000136</v>
       </c>
       <c r="B71" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8497,10 +8502,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>584092</v>
+        <v>583699</v>
       </c>
       <c r="R71" t="n">
-        <v>7211517</v>
+        <v>7212348</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8527,17 +8532,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8564,10 +8569,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129000136</v>
+        <v>128998140</v>
       </c>
       <c r="B72" t="n">
-        <v>57720</v>
+        <v>91509</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8575,34 +8580,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583699</v>
+        <v>583855</v>
       </c>
       <c r="R72" t="n">
-        <v>7212348</v>
+        <v>7213081</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8637,11 +8642,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8654,57 +8654,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129000179</v>
+        <v>128998144</v>
       </c>
       <c r="B73" t="n">
-        <v>79124</v>
+        <v>82988</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583976</v>
+        <v>583765</v>
       </c>
       <c r="R73" t="n">
-        <v>7212366</v>
+        <v>7212611</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8751,22 +8751,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128998142</v>
+        <v>129000183</v>
       </c>
       <c r="B74" t="n">
-        <v>91504</v>
+        <v>79029</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8774,34 +8774,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583800</v>
+        <v>584220</v>
       </c>
       <c r="R74" t="n">
-        <v>7212769</v>
+        <v>7211664</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8828,12 +8828,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8848,44 +8848,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128998122</v>
+        <v>128998142</v>
       </c>
       <c r="B75" t="n">
-        <v>105684</v>
+        <v>91509</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221725</v>
+        <v>1108</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8895,10 +8895,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583934</v>
+        <v>583800</v>
       </c>
       <c r="R75" t="n">
-        <v>7212490</v>
+        <v>7212769</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8960,7 +8960,7 @@
         <v>128997038</v>
       </c>
       <c r="B76" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9054,45 +9054,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129000183</v>
+        <v>128998122</v>
       </c>
       <c r="B77" t="n">
-        <v>79124</v>
+        <v>105691</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>584220</v>
+        <v>583934</v>
       </c>
       <c r="R77" t="n">
-        <v>7211664</v>
+        <v>7212490</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9119,12 +9119,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9139,12 +9139,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9154,7 +9154,7 @@
         <v>128998128</v>
       </c>
       <c r="B78" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>129000152</v>
       </c>
       <c r="B79" t="n">
-        <v>80257</v>
+        <v>80162</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9345,10 +9345,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128998131</v>
+        <v>129000137</v>
       </c>
       <c r="B80" t="n">
-        <v>57717</v>
+        <v>57723</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9356,16 +9356,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9376,14 +9376,14 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>584025</v>
+        <v>583784</v>
       </c>
       <c r="R80" t="n">
-        <v>7212370</v>
+        <v>7212338</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9418,6 +9418,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9430,12 +9435,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9445,7 +9450,7 @@
         <v>128998135</v>
       </c>
       <c r="B81" t="n">
-        <v>91877</v>
+        <v>91882</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9542,7 +9547,7 @@
         <v>128998124</v>
       </c>
       <c r="B82" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9636,7 +9641,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129000137</v>
+        <v>128998131</v>
       </c>
       <c r="B83" t="n">
         <v>57720</v>
@@ -9647,16 +9652,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9667,14 +9672,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>583784</v>
+        <v>584025</v>
       </c>
       <c r="R83" t="n">
-        <v>7212338</v>
+        <v>7212370</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9709,11 +9714,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9726,22 +9726,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128998147</v>
+        <v>129000163</v>
       </c>
       <c r="B84" t="n">
-        <v>91526</v>
+        <v>91509</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9749,34 +9749,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>583732</v>
+        <v>584005</v>
       </c>
       <c r="R84" t="n">
-        <v>7212858</v>
+        <v>7211652</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9803,12 +9803,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9823,44 +9823,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129000181</v>
+        <v>129000106</v>
       </c>
       <c r="B85" t="n">
-        <v>79124</v>
+        <v>92210</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9870,10 +9870,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>583824</v>
+        <v>583634</v>
       </c>
       <c r="R85" t="n">
-        <v>7211526</v>
+        <v>7212397</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9900,12 +9900,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9932,10 +9932,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129000163</v>
+        <v>129000171</v>
       </c>
       <c r="B86" t="n">
-        <v>91504</v>
+        <v>91531</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9943,21 +9943,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9967,10 +9967,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>584005</v>
+        <v>583882</v>
       </c>
       <c r="R86" t="n">
-        <v>7211652</v>
+        <v>7212369</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9997,12 +9997,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10032,7 +10032,7 @@
         <v>129000159</v>
       </c>
       <c r="B87" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10126,10 +10126,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129000171</v>
+        <v>129000181</v>
       </c>
       <c r="B88" t="n">
-        <v>91526</v>
+        <v>79029</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10137,21 +10137,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10161,10 +10161,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>583882</v>
+        <v>583824</v>
       </c>
       <c r="R88" t="n">
-        <v>7212369</v>
+        <v>7211526</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10191,12 +10191,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10223,45 +10223,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129000106</v>
+        <v>128998147</v>
       </c>
       <c r="B89" t="n">
-        <v>92205</v>
+        <v>91531</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>583634</v>
+        <v>583732</v>
       </c>
       <c r="R89" t="n">
-        <v>7212397</v>
+        <v>7212858</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10308,44 +10308,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129000141</v>
+        <v>129000178</v>
       </c>
       <c r="B90" t="n">
-        <v>97507</v>
+        <v>79029</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10355,10 +10355,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>584301</v>
+        <v>583707</v>
       </c>
       <c r="R90" t="n">
-        <v>7211657</v>
+        <v>7212347</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10385,12 +10385,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10417,32 +10417,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129000178</v>
+        <v>129000141</v>
       </c>
       <c r="B91" t="n">
-        <v>79124</v>
+        <v>97514</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10452,10 +10452,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>583707</v>
+        <v>584301</v>
       </c>
       <c r="R91" t="n">
-        <v>7212347</v>
+        <v>7211657</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10482,12 +10482,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10514,45 +10514,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128998153</v>
+        <v>129000103</v>
       </c>
       <c r="B92" t="n">
-        <v>80264</v>
+        <v>91513</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>583842</v>
+        <v>583841</v>
       </c>
       <c r="R92" t="n">
-        <v>7212492</v>
+        <v>7212355</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10599,57 +10599,57 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128998133</v>
+        <v>129000189</v>
       </c>
       <c r="B93" t="n">
-        <v>80230</v>
+        <v>80169</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>583743</v>
+        <v>583856</v>
       </c>
       <c r="R93" t="n">
-        <v>7212862</v>
+        <v>7212375</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10696,44 +10696,44 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129000145</v>
+        <v>129000115</v>
       </c>
       <c r="B94" t="n">
-        <v>57720</v>
+        <v>80163</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10743,10 +10743,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>583826</v>
+        <v>583856</v>
       </c>
       <c r="R94" t="n">
-        <v>7211682</v>
+        <v>7212374</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10773,12 +10773,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10805,32 +10805,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129000149</v>
+        <v>129000145</v>
       </c>
       <c r="B95" t="n">
-        <v>97513</v>
+        <v>57723</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10840,10 +10840,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>583660</v>
+        <v>583826</v>
       </c>
       <c r="R95" t="n">
-        <v>7212365</v>
+        <v>7211682</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10870,12 +10870,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10902,32 +10902,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129000103</v>
+        <v>129000149</v>
       </c>
       <c r="B96" t="n">
-        <v>91508</v>
+        <v>97520</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10937,10 +10937,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>583841</v>
+        <v>583660</v>
       </c>
       <c r="R96" t="n">
-        <v>7212355</v>
+        <v>7212365</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10999,10 +10999,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129000115</v>
+        <v>128998153</v>
       </c>
       <c r="B97" t="n">
-        <v>80258</v>
+        <v>80169</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11010,34 +11010,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>583856</v>
+        <v>583842</v>
       </c>
       <c r="R97" t="n">
-        <v>7212374</v>
+        <v>7212492</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11084,57 +11084,57 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129000189</v>
+        <v>128998133</v>
       </c>
       <c r="B98" t="n">
-        <v>80264</v>
+        <v>80135</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>583856</v>
+        <v>583743</v>
       </c>
       <c r="R98" t="n">
-        <v>7212375</v>
+        <v>7212862</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11181,57 +11181,57 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128998134</v>
+        <v>129000188</v>
       </c>
       <c r="B99" t="n">
-        <v>91804</v>
+        <v>80169</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>583813</v>
+        <v>583606</v>
       </c>
       <c r="R99" t="n">
-        <v>7212866</v>
+        <v>7212484</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11278,44 +11278,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129000188</v>
+        <v>129000094</v>
       </c>
       <c r="B100" t="n">
-        <v>80264</v>
+        <v>83005</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11325,10 +11325,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>583606</v>
+        <v>583585</v>
       </c>
       <c r="R100" t="n">
-        <v>7212484</v>
+        <v>7212671</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11390,7 +11390,7 @@
         <v>129000110</v>
       </c>
       <c r="B101" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11484,10 +11484,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129000094</v>
+        <v>128998134</v>
       </c>
       <c r="B102" t="n">
-        <v>75209</v>
+        <v>91809</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11495,34 +11495,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>583585</v>
+        <v>583813</v>
       </c>
       <c r="R102" t="n">
-        <v>7212671</v>
+        <v>7212866</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11569,57 +11569,57 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128998152</v>
+        <v>129000100</v>
       </c>
       <c r="B103" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>583744</v>
+        <v>583841</v>
       </c>
       <c r="R103" t="n">
-        <v>7212703</v>
+        <v>7212873</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11666,12 +11666,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11681,7 +11681,7 @@
         <v>128998127</v>
       </c>
       <c r="B104" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11788,32 +11788,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129000100</v>
+        <v>129000096</v>
       </c>
       <c r="B105" t="n">
-        <v>91473</v>
+        <v>83005</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11823,10 +11823,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>583841</v>
+        <v>583980</v>
       </c>
       <c r="R105" t="n">
-        <v>7212873</v>
+        <v>7212363</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11885,10 +11885,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129000096</v>
+        <v>128998152</v>
       </c>
       <c r="B106" t="n">
-        <v>75209</v>
+        <v>79029</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11896,34 +11896,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>583980</v>
+        <v>583744</v>
       </c>
       <c r="R106" t="n">
-        <v>7212363</v>
+        <v>7212703</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11970,57 +11970,57 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128998130</v>
+        <v>129000116</v>
       </c>
       <c r="B107" t="n">
-        <v>80258</v>
+        <v>57720</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>583781</v>
+        <v>584099</v>
       </c>
       <c r="R107" t="n">
-        <v>7212767</v>
+        <v>7211521</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12047,12 +12047,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Spillkråkehack på låga</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12067,22 +12072,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129000165</v>
+        <v>128997035</v>
       </c>
       <c r="B108" t="n">
-        <v>91504</v>
+        <v>57883</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12090,21 +12095,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12114,10 +12119,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>583888</v>
+        <v>583868</v>
       </c>
       <c r="R108" t="n">
-        <v>7211663</v>
+        <v>7212926</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12144,12 +12149,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12164,22 +12169,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129000116</v>
+        <v>129000165</v>
       </c>
       <c r="B109" t="n">
-        <v>57717</v>
+        <v>91509</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12187,21 +12192,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12211,10 +12216,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>584099</v>
+        <v>583888</v>
       </c>
       <c r="R109" t="n">
-        <v>7211521</v>
+        <v>7211663</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12247,11 +12252,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Spillkråkehack på låga</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12281,7 +12281,7 @@
         <v>129000153</v>
       </c>
       <c r="B110" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>129000177</v>
       </c>
       <c r="B111" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12488,10 +12488,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128997035</v>
+        <v>128997040</v>
       </c>
       <c r="B112" t="n">
-        <v>57880</v>
+        <v>91509</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12499,21 +12499,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12523,10 +12523,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>583868</v>
+        <v>583800</v>
       </c>
       <c r="R112" t="n">
-        <v>7212926</v>
+        <v>7212621</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12585,45 +12585,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128997040</v>
+        <v>128998130</v>
       </c>
       <c r="B113" t="n">
-        <v>91504</v>
+        <v>80163</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>583800</v>
+        <v>583781</v>
       </c>
       <c r="R113" t="n">
-        <v>7212621</v>
+        <v>7212767</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12670,57 +12670,57 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128998155</v>
+        <v>129000175</v>
       </c>
       <c r="B114" t="n">
-        <v>80264</v>
+        <v>91531</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>583778</v>
+        <v>583975</v>
       </c>
       <c r="R114" t="n">
-        <v>7212766</v>
+        <v>7211530</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12747,12 +12747,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12767,57 +12767,57 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128998146</v>
+        <v>129000114</v>
       </c>
       <c r="B115" t="n">
-        <v>91526</v>
+        <v>80163</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>583700</v>
+        <v>583606</v>
       </c>
       <c r="R115" t="n">
-        <v>7212870</v>
+        <v>7212483</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12864,22 +12864,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128998150</v>
+        <v>128998146</v>
       </c>
       <c r="B116" t="n">
-        <v>79124</v>
+        <v>91531</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12887,21 +12887,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12911,10 +12911,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>583862</v>
+        <v>583700</v>
       </c>
       <c r="R116" t="n">
-        <v>7212466</v>
+        <v>7212870</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12973,45 +12973,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129000114</v>
+        <v>128998150</v>
       </c>
       <c r="B117" t="n">
-        <v>80258</v>
+        <v>79029</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>583606</v>
+        <v>583862</v>
       </c>
       <c r="R117" t="n">
-        <v>7212483</v>
+        <v>7212466</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13058,57 +13058,57 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129000175</v>
+        <v>128998155</v>
       </c>
       <c r="B118" t="n">
-        <v>91526</v>
+        <v>80169</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>583975</v>
+        <v>583778</v>
       </c>
       <c r="R118" t="n">
-        <v>7211530</v>
+        <v>7212766</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13135,12 +13135,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13155,57 +13155,57 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128998132</v>
+        <v>129000107</v>
       </c>
       <c r="B119" t="n">
-        <v>57717</v>
+        <v>92210</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>583834</v>
+        <v>583938</v>
       </c>
       <c r="R119" t="n">
-        <v>7212585</v>
+        <v>7211643</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13232,12 +13232,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13252,57 +13252,57 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128998136</v>
+        <v>129000150</v>
       </c>
       <c r="B120" t="n">
-        <v>80265</v>
+        <v>91882</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6464</v>
+        <v>1506</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>583838</v>
+        <v>583951</v>
       </c>
       <c r="R120" t="n">
-        <v>7212502</v>
+        <v>7211500</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13329,12 +13329,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13349,44 +13349,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129000150</v>
+        <v>129000104</v>
       </c>
       <c r="B121" t="n">
-        <v>91877</v>
+        <v>91513</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13396,10 +13396,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>583951</v>
+        <v>584023</v>
       </c>
       <c r="R121" t="n">
-        <v>7211500</v>
+        <v>7212353</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13426,12 +13426,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13458,45 +13458,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129000107</v>
+        <v>128998132</v>
       </c>
       <c r="B122" t="n">
-        <v>92205</v>
+        <v>57720</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>583938</v>
+        <v>583834</v>
       </c>
       <c r="R122" t="n">
-        <v>7211643</v>
+        <v>7212585</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13523,12 +13523,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13543,57 +13543,57 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129000104</v>
+        <v>128998136</v>
       </c>
       <c r="B123" t="n">
-        <v>91508</v>
+        <v>80170</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>584023</v>
+        <v>583838</v>
       </c>
       <c r="R123" t="n">
-        <v>7212353</v>
+        <v>7212502</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13640,22 +13640,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128997039</v>
+        <v>129000122</v>
       </c>
       <c r="B124" t="n">
-        <v>91504</v>
+        <v>80135</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13663,21 +13663,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>583807</v>
+        <v>583833</v>
       </c>
       <c r="R124" t="n">
-        <v>7212750</v>
+        <v>7212856</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13737,44 +13737,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129000147</v>
+        <v>129000170</v>
       </c>
       <c r="B125" t="n">
-        <v>97513</v>
+        <v>91527</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221941</v>
+        <v>1204</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13784,10 +13784,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>584141</v>
+        <v>583844</v>
       </c>
       <c r="R125" t="n">
-        <v>7211590</v>
+        <v>7212348</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13814,12 +13814,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13846,32 +13846,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129000126</v>
+        <v>129000147</v>
       </c>
       <c r="B126" t="n">
-        <v>75214</v>
+        <v>97520</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1467</v>
+        <v>221941</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13881,10 +13881,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>583693</v>
+        <v>584141</v>
       </c>
       <c r="R126" t="n">
-        <v>7211591</v>
+        <v>7211590</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13943,10 +13943,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129000122</v>
+        <v>129000126</v>
       </c>
       <c r="B127" t="n">
-        <v>80230</v>
+        <v>83010</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13954,21 +13954,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13978,10 +13978,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>583833</v>
+        <v>583693</v>
       </c>
       <c r="R127" t="n">
-        <v>7212856</v>
+        <v>7211591</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14008,12 +14008,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14040,10 +14040,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129000170</v>
+        <v>129000130</v>
       </c>
       <c r="B128" t="n">
-        <v>91522</v>
+        <v>57723</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14051,21 +14051,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14075,10 +14075,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>583844</v>
+        <v>584350</v>
       </c>
       <c r="R128" t="n">
-        <v>7212348</v>
+        <v>7211690</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14105,12 +14105,17 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14137,10 +14142,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129000130</v>
+        <v>128997039</v>
       </c>
       <c r="B129" t="n">
-        <v>57720</v>
+        <v>91509</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14148,21 +14153,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14172,10 +14177,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>584350</v>
+        <v>583807</v>
       </c>
       <c r="R129" t="n">
-        <v>7211690</v>
+        <v>7212750</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14202,17 +14207,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Äldre och färska ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14227,12 +14227,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -14242,7 +14242,7 @@
         <v>128998250</v>
       </c>
       <c r="B130" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14349,45 +14349,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128998126</v>
+        <v>129000187</v>
       </c>
       <c r="B131" t="n">
-        <v>92205</v>
+        <v>88913</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3298</v>
+        <v>510</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>583748</v>
+        <v>583966</v>
       </c>
       <c r="R131" t="n">
-        <v>7212869</v>
+        <v>7211510</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14414,12 +14414,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14434,22 +14434,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128998149</v>
+        <v>129000176</v>
       </c>
       <c r="B132" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14477,14 +14477,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>584059</v>
+        <v>583766</v>
       </c>
       <c r="R132" t="n">
-        <v>7212428</v>
+        <v>7212828</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14531,22 +14531,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129000176</v>
+        <v>128998149</v>
       </c>
       <c r="B133" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14574,14 +14574,14 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>583766</v>
+        <v>584059</v>
       </c>
       <c r="R133" t="n">
-        <v>7212828</v>
+        <v>7212428</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14628,39 +14628,39 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129000157</v>
+        <v>129000146</v>
       </c>
       <c r="B134" t="n">
-        <v>57824</v>
+        <v>57723</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -14675,10 +14675,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>583712</v>
+        <v>583819</v>
       </c>
       <c r="R134" t="n">
-        <v>7211576</v>
+        <v>7211689</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14711,6 +14711,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14737,27 +14742,27 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129000146</v>
+        <v>129000157</v>
       </c>
       <c r="B135" t="n">
-        <v>57720</v>
+        <v>57827</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -14772,10 +14777,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>583819</v>
+        <v>583712</v>
       </c>
       <c r="R135" t="n">
-        <v>7211689</v>
+        <v>7211576</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14808,11 +14813,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14839,45 +14839,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129000187</v>
+        <v>128998126</v>
       </c>
       <c r="B136" t="n">
-        <v>88908</v>
+        <v>92210</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>510</v>
+        <v>3298</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>583966</v>
+        <v>583748</v>
       </c>
       <c r="R136" t="n">
-        <v>7211510</v>
+        <v>7212869</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14904,12 +14904,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14924,57 +14924,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128998138</v>
+        <v>129000172</v>
       </c>
       <c r="B137" t="n">
-        <v>80265</v>
+        <v>91531</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>583742</v>
+        <v>583719</v>
       </c>
       <c r="R137" t="n">
-        <v>7213116</v>
+        <v>7212791</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15021,22 +15021,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129000124</v>
+        <v>129000173</v>
       </c>
       <c r="B138" t="n">
-        <v>75214</v>
+        <v>91531</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15044,21 +15044,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15068,10 +15068,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>583770</v>
+        <v>583879</v>
       </c>
       <c r="R138" t="n">
-        <v>7212830</v>
+        <v>7211699</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15098,12 +15098,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15130,10 +15130,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129000172</v>
+        <v>129000124</v>
       </c>
       <c r="B139" t="n">
-        <v>91526</v>
+        <v>83010</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15141,21 +15141,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15165,10 +15165,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>583719</v>
+        <v>583770</v>
       </c>
       <c r="R139" t="n">
-        <v>7212791</v>
+        <v>7212830</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15227,45 +15227,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129000173</v>
+        <v>128998138</v>
       </c>
       <c r="B140" t="n">
-        <v>91526</v>
+        <v>80170</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>583879</v>
+        <v>583742</v>
       </c>
       <c r="R140" t="n">
-        <v>7211699</v>
+        <v>7213116</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15312,22 +15312,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129000097</v>
+        <v>129000182</v>
       </c>
       <c r="B141" t="n">
-        <v>75209</v>
+        <v>79029</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15335,21 +15335,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15359,10 +15359,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>584170</v>
+        <v>584124</v>
       </c>
       <c r="R141" t="n">
-        <v>7211600</v>
+        <v>7211556</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15421,10 +15421,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129000135</v>
+        <v>129000097</v>
       </c>
       <c r="B142" t="n">
-        <v>57720</v>
+        <v>83005</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15432,21 +15432,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15456,10 +15456,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>584139</v>
+        <v>584170</v>
       </c>
       <c r="R142" t="n">
-        <v>7211559</v>
+        <v>7211600</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15492,11 +15492,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15526,7 +15521,7 @@
         <v>129000119</v>
       </c>
       <c r="B143" t="n">
-        <v>75207</v>
+        <v>83003</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15620,10 +15615,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129000182</v>
+        <v>129000135</v>
       </c>
       <c r="B144" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15631,21 +15626,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15655,10 +15650,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>584124</v>
+        <v>584139</v>
       </c>
       <c r="R144" t="n">
-        <v>7211556</v>
+        <v>7211559</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15691,6 +15686,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15717,10 +15717,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128998151</v>
+        <v>129000101</v>
       </c>
       <c r="B145" t="n">
-        <v>79124</v>
+        <v>91513</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15728,34 +15728,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>583830</v>
+        <v>583663</v>
       </c>
       <c r="R145" t="n">
-        <v>7212605</v>
+        <v>7212429</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15802,57 +15802,57 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128998148</v>
+        <v>129000169</v>
       </c>
       <c r="B146" t="n">
-        <v>91526</v>
+        <v>82988</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>583764</v>
+        <v>583695</v>
       </c>
       <c r="R146" t="n">
-        <v>7212875</v>
+        <v>7211591</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15879,12 +15879,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15899,57 +15899,57 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128998129</v>
+        <v>129000144</v>
       </c>
       <c r="B147" t="n">
-        <v>80258</v>
+        <v>57723</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>583743</v>
+        <v>583832</v>
       </c>
       <c r="R147" t="n">
-        <v>7212862</v>
+        <v>7211693</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15976,12 +15976,17 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15996,44 +16001,44 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128998154</v>
+        <v>128998148</v>
       </c>
       <c r="B148" t="n">
-        <v>80264</v>
+        <v>91531</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16043,10 +16048,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>583743</v>
+        <v>583764</v>
       </c>
       <c r="R148" t="n">
-        <v>7212862</v>
+        <v>7212875</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16105,10 +16110,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129000169</v>
+        <v>128998129</v>
       </c>
       <c r="B149" t="n">
-        <v>75192</v>
+        <v>80163</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16116,34 +16121,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6439</v>
+        <v>6462</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>583695</v>
+        <v>583743</v>
       </c>
       <c r="R149" t="n">
-        <v>7211591</v>
+        <v>7212862</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16170,12 +16175,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16190,57 +16195,57 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129000101</v>
+        <v>128998154</v>
       </c>
       <c r="B150" t="n">
-        <v>91508</v>
+        <v>80169</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>583663</v>
+        <v>583743</v>
       </c>
       <c r="R150" t="n">
-        <v>7212429</v>
+        <v>7212862</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16287,22 +16292,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129000144</v>
+        <v>128998151</v>
       </c>
       <c r="B151" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16310,34 +16315,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>583832</v>
+        <v>583830</v>
       </c>
       <c r="R151" t="n">
-        <v>7211693</v>
+        <v>7212605</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16364,17 +16369,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16389,12 +16389,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -16404,7 +16404,7 @@
         <v>129000129</v>
       </c>
       <c r="B152" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16498,10 +16498,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128998141</v>
+        <v>129000121</v>
       </c>
       <c r="B153" t="n">
-        <v>91504</v>
+        <v>80135</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16509,34 +16509,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>583789</v>
+        <v>583770</v>
       </c>
       <c r="R153" t="n">
-        <v>7213129</v>
+        <v>7212825</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16583,22 +16583,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129000180</v>
+        <v>129000160</v>
       </c>
       <c r="B154" t="n">
-        <v>79124</v>
+        <v>91509</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16606,21 +16606,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16630,10 +16630,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>583695</v>
+        <v>583674</v>
       </c>
       <c r="R154" t="n">
-        <v>7211621</v>
+        <v>7212755</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16660,12 +16660,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16692,10 +16692,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129000132</v>
+        <v>129000180</v>
       </c>
       <c r="B155" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16703,21 +16703,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16727,10 +16727,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>583968</v>
+        <v>583695</v>
       </c>
       <c r="R155" t="n">
-        <v>7212362</v>
+        <v>7211621</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16757,17 +16757,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16794,10 +16789,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129000121</v>
+        <v>129000132</v>
       </c>
       <c r="B156" t="n">
-        <v>80230</v>
+        <v>57723</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16805,21 +16800,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16829,10 +16824,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>583770</v>
+        <v>583968</v>
       </c>
       <c r="R156" t="n">
-        <v>7212825</v>
+        <v>7212362</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16865,6 +16860,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16891,10 +16891,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129000160</v>
+        <v>129000142</v>
       </c>
       <c r="B157" t="n">
-        <v>91504</v>
+        <v>57723</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16902,21 +16902,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16926,10 +16926,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>583674</v>
+        <v>583922</v>
       </c>
       <c r="R157" t="n">
-        <v>7212755</v>
+        <v>7211662</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16956,12 +16956,17 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16988,10 +16993,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129000142</v>
+        <v>128998141</v>
       </c>
       <c r="B158" t="n">
-        <v>57720</v>
+        <v>91509</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16999,34 +17004,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>583922</v>
+        <v>583789</v>
       </c>
       <c r="R158" t="n">
-        <v>7211662</v>
+        <v>7213129</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17053,17 +17058,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17078,22 +17078,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129000168</v>
+        <v>129000166</v>
       </c>
       <c r="B159" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17125,10 +17125,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>584331</v>
+        <v>583796</v>
       </c>
       <c r="R159" t="n">
-        <v>7211693</v>
+        <v>7211546</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17187,10 +17187,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129000184</v>
+        <v>129000168</v>
       </c>
       <c r="B160" t="n">
-        <v>79124</v>
+        <v>91509</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17198,21 +17198,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17222,10 +17222,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>584333</v>
+        <v>584331</v>
       </c>
       <c r="R160" t="n">
-        <v>7211688</v>
+        <v>7211693</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17284,45 +17284,48 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129000166</v>
+        <v>129000185</v>
       </c>
       <c r="B161" t="n">
-        <v>91504</v>
+        <v>92839</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1108</v>
+        <v>5964</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>583796</v>
+        <v>584074</v>
       </c>
       <c r="R161" t="n">
-        <v>7211546</v>
+        <v>7211675</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17363,6 +17366,7 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -17381,48 +17385,45 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129000185</v>
+        <v>129000184</v>
       </c>
       <c r="B162" t="n">
-        <v>92834</v>
+        <v>79029</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>584074</v>
+        <v>584333</v>
       </c>
       <c r="R162" t="n">
-        <v>7211675</v>
+        <v>7211688</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17463,7 +17464,6 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -17482,10 +17482,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129000174</v>
+        <v>129000167</v>
       </c>
       <c r="B163" t="n">
-        <v>91526</v>
+        <v>91509</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17493,21 +17493,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17517,10 +17517,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>583934</v>
+        <v>584144</v>
       </c>
       <c r="R163" t="n">
-        <v>7211520</v>
+        <v>7211566</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17579,10 +17579,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129000167</v>
+        <v>129000162</v>
       </c>
       <c r="B164" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17614,10 +17614,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>584144</v>
+        <v>583583</v>
       </c>
       <c r="R164" t="n">
-        <v>7211566</v>
+        <v>7212676</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17644,12 +17644,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17676,10 +17676,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129000162</v>
+        <v>129000174</v>
       </c>
       <c r="B165" t="n">
-        <v>91504</v>
+        <v>91531</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17687,21 +17687,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17711,10 +17711,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>583583</v>
+        <v>583934</v>
       </c>
       <c r="R165" t="n">
-        <v>7212676</v>
+        <v>7211520</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17741,12 +17741,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17773,32 +17773,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129000138</v>
+        <v>129000154</v>
       </c>
       <c r="B166" t="n">
-        <v>57720</v>
+        <v>80170</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17808,10 +17808,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>583805</v>
+        <v>583832</v>
       </c>
       <c r="R166" t="n">
-        <v>7211693</v>
+        <v>7212853</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17838,17 +17838,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17875,32 +17870,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129000154</v>
+        <v>129000138</v>
       </c>
       <c r="B167" t="n">
-        <v>80265</v>
+        <v>57723</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17910,10 +17905,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>583832</v>
+        <v>583805</v>
       </c>
       <c r="R167" t="n">
-        <v>7212853</v>
+        <v>7211693</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17940,12 +17935,17 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17969,6 +17969,301 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>129012557</v>
+      </c>
+      <c r="B168" t="n">
+        <v>88913</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>510</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>583791</v>
+      </c>
+      <c r="R168" t="n">
+        <v>7212873</v>
+      </c>
+      <c r="S168" t="n">
+        <v>10</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>129012558</v>
+      </c>
+      <c r="B169" t="n">
+        <v>92183</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>898</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>583785</v>
+      </c>
+      <c r="R169" t="n">
+        <v>7212893</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>129012556</v>
+      </c>
+      <c r="B170" t="n">
+        <v>91871</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Inre Verkansliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>583784</v>
+      </c>
+      <c r="R170" t="n">
+        <v>7212888</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -8171,45 +8171,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129000140</v>
+        <v>128998144</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>82993</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>584092</v>
+        <v>583765</v>
       </c>
       <c r="R68" t="n">
-        <v>7211517</v>
+        <v>7212611</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8236,17 +8236,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8261,22 +8256,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128998140</v>
+        <v>129000140</v>
       </c>
       <c r="B69" t="n">
-        <v>91516</v>
+        <v>57723</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8284,34 +8279,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>583855</v>
+        <v>584092</v>
       </c>
       <c r="R69" t="n">
-        <v>7213081</v>
+        <v>7211517</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8338,12 +8333,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8358,44 +8358,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128998144</v>
+        <v>128998140</v>
       </c>
       <c r="B70" t="n">
-        <v>82993</v>
+        <v>91516</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6439</v>
+        <v>1108</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583765</v>
+        <v>583855</v>
       </c>
       <c r="R70" t="n">
-        <v>7212611</v>
+        <v>7213081</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8467,32 +8467,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129000183</v>
+        <v>128997038</v>
       </c>
       <c r="B71" t="n">
-        <v>79034</v>
+        <v>97528</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>584220</v>
+        <v>583850</v>
       </c>
       <c r="R71" t="n">
-        <v>7211664</v>
+        <v>7212515</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8532,12 +8532,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8552,44 +8552,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128998142</v>
+        <v>128998122</v>
       </c>
       <c r="B72" t="n">
-        <v>91516</v>
+        <v>105699</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1108</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8599,10 +8599,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583800</v>
+        <v>583934</v>
       </c>
       <c r="R72" t="n">
-        <v>7212769</v>
+        <v>7212490</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8661,32 +8661,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128997038</v>
+        <v>129000183</v>
       </c>
       <c r="B73" t="n">
-        <v>97528</v>
+        <v>79034</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8696,10 +8696,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583850</v>
+        <v>584220</v>
       </c>
       <c r="R73" t="n">
-        <v>7212515</v>
+        <v>7211664</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8726,12 +8726,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8746,44 +8746,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128998122</v>
+        <v>128998142</v>
       </c>
       <c r="B74" t="n">
-        <v>105699</v>
+        <v>91516</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221725</v>
+        <v>1108</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8793,10 +8793,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583934</v>
+        <v>583800</v>
       </c>
       <c r="R74" t="n">
-        <v>7212490</v>
+        <v>7212769</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10420,7 +10420,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128997040</v>
+        <v>129000165</v>
       </c>
       <c r="B91" t="n">
         <v>91516</v>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>583800</v>
+        <v>583888</v>
       </c>
       <c r="R91" t="n">
-        <v>7212621</v>
+        <v>7211663</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10485,12 +10485,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10505,22 +10505,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128997035</v>
+        <v>129000116</v>
       </c>
       <c r="B92" t="n">
-        <v>57883</v>
+        <v>57720</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10528,21 +10528,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10552,10 +10552,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>583868</v>
+        <v>584099</v>
       </c>
       <c r="R92" t="n">
-        <v>7212926</v>
+        <v>7211521</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10582,12 +10582,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Spillkråkehack på låga</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10602,19 +10607,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129000165</v>
+        <v>128997040</v>
       </c>
       <c r="B93" t="n">
         <v>91516</v>
@@ -10649,10 +10654,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>583888</v>
+        <v>583800</v>
       </c>
       <c r="R93" t="n">
-        <v>7211663</v>
+        <v>7212621</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10679,12 +10684,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10699,57 +10704,57 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129000116</v>
+        <v>128998130</v>
       </c>
       <c r="B94" t="n">
-        <v>57720</v>
+        <v>80168</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>584099</v>
+        <v>583781</v>
       </c>
       <c r="R94" t="n">
-        <v>7211521</v>
+        <v>7212767</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10776,17 +10781,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Spillkråkehack på låga</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10801,57 +10801,57 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128998130</v>
+        <v>128997035</v>
       </c>
       <c r="B95" t="n">
-        <v>80168</v>
+        <v>57883</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>583781</v>
+        <v>583868</v>
       </c>
       <c r="R95" t="n">
-        <v>7212767</v>
+        <v>7212926</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10898,22 +10898,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128998146</v>
+        <v>128998150</v>
       </c>
       <c r="B96" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10921,21 +10921,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10945,10 +10945,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>583700</v>
+        <v>583862</v>
       </c>
       <c r="R96" t="n">
-        <v>7212870</v>
+        <v>7212466</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11007,10 +11007,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128998150</v>
+        <v>129000175</v>
       </c>
       <c r="B97" t="n">
-        <v>79034</v>
+        <v>91538</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11018,34 +11018,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>583862</v>
+        <v>583975</v>
       </c>
       <c r="R97" t="n">
-        <v>7212466</v>
+        <v>7211530</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11072,12 +11072,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11092,19 +11092,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129000175</v>
+        <v>128998146</v>
       </c>
       <c r="B98" t="n">
         <v>91538</v>
@@ -11135,14 +11135,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>583975</v>
+        <v>583700</v>
       </c>
       <c r="R98" t="n">
-        <v>7211530</v>
+        <v>7212870</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11169,12 +11169,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11189,12 +11189,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -11298,45 +11298,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128998136</v>
+        <v>129000150</v>
       </c>
       <c r="B100" t="n">
-        <v>80175</v>
+        <v>91890</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6464</v>
+        <v>1506</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>583838</v>
+        <v>583951</v>
       </c>
       <c r="R100" t="n">
-        <v>7212502</v>
+        <v>7211500</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11363,12 +11363,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11383,12 +11383,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11492,45 +11492,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129000150</v>
+        <v>128998132</v>
       </c>
       <c r="B102" t="n">
-        <v>91890</v>
+        <v>57720</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1506</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>583951</v>
+        <v>583834</v>
       </c>
       <c r="R102" t="n">
-        <v>7211500</v>
+        <v>7212585</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11557,12 +11557,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11577,44 +11577,44 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128998132</v>
+        <v>128998136</v>
       </c>
       <c r="B103" t="n">
-        <v>57720</v>
+        <v>80175</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11624,10 +11624,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>583834</v>
+        <v>583838</v>
       </c>
       <c r="R103" t="n">
-        <v>7212585</v>
+        <v>7212502</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11686,10 +11686,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129000126</v>
+        <v>128998250</v>
       </c>
       <c r="B104" t="n">
-        <v>83015</v>
+        <v>57723</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11697,34 +11697,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>583693</v>
+        <v>583752</v>
       </c>
       <c r="R104" t="n">
-        <v>7211591</v>
+        <v>7212679</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11751,12 +11759,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11771,22 +11784,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129000130</v>
+        <v>129000126</v>
       </c>
       <c r="B105" t="n">
-        <v>57723</v>
+        <v>83015</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11794,21 +11807,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11818,10 +11831,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>584350</v>
+        <v>583693</v>
       </c>
       <c r="R105" t="n">
-        <v>7211690</v>
+        <v>7211591</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11854,11 +11867,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11885,32 +11893,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129000147</v>
+        <v>129000130</v>
       </c>
       <c r="B106" t="n">
-        <v>97528</v>
+        <v>57723</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11920,10 +11928,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>584141</v>
+        <v>584350</v>
       </c>
       <c r="R106" t="n">
-        <v>7211590</v>
+        <v>7211690</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11956,6 +11964,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11982,32 +11995,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128997039</v>
+        <v>129000147</v>
       </c>
       <c r="B107" t="n">
-        <v>91516</v>
+        <v>97528</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1108</v>
+        <v>221941</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12017,10 +12030,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>583807</v>
+        <v>584141</v>
       </c>
       <c r="R107" t="n">
-        <v>7212750</v>
+        <v>7211590</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12047,12 +12060,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12067,22 +12080,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128998250</v>
+        <v>128997039</v>
       </c>
       <c r="B108" t="n">
-        <v>57723</v>
+        <v>91516</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12090,42 +12103,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>583752</v>
+        <v>583807</v>
       </c>
       <c r="R108" t="n">
-        <v>7212679</v>
+        <v>7212750</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12160,11 +12165,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -12177,12 +12177,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -12388,10 +12388,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128998126</v>
+        <v>129000157</v>
       </c>
       <c r="B111" t="n">
-        <v>92218</v>
+        <v>57827</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12399,34 +12399,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3298</v>
+        <v>103031</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>583748</v>
+        <v>583712</v>
       </c>
       <c r="R111" t="n">
-        <v>7212869</v>
+        <v>7211576</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12453,12 +12453,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12473,22 +12473,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129000157</v>
+        <v>128998126</v>
       </c>
       <c r="B112" t="n">
-        <v>57827</v>
+        <v>92218</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12496,34 +12496,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>103031</v>
+        <v>3298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>583712</v>
+        <v>583748</v>
       </c>
       <c r="R112" t="n">
-        <v>7211576</v>
+        <v>7212869</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12550,12 +12550,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12570,12 +12570,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -13363,10 +13363,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128998148</v>
+        <v>129000144</v>
       </c>
       <c r="B121" t="n">
-        <v>91538</v>
+        <v>57723</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13374,34 +13374,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>583764</v>
+        <v>583832</v>
       </c>
       <c r="R121" t="n">
-        <v>7212875</v>
+        <v>7211693</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13428,12 +13428,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13448,22 +13453,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129000144</v>
+        <v>128998148</v>
       </c>
       <c r="B122" t="n">
-        <v>57723</v>
+        <v>91538</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13471,34 +13476,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>583832</v>
+        <v>583764</v>
       </c>
       <c r="R122" t="n">
-        <v>7211693</v>
+        <v>7212875</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13525,17 +13530,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13550,12 +13550,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -14149,10 +14149,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129000166</v>
+        <v>129000184</v>
       </c>
       <c r="B129" t="n">
-        <v>91516</v>
+        <v>79034</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14160,21 +14160,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14184,10 +14184,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>583796</v>
+        <v>584333</v>
       </c>
       <c r="R129" t="n">
-        <v>7211546</v>
+        <v>7211688</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14246,7 +14246,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129000168</v>
+        <v>129000166</v>
       </c>
       <c r="B130" t="n">
         <v>91516</v>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>584331</v>
+        <v>583796</v>
       </c>
       <c r="R130" t="n">
-        <v>7211693</v>
+        <v>7211546</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14343,10 +14343,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129000184</v>
+        <v>129000168</v>
       </c>
       <c r="B131" t="n">
-        <v>79034</v>
+        <v>91516</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14354,21 +14354,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14378,10 +14378,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>584333</v>
+        <v>584331</v>
       </c>
       <c r="R131" t="n">
-        <v>7211688</v>
+        <v>7211693</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15631,10 +15631,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129085077</v>
+        <v>129000137</v>
       </c>
       <c r="B144" t="n">
-        <v>91520</v>
+        <v>57723</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15642,37 +15642,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>583874</v>
+        <v>583784</v>
       </c>
       <c r="R144" t="n">
-        <v>7212775</v>
+        <v>7212338</v>
       </c>
       <c r="S144" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15702,6 +15702,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15716,19 +15721,19 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129085080</v>
+        <v>129085077</v>
       </c>
       <c r="B145" t="n">
         <v>91520</v>
@@ -15763,10 +15768,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>583726</v>
+        <v>583874</v>
       </c>
       <c r="R145" t="n">
-        <v>7212315</v>
+        <v>7212775</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15825,10 +15830,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129000137</v>
+        <v>129085080</v>
       </c>
       <c r="B146" t="n">
-        <v>57723</v>
+        <v>91520</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15836,37 +15841,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>583784</v>
+        <v>583726</v>
       </c>
       <c r="R146" t="n">
-        <v>7212338</v>
+        <v>7212315</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15896,11 +15901,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15915,44 +15915,44 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129000106</v>
+        <v>129000159</v>
       </c>
       <c r="B147" t="n">
-        <v>92218</v>
+        <v>56904</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3298</v>
+        <v>102612</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15962,10 +15962,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>583634</v>
+        <v>583817</v>
       </c>
       <c r="R147" t="n">
-        <v>7212397</v>
+        <v>7212328</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16024,32 +16024,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129000171</v>
+        <v>129000106</v>
       </c>
       <c r="B148" t="n">
-        <v>91538</v>
+        <v>92218</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16059,10 +16059,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>583882</v>
+        <v>583634</v>
       </c>
       <c r="R148" t="n">
-        <v>7212369</v>
+        <v>7212397</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16121,10 +16121,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129000159</v>
+        <v>129000171</v>
       </c>
       <c r="B149" t="n">
-        <v>56904</v>
+        <v>91538</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16132,21 +16132,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16156,10 +16156,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>583817</v>
+        <v>583882</v>
       </c>
       <c r="R149" t="n">
-        <v>7212328</v>
+        <v>7212369</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16509,32 +16509,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129000103</v>
+        <v>129000189</v>
       </c>
       <c r="B153" t="n">
-        <v>91520</v>
+        <v>80174</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16544,10 +16544,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>583841</v>
+        <v>583856</v>
       </c>
       <c r="R153" t="n">
-        <v>7212355</v>
+        <v>7212375</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16606,10 +16606,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129085076</v>
+        <v>129000149</v>
       </c>
       <c r="B154" t="n">
-        <v>91485</v>
+        <v>97528</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16617,37 +16617,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>583540</v>
+        <v>583660</v>
       </c>
       <c r="R154" t="n">
-        <v>7212450</v>
+        <v>7212365</v>
       </c>
       <c r="S154" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16691,22 +16691,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129000189</v>
+        <v>129085076</v>
       </c>
       <c r="B155" t="n">
-        <v>80174</v>
+        <v>91485</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16714,37 +16714,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>583856</v>
+        <v>583540</v>
       </c>
       <c r="R155" t="n">
-        <v>7212375</v>
+        <v>7212450</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16788,44 +16788,44 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129000149</v>
+        <v>129000103</v>
       </c>
       <c r="B156" t="n">
-        <v>97528</v>
+        <v>91520</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16835,10 +16835,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>583660</v>
+        <v>583841</v>
       </c>
       <c r="R156" t="n">
-        <v>7212365</v>
+        <v>7212355</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17789,10 +17789,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129000114</v>
+        <v>129085074</v>
       </c>
       <c r="B166" t="n">
-        <v>80168</v>
+        <v>105699</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17800,37 +17800,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>583606</v>
+        <v>583517</v>
       </c>
       <c r="R166" t="n">
-        <v>7212483</v>
+        <v>7212494</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17874,19 +17874,19 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129085074</v>
+        <v>129085075</v>
       </c>
       <c r="B167" t="n">
         <v>105699</v>
@@ -17921,10 +17921,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>583517</v>
+        <v>583896</v>
       </c>
       <c r="R167" t="n">
-        <v>7212494</v>
+        <v>7212322</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -17983,10 +17983,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129085075</v>
+        <v>129000114</v>
       </c>
       <c r="B168" t="n">
-        <v>105699</v>
+        <v>80168</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17994,37 +17994,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>583896</v>
+        <v>583606</v>
       </c>
       <c r="R168" t="n">
-        <v>7212322</v>
+        <v>7212483</v>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18068,19 +18068,19 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129085078</v>
+        <v>129000104</v>
       </c>
       <c r="B169" t="n">
         <v>91520</v>
@@ -18111,17 +18111,17 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>583677</v>
+        <v>584023</v>
       </c>
       <c r="R169" t="n">
-        <v>7212815</v>
+        <v>7212353</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18165,19 +18165,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129000104</v>
+        <v>129085078</v>
       </c>
       <c r="B170" t="n">
         <v>91520</v>
@@ -18208,17 +18208,17 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>584023</v>
+        <v>583677</v>
       </c>
       <c r="R170" t="n">
-        <v>7212353</v>
+        <v>7212815</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18262,12 +18262,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -19147,10 +19147,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129000129</v>
+        <v>129085095</v>
       </c>
       <c r="B180" t="n">
-        <v>91805</v>
+        <v>91538</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19158,37 +19158,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>583810</v>
+        <v>583378</v>
       </c>
       <c r="R180" t="n">
-        <v>7212852</v>
+        <v>7212728</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19232,44 +19232,44 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129073201</v>
+        <v>129073202</v>
       </c>
       <c r="B181" t="n">
-        <v>92308</v>
+        <v>95501</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>918</v>
+        <v>2387</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19279,10 +19279,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>583599</v>
+        <v>584165</v>
       </c>
       <c r="R181" t="n">
-        <v>7212710</v>
+        <v>7211601</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19309,12 +19309,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19341,32 +19341,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129000101</v>
+        <v>129073201</v>
       </c>
       <c r="B182" t="n">
-        <v>91520</v>
+        <v>92308</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1202</v>
+        <v>918</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19376,10 +19376,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>583663</v>
+        <v>583599</v>
       </c>
       <c r="R182" t="n">
-        <v>7212429</v>
+        <v>7212710</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19431,17 +19431,17 @@
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129085095</v>
+        <v>129000101</v>
       </c>
       <c r="B183" t="n">
-        <v>91538</v>
+        <v>91520</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19449,37 +19449,37 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>583378</v>
+        <v>583663</v>
       </c>
       <c r="R183" t="n">
-        <v>7212728</v>
+        <v>7212429</v>
       </c>
       <c r="S183" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -19523,44 +19523,44 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129073202</v>
+        <v>129000129</v>
       </c>
       <c r="B184" t="n">
-        <v>95501</v>
+        <v>91805</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2387</v>
+        <v>658</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19570,10 +19570,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>584165</v>
+        <v>583810</v>
       </c>
       <c r="R184" t="n">
-        <v>7211601</v>
+        <v>7212852</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19600,12 +19600,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19625,7 +19625,7 @@
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
@@ -19826,7 +19826,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129000132</v>
+        <v>129085086</v>
       </c>
       <c r="B187" t="n">
         <v>57723</v>
@@ -19855,19 +19855,23 @@
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>583968</v>
+        <v>583569</v>
       </c>
       <c r="R187" t="n">
-        <v>7212362</v>
+        <v>7212757</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19901,7 +19905,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19916,60 +19920,60 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129085082</v>
+        <v>129000132</v>
       </c>
       <c r="B188" t="n">
-        <v>80168</v>
+        <v>57723</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>583926</v>
+        <v>583968</v>
       </c>
       <c r="R188" t="n">
-        <v>7212799</v>
+        <v>7212362</v>
       </c>
       <c r="S188" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19999,6 +20003,11 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20013,61 +20022,57 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129085086</v>
+        <v>129085082</v>
       </c>
       <c r="B189" t="n">
-        <v>57723</v>
+        <v>80168</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>583569</v>
+        <v>583926</v>
       </c>
       <c r="R189" t="n">
-        <v>7212757</v>
+        <v>7212799</v>
       </c>
       <c r="S189" t="n">
         <v>15</v>
@@ -20100,11 +20105,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">

--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -8171,45 +8171,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128998144</v>
+        <v>129000140</v>
       </c>
       <c r="B68" t="n">
-        <v>82993</v>
+        <v>57723</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583765</v>
+        <v>584092</v>
       </c>
       <c r="R68" t="n">
-        <v>7212611</v>
+        <v>7211517</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8236,12 +8236,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8256,57 +8261,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129000140</v>
+        <v>128998144</v>
       </c>
       <c r="B69" t="n">
-        <v>57723</v>
+        <v>82993</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>584092</v>
+        <v>583765</v>
       </c>
       <c r="R69" t="n">
-        <v>7211517</v>
+        <v>7212611</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8333,17 +8338,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8358,12 +8358,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8373,7 +8373,7 @@
         <v>128998140</v>
       </c>
       <c r="B70" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8467,32 +8467,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128997038</v>
+        <v>129000183</v>
       </c>
       <c r="B71" t="n">
-        <v>97528</v>
+        <v>79034</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>583850</v>
+        <v>584220</v>
       </c>
       <c r="R71" t="n">
-        <v>7212515</v>
+        <v>7211664</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8532,12 +8532,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8552,44 +8552,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128998122</v>
+        <v>128998142</v>
       </c>
       <c r="B72" t="n">
-        <v>105699</v>
+        <v>91519</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>1108</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8599,10 +8599,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583934</v>
+        <v>583800</v>
       </c>
       <c r="R72" t="n">
-        <v>7212490</v>
+        <v>7212769</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8661,32 +8661,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129000183</v>
+        <v>128997038</v>
       </c>
       <c r="B73" t="n">
-        <v>79034</v>
+        <v>97533</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8696,10 +8696,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>584220</v>
+        <v>583850</v>
       </c>
       <c r="R73" t="n">
-        <v>7211664</v>
+        <v>7212515</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8726,12 +8726,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8746,44 +8746,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128998142</v>
+        <v>128998122</v>
       </c>
       <c r="B74" t="n">
-        <v>91516</v>
+        <v>105704</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1108</v>
+        <v>221725</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8793,10 +8793,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583800</v>
+        <v>583934</v>
       </c>
       <c r="R74" t="n">
-        <v>7212769</v>
+        <v>7212490</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8855,45 +8855,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129000152</v>
+        <v>128998128</v>
       </c>
       <c r="B75" t="n">
-        <v>80167</v>
+        <v>57883</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>584338</v>
+        <v>583799</v>
       </c>
       <c r="R75" t="n">
-        <v>7211689</v>
+        <v>7212748</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8940,57 +8940,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128998128</v>
+        <v>129000152</v>
       </c>
       <c r="B76" t="n">
-        <v>57883</v>
+        <v>80167</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583799</v>
+        <v>584338</v>
       </c>
       <c r="R76" t="n">
-        <v>7212748</v>
+        <v>7211689</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9017,12 +9017,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9037,44 +9037,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128998135</v>
+        <v>128998124</v>
       </c>
       <c r="B77" t="n">
-        <v>91890</v>
+        <v>91523</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583778</v>
+        <v>583784</v>
       </c>
       <c r="R77" t="n">
-        <v>7212890</v>
+        <v>7212884</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9146,10 +9146,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128998124</v>
+        <v>128998131</v>
       </c>
       <c r="B78" t="n">
-        <v>91520</v>
+        <v>57720</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9157,21 +9157,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>583784</v>
+        <v>584025</v>
       </c>
       <c r="R78" t="n">
-        <v>7212884</v>
+        <v>7212370</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9243,32 +9243,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128998131</v>
+        <v>128998135</v>
       </c>
       <c r="B79" t="n">
-        <v>57720</v>
+        <v>91893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>584025</v>
+        <v>583778</v>
       </c>
       <c r="R79" t="n">
-        <v>7212370</v>
+        <v>7212890</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
         <v>128998147</v>
       </c>
       <c r="B80" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>129000163</v>
       </c>
       <c r="B81" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>129000141</v>
       </c>
       <c r="B83" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9825,10 +9825,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129000115</v>
+        <v>128998153</v>
       </c>
       <c r="B85" t="n">
-        <v>80168</v>
+        <v>80174</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9836,34 +9836,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>583856</v>
+        <v>583842</v>
       </c>
       <c r="R85" t="n">
-        <v>7212374</v>
+        <v>7212492</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9910,44 +9910,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129000145</v>
+        <v>129000115</v>
       </c>
       <c r="B86" t="n">
-        <v>57723</v>
+        <v>80168</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9957,10 +9957,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>583826</v>
+        <v>583856</v>
       </c>
       <c r="R86" t="n">
-        <v>7211682</v>
+        <v>7212374</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9987,12 +9987,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10019,45 +10019,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128998153</v>
+        <v>129000145</v>
       </c>
       <c r="B87" t="n">
-        <v>80174</v>
+        <v>57723</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>583842</v>
+        <v>583826</v>
       </c>
       <c r="R87" t="n">
-        <v>7212492</v>
+        <v>7211682</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10084,12 +10084,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10104,12 +10104,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10119,7 +10119,7 @@
         <v>128998134</v>
       </c>
       <c r="B88" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10420,10 +10420,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129000165</v>
+        <v>128997040</v>
       </c>
       <c r="B91" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>583888</v>
+        <v>583800</v>
       </c>
       <c r="R91" t="n">
-        <v>7211663</v>
+        <v>7212621</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10485,12 +10485,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10505,57 +10505,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129000116</v>
+        <v>128998130</v>
       </c>
       <c r="B92" t="n">
-        <v>57720</v>
+        <v>80168</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>584099</v>
+        <v>583781</v>
       </c>
       <c r="R92" t="n">
-        <v>7211521</v>
+        <v>7212767</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10582,17 +10582,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Spillkråkehack på låga</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10607,22 +10602,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128997040</v>
+        <v>129000116</v>
       </c>
       <c r="B93" t="n">
-        <v>91516</v>
+        <v>57720</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10630,21 +10625,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10654,10 +10649,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>583800</v>
+        <v>584099</v>
       </c>
       <c r="R93" t="n">
-        <v>7212621</v>
+        <v>7211521</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10684,12 +10679,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Spillkråkehack på låga</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10704,57 +10704,57 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128998130</v>
+        <v>128997035</v>
       </c>
       <c r="B94" t="n">
-        <v>80168</v>
+        <v>57883</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>583781</v>
+        <v>583868</v>
       </c>
       <c r="R94" t="n">
-        <v>7212767</v>
+        <v>7212926</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10801,22 +10801,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128997035</v>
+        <v>129000165</v>
       </c>
       <c r="B95" t="n">
-        <v>57883</v>
+        <v>91519</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10824,21 +10824,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10848,10 +10848,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>583868</v>
+        <v>583888</v>
       </c>
       <c r="R95" t="n">
-        <v>7212926</v>
+        <v>7211663</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10878,12 +10878,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10898,12 +10898,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11007,45 +11007,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129000175</v>
+        <v>128998155</v>
       </c>
       <c r="B97" t="n">
-        <v>91538</v>
+        <v>80174</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>583975</v>
+        <v>583778</v>
       </c>
       <c r="R97" t="n">
-        <v>7211530</v>
+        <v>7212766</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11072,12 +11072,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11092,22 +11092,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128998146</v>
+        <v>129000175</v>
       </c>
       <c r="B98" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11135,14 +11135,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>583700</v>
+        <v>583975</v>
       </c>
       <c r="R98" t="n">
-        <v>7212870</v>
+        <v>7211530</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11169,12 +11169,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11189,44 +11189,44 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128998155</v>
+        <v>128998146</v>
       </c>
       <c r="B99" t="n">
-        <v>80174</v>
+        <v>91541</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11236,10 +11236,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>583778</v>
+        <v>583700</v>
       </c>
       <c r="R99" t="n">
-        <v>7212766</v>
+        <v>7212870</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11298,45 +11298,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129000150</v>
+        <v>128998136</v>
       </c>
       <c r="B100" t="n">
-        <v>91890</v>
+        <v>80175</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1506</v>
+        <v>6464</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>583951</v>
+        <v>583838</v>
       </c>
       <c r="R100" t="n">
-        <v>7211500</v>
+        <v>7212502</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11363,12 +11363,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11383,57 +11383,57 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129000107</v>
+        <v>128998132</v>
       </c>
       <c r="B101" t="n">
-        <v>92218</v>
+        <v>57720</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>583938</v>
+        <v>583834</v>
       </c>
       <c r="R101" t="n">
-        <v>7211643</v>
+        <v>7212585</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11480,57 +11480,57 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128998132</v>
+        <v>129000150</v>
       </c>
       <c r="B102" t="n">
-        <v>57720</v>
+        <v>91893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>583834</v>
+        <v>583951</v>
       </c>
       <c r="R102" t="n">
-        <v>7212585</v>
+        <v>7211500</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11557,12 +11557,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11577,22 +11577,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128998136</v>
+        <v>129000107</v>
       </c>
       <c r="B103" t="n">
-        <v>80175</v>
+        <v>92223</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11600,34 +11600,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>583838</v>
+        <v>583938</v>
       </c>
       <c r="R103" t="n">
-        <v>7212502</v>
+        <v>7211643</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11654,12 +11654,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11674,12 +11674,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11796,10 +11796,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129000126</v>
+        <v>128997039</v>
       </c>
       <c r="B105" t="n">
-        <v>83015</v>
+        <v>91519</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11807,21 +11807,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11831,10 +11831,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>583693</v>
+        <v>583807</v>
       </c>
       <c r="R105" t="n">
-        <v>7211591</v>
+        <v>7212750</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11861,12 +11861,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11881,22 +11881,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129000130</v>
+        <v>129000126</v>
       </c>
       <c r="B106" t="n">
-        <v>57723</v>
+        <v>83015</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11904,21 +11904,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11928,10 +11928,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>584350</v>
+        <v>583693</v>
       </c>
       <c r="R106" t="n">
-        <v>7211690</v>
+        <v>7211591</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11964,11 +11964,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11995,32 +11990,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129000147</v>
+        <v>129000130</v>
       </c>
       <c r="B107" t="n">
-        <v>97528</v>
+        <v>57723</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12030,10 +12025,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>584141</v>
+        <v>584350</v>
       </c>
       <c r="R107" t="n">
-        <v>7211590</v>
+        <v>7211690</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12066,6 +12061,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12092,32 +12092,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128997039</v>
+        <v>129000147</v>
       </c>
       <c r="B108" t="n">
-        <v>91516</v>
+        <v>97533</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1108</v>
+        <v>221941</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12127,10 +12127,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>583807</v>
+        <v>584141</v>
       </c>
       <c r="R108" t="n">
-        <v>7212750</v>
+        <v>7211590</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12157,12 +12157,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12177,12 +12177,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -12192,7 +12192,7 @@
         <v>129000187</v>
       </c>
       <c r="B109" t="n">
-        <v>88920</v>
+        <v>88923</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12286,45 +12286,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129000146</v>
+        <v>128998126</v>
       </c>
       <c r="B110" t="n">
-        <v>57723</v>
+        <v>92223</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>583819</v>
+        <v>583748</v>
       </c>
       <c r="R110" t="n">
-        <v>7211689</v>
+        <v>7212869</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12351,17 +12351,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12376,57 +12371,57 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129000157</v>
+        <v>128998149</v>
       </c>
       <c r="B111" t="n">
-        <v>57827</v>
+        <v>79034</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>583712</v>
+        <v>584059</v>
       </c>
       <c r="R111" t="n">
-        <v>7211576</v>
+        <v>7212428</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12453,12 +12448,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12473,57 +12468,57 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128998126</v>
+        <v>129000146</v>
       </c>
       <c r="B112" t="n">
-        <v>92218</v>
+        <v>57723</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>583748</v>
+        <v>583819</v>
       </c>
       <c r="R112" t="n">
-        <v>7212869</v>
+        <v>7211689</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12550,12 +12545,17 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12570,57 +12570,57 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128998149</v>
+        <v>129000157</v>
       </c>
       <c r="B113" t="n">
-        <v>79034</v>
+        <v>57827</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>584059</v>
+        <v>583712</v>
       </c>
       <c r="R113" t="n">
-        <v>7212428</v>
+        <v>7211576</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12647,12 +12647,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12667,57 +12667,57 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128998138</v>
+        <v>129000173</v>
       </c>
       <c r="B114" t="n">
-        <v>80175</v>
+        <v>91541</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>583742</v>
+        <v>583879</v>
       </c>
       <c r="R114" t="n">
-        <v>7213116</v>
+        <v>7211699</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12744,12 +12744,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12764,57 +12764,57 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129000173</v>
+        <v>128998138</v>
       </c>
       <c r="B115" t="n">
-        <v>91538</v>
+        <v>80175</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>583879</v>
+        <v>583742</v>
       </c>
       <c r="R115" t="n">
-        <v>7211699</v>
+        <v>7213116</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12841,12 +12841,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12861,22 +12861,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129000135</v>
+        <v>129000182</v>
       </c>
       <c r="B116" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12884,21 +12884,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12908,10 +12908,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>584139</v>
+        <v>584124</v>
       </c>
       <c r="R116" t="n">
-        <v>7211559</v>
+        <v>7211556</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12944,11 +12944,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12975,32 +12970,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129000119</v>
+        <v>129000097</v>
       </c>
       <c r="B117" t="n">
-        <v>83008</v>
+        <v>83010</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6486</v>
+        <v>6440</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13010,10 +13005,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>583763</v>
+        <v>584170</v>
       </c>
       <c r="R117" t="n">
-        <v>7211568</v>
+        <v>7211600</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13072,32 +13067,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129000182</v>
+        <v>129000119</v>
       </c>
       <c r="B118" t="n">
-        <v>79034</v>
+        <v>83008</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13107,10 +13102,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>584124</v>
+        <v>583763</v>
       </c>
       <c r="R118" t="n">
-        <v>7211556</v>
+        <v>7211568</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13169,10 +13164,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129000097</v>
+        <v>129000135</v>
       </c>
       <c r="B119" t="n">
-        <v>83010</v>
+        <v>57723</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13180,21 +13175,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13204,10 +13199,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>584170</v>
+        <v>584139</v>
       </c>
       <c r="R119" t="n">
-        <v>7211600</v>
+        <v>7211559</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13240,6 +13235,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13266,10 +13266,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129000169</v>
+        <v>128998129</v>
       </c>
       <c r="B120" t="n">
-        <v>82993</v>
+        <v>80168</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13277,34 +13277,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6439</v>
+        <v>6462</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>583695</v>
+        <v>583743</v>
       </c>
       <c r="R120" t="n">
-        <v>7211591</v>
+        <v>7212862</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13331,12 +13331,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13351,57 +13351,57 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129000144</v>
+        <v>128998154</v>
       </c>
       <c r="B121" t="n">
-        <v>57723</v>
+        <v>80174</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>583832</v>
+        <v>583743</v>
       </c>
       <c r="R121" t="n">
-        <v>7211693</v>
+        <v>7212862</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13428,17 +13428,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13453,12 +13448,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -13468,7 +13463,7 @@
         <v>128998148</v>
       </c>
       <c r="B122" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13659,45 +13654,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128998129</v>
+        <v>129000144</v>
       </c>
       <c r="B124" t="n">
-        <v>80168</v>
+        <v>57723</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>583743</v>
+        <v>583832</v>
       </c>
       <c r="R124" t="n">
-        <v>7212862</v>
+        <v>7211693</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13724,12 +13719,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13744,22 +13744,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128998154</v>
+        <v>129000169</v>
       </c>
       <c r="B125" t="n">
-        <v>80174</v>
+        <v>82993</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13767,34 +13767,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6463</v>
+        <v>6439</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>583743</v>
+        <v>583695</v>
       </c>
       <c r="R125" t="n">
-        <v>7212862</v>
+        <v>7211591</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13821,12 +13821,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13841,12 +13841,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -14055,7 +14055,7 @@
         <v>128998141</v>
       </c>
       <c r="B128" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14149,10 +14149,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129000184</v>
+        <v>129000166</v>
       </c>
       <c r="B129" t="n">
-        <v>79034</v>
+        <v>91519</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14160,21 +14160,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14184,10 +14184,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>584333</v>
+        <v>583796</v>
       </c>
       <c r="R129" t="n">
-        <v>7211688</v>
+        <v>7211546</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14246,10 +14246,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129000166</v>
+        <v>129000168</v>
       </c>
       <c r="B130" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>583796</v>
+        <v>584331</v>
       </c>
       <c r="R130" t="n">
-        <v>7211546</v>
+        <v>7211693</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14343,45 +14343,48 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129000168</v>
+        <v>129000185</v>
       </c>
       <c r="B131" t="n">
-        <v>91516</v>
+        <v>92852</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1108</v>
+        <v>5964</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>584331</v>
+        <v>584074</v>
       </c>
       <c r="R131" t="n">
-        <v>7211693</v>
+        <v>7211675</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14422,6 +14425,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14440,48 +14444,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129000185</v>
+        <v>129000184</v>
       </c>
       <c r="B132" t="n">
-        <v>92847</v>
+        <v>79034</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>584074</v>
+        <v>584333</v>
       </c>
       <c r="R132" t="n">
-        <v>7211675</v>
+        <v>7211688</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14522,7 +14523,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14541,10 +14541,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129000174</v>
+        <v>129000167</v>
       </c>
       <c r="B133" t="n">
-        <v>91538</v>
+        <v>91519</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14552,21 +14552,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14576,10 +14576,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>583934</v>
+        <v>584144</v>
       </c>
       <c r="R133" t="n">
-        <v>7211520</v>
+        <v>7211566</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14638,10 +14638,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129000138</v>
+        <v>129000174</v>
       </c>
       <c r="B134" t="n">
-        <v>57723</v>
+        <v>91541</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14649,21 +14649,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14673,10 +14673,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>583805</v>
+        <v>583934</v>
       </c>
       <c r="R134" t="n">
-        <v>7211693</v>
+        <v>7211520</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14709,11 +14709,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14740,10 +14735,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129000167</v>
+        <v>129000138</v>
       </c>
       <c r="B135" t="n">
-        <v>91516</v>
+        <v>57723</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14751,21 +14746,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14775,10 +14770,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>584144</v>
+        <v>583805</v>
       </c>
       <c r="R135" t="n">
-        <v>7211566</v>
+        <v>7211693</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14811,6 +14806,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14840,7 +14840,7 @@
         <v>129012557</v>
       </c>
       <c r="B136" t="n">
-        <v>88920</v>
+        <v>88923</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>129012558</v>
       </c>
       <c r="B137" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>129012556</v>
       </c>
       <c r="B138" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>129000128</v>
       </c>
       <c r="B139" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15631,10 +15631,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129000137</v>
+        <v>129085077</v>
       </c>
       <c r="B144" t="n">
-        <v>57723</v>
+        <v>91523</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15642,37 +15642,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>583784</v>
+        <v>583874</v>
       </c>
       <c r="R144" t="n">
-        <v>7212338</v>
+        <v>7212775</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15702,11 +15702,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15721,22 +15716,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129085077</v>
+        <v>129085080</v>
       </c>
       <c r="B145" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15768,10 +15763,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>583874</v>
+        <v>583726</v>
       </c>
       <c r="R145" t="n">
-        <v>7212775</v>
+        <v>7212315</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15830,10 +15825,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129085080</v>
+        <v>129000137</v>
       </c>
       <c r="B146" t="n">
-        <v>91520</v>
+        <v>57723</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15841,37 +15836,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>583726</v>
+        <v>583784</v>
       </c>
       <c r="R146" t="n">
-        <v>7212315</v>
+        <v>7212338</v>
       </c>
       <c r="S146" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15901,6 +15896,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15915,44 +15915,44 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129000159</v>
+        <v>129000106</v>
       </c>
       <c r="B147" t="n">
-        <v>56904</v>
+        <v>92223</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>102612</v>
+        <v>3298</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15962,10 +15962,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>583817</v>
+        <v>583634</v>
       </c>
       <c r="R147" t="n">
-        <v>7212328</v>
+        <v>7212397</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16024,32 +16024,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129000106</v>
+        <v>129000171</v>
       </c>
       <c r="B148" t="n">
-        <v>92218</v>
+        <v>91541</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16059,10 +16059,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>583634</v>
+        <v>583882</v>
       </c>
       <c r="R148" t="n">
-        <v>7212397</v>
+        <v>7212369</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16121,10 +16121,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129000171</v>
+        <v>129085094</v>
       </c>
       <c r="B149" t="n">
-        <v>91538</v>
+        <v>91519</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16132,37 +16132,37 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>583882</v>
+        <v>583526</v>
       </c>
       <c r="R149" t="n">
-        <v>7212369</v>
+        <v>7212468</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16206,22 +16206,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129085094</v>
+        <v>129000159</v>
       </c>
       <c r="B150" t="n">
-        <v>91516</v>
+        <v>56904</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16229,37 +16229,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>583526</v>
+        <v>583817</v>
       </c>
       <c r="R150" t="n">
-        <v>7212468</v>
+        <v>7212328</v>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16303,12 +16303,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -16415,7 +16415,7 @@
         <v>129085088</v>
       </c>
       <c r="B152" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16509,32 +16509,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129000189</v>
+        <v>129000103</v>
       </c>
       <c r="B153" t="n">
-        <v>80174</v>
+        <v>91523</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16544,10 +16544,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>583856</v>
+        <v>583841</v>
       </c>
       <c r="R153" t="n">
-        <v>7212375</v>
+        <v>7212355</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16606,10 +16606,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129000149</v>
+        <v>129000189</v>
       </c>
       <c r="B154" t="n">
-        <v>97528</v>
+        <v>80174</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16617,21 +16617,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16641,10 +16641,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>583660</v>
+        <v>583856</v>
       </c>
       <c r="R154" t="n">
-        <v>7212365</v>
+        <v>7212375</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16703,10 +16703,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129085076</v>
+        <v>129000149</v>
       </c>
       <c r="B155" t="n">
-        <v>91485</v>
+        <v>97533</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16714,37 +16714,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>583540</v>
+        <v>583660</v>
       </c>
       <c r="R155" t="n">
-        <v>7212450</v>
+        <v>7212365</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16788,60 +16788,60 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129000103</v>
+        <v>129085076</v>
       </c>
       <c r="B156" t="n">
-        <v>91520</v>
+        <v>91488</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>583841</v>
+        <v>583540</v>
       </c>
       <c r="R156" t="n">
-        <v>7212355</v>
+        <v>7212450</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16885,60 +16885,60 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129000188</v>
+        <v>129085096</v>
       </c>
       <c r="B157" t="n">
-        <v>80174</v>
+        <v>91541</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>583606</v>
+        <v>583522</v>
       </c>
       <c r="R157" t="n">
-        <v>7212484</v>
+        <v>7212551</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16982,12 +16982,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -17091,48 +17091,48 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129085096</v>
+        <v>129000188</v>
       </c>
       <c r="B159" t="n">
-        <v>91538</v>
+        <v>80174</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>583522</v>
+        <v>583606</v>
       </c>
       <c r="R159" t="n">
-        <v>7212551</v>
+        <v>7212484</v>
       </c>
       <c r="S159" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17176,12 +17176,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -17385,7 +17385,7 @@
         <v>129000100</v>
       </c>
       <c r="B162" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>129073200</v>
       </c>
       <c r="B163" t="n">
-        <v>91695</v>
+        <v>91698</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17576,10 +17576,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129000153</v>
+        <v>129000177</v>
       </c>
       <c r="B164" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17587,37 +17587,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>583768</v>
+        <v>583609</v>
       </c>
       <c r="R164" t="n">
-        <v>7212826</v>
+        <v>7212495</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17658,24 +17655,8 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
@@ -17692,10 +17673,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129000177</v>
+        <v>129000153</v>
       </c>
       <c r="B165" t="n">
-        <v>79034</v>
+        <v>80139</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17703,34 +17684,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>583609</v>
+        <v>583768</v>
       </c>
       <c r="R165" t="n">
-        <v>7212495</v>
+        <v>7212826</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17771,8 +17755,24 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
@@ -17789,10 +17789,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129085074</v>
+        <v>129000114</v>
       </c>
       <c r="B166" t="n">
-        <v>105699</v>
+        <v>80168</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17800,37 +17800,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>583517</v>
+        <v>583606</v>
       </c>
       <c r="R166" t="n">
-        <v>7212494</v>
+        <v>7212483</v>
       </c>
       <c r="S166" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17874,22 +17874,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129085075</v>
+        <v>129085074</v>
       </c>
       <c r="B167" t="n">
-        <v>105699</v>
+        <v>105704</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17921,10 +17921,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>583896</v>
+        <v>583517</v>
       </c>
       <c r="R167" t="n">
-        <v>7212322</v>
+        <v>7212494</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -17983,10 +17983,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129000114</v>
+        <v>129085075</v>
       </c>
       <c r="B168" t="n">
-        <v>80168</v>
+        <v>105704</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17994,37 +17994,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>583606</v>
+        <v>583896</v>
       </c>
       <c r="R168" t="n">
-        <v>7212483</v>
+        <v>7212322</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18068,22 +18068,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129000104</v>
+        <v>129085078</v>
       </c>
       <c r="B169" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18111,17 +18111,17 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>584023</v>
+        <v>583677</v>
       </c>
       <c r="R169" t="n">
-        <v>7212353</v>
+        <v>7212815</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18165,22 +18165,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129085078</v>
+        <v>129000104</v>
       </c>
       <c r="B170" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18208,17 +18208,17 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>583677</v>
+        <v>584023</v>
       </c>
       <c r="R170" t="n">
-        <v>7212815</v>
+        <v>7212353</v>
       </c>
       <c r="S170" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18262,22 +18262,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129000122</v>
+        <v>129000170</v>
       </c>
       <c r="B171" t="n">
-        <v>80140</v>
+        <v>91537</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18285,21 +18285,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>583833</v>
+        <v>583844</v>
       </c>
       <c r="R171" t="n">
-        <v>7212856</v>
+        <v>7212348</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18371,10 +18371,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129000170</v>
+        <v>129000122</v>
       </c>
       <c r="B172" t="n">
-        <v>91534</v>
+        <v>80140</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18382,21 +18382,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18406,10 +18406,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>583844</v>
+        <v>583833</v>
       </c>
       <c r="R172" t="n">
-        <v>7212348</v>
+        <v>7212856</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18762,7 +18762,7 @@
         <v>129000172</v>
       </c>
       <c r="B176" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>129085079</v>
       </c>
       <c r="B179" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19147,48 +19147,48 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129085095</v>
+        <v>129073201</v>
       </c>
       <c r="B180" t="n">
-        <v>91538</v>
+        <v>92313</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5432</v>
+        <v>918</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>583378</v>
+        <v>583599</v>
       </c>
       <c r="R180" t="n">
-        <v>7212728</v>
+        <v>7212710</v>
       </c>
       <c r="S180" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19232,12 +19232,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
@@ -19247,7 +19247,7 @@
         <v>129073202</v>
       </c>
       <c r="B181" t="n">
-        <v>95501</v>
+        <v>95506</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19341,32 +19341,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129073201</v>
+        <v>129000101</v>
       </c>
       <c r="B182" t="n">
-        <v>92308</v>
+        <v>91523</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>918</v>
+        <v>1202</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19376,10 +19376,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>583599</v>
+        <v>583663</v>
       </c>
       <c r="R182" t="n">
-        <v>7212710</v>
+        <v>7212429</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19431,17 +19431,17 @@
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129000101</v>
+        <v>129000129</v>
       </c>
       <c r="B183" t="n">
-        <v>91520</v>
+        <v>91808</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19449,21 +19449,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19473,10 +19473,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>583663</v>
+        <v>583810</v>
       </c>
       <c r="R183" t="n">
-        <v>7212429</v>
+        <v>7212852</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19535,10 +19535,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129000129</v>
+        <v>129085095</v>
       </c>
       <c r="B184" t="n">
-        <v>91805</v>
+        <v>91541</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19546,37 +19546,37 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>583810</v>
+        <v>583378</v>
       </c>
       <c r="R184" t="n">
-        <v>7212852</v>
+        <v>7212728</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19620,12 +19620,12 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
@@ -19729,10 +19729,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129000160</v>
+        <v>129000132</v>
       </c>
       <c r="B186" t="n">
-        <v>91516</v>
+        <v>57723</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19740,21 +19740,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19764,10 +19764,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>583674</v>
+        <v>583968</v>
       </c>
       <c r="R186" t="n">
-        <v>7212755</v>
+        <v>7212362</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19800,6 +19800,11 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19826,27 +19831,27 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129085086</v>
+        <v>129085092</v>
       </c>
       <c r="B187" t="n">
-        <v>57723</v>
+        <v>58093</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -19855,20 +19860,16 @@
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>583569</v>
+        <v>584017</v>
       </c>
       <c r="R187" t="n">
-        <v>7212757</v>
+        <v>7212353</v>
       </c>
       <c r="S187" t="n">
         <v>15</v>
@@ -19903,11 +19904,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD187" t="b">
         <v>0</v>
       </c>
@@ -19925,17 +19921,17 @@
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129000132</v>
+        <v>129000160</v>
       </c>
       <c r="B188" t="n">
-        <v>57723</v>
+        <v>91519</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19943,21 +19939,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19967,10 +19963,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>583968</v>
+        <v>583674</v>
       </c>
       <c r="R188" t="n">
-        <v>7212362</v>
+        <v>7212755</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20003,11 +19999,6 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20131,27 +20122,27 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129085092</v>
+        <v>129085086</v>
       </c>
       <c r="B190" t="n">
-        <v>58093</v>
+        <v>57723</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -20160,16 +20151,20 @@
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>584017</v>
+        <v>583569</v>
       </c>
       <c r="R190" t="n">
-        <v>7212353</v>
+        <v>7212757</v>
       </c>
       <c r="S190" t="n">
         <v>15</v>
@@ -20204,6 +20199,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD190" t="b">
         <v>0</v>
       </c>
@@ -20221,39 +20221,39 @@
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129000154</v>
+        <v>129000162</v>
       </c>
       <c r="B191" t="n">
-        <v>80175</v>
+        <v>91519</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20263,10 +20263,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>583832</v>
+        <v>583583</v>
       </c>
       <c r="R191" t="n">
-        <v>7212853</v>
+        <v>7212676</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20325,32 +20325,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129000162</v>
+        <v>129000154</v>
       </c>
       <c r="B192" t="n">
-        <v>91516</v>
+        <v>80175</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20360,10 +20360,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>583583</v>
+        <v>583832</v>
       </c>
       <c r="R192" t="n">
-        <v>7212676</v>
+        <v>7212853</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>

--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -8171,10 +8171,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129000140</v>
+        <v>128998140</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>91522</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8182,34 +8182,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>584092</v>
+        <v>583855</v>
       </c>
       <c r="R68" t="n">
-        <v>7211517</v>
+        <v>7213081</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8236,17 +8236,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8261,12 +8256,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8276,7 +8271,7 @@
         <v>128998144</v>
       </c>
       <c r="B69" t="n">
-        <v>82993</v>
+        <v>82994</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8370,10 +8365,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128998140</v>
+        <v>129000140</v>
       </c>
       <c r="B70" t="n">
-        <v>91519</v>
+        <v>57723</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8381,34 +8376,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583855</v>
+        <v>584092</v>
       </c>
       <c r="R70" t="n">
-        <v>7213081</v>
+        <v>7211517</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8435,12 +8430,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8455,57 +8455,57 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129000183</v>
+        <v>128998122</v>
       </c>
       <c r="B71" t="n">
-        <v>79034</v>
+        <v>105707</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>584220</v>
+        <v>583934</v>
       </c>
       <c r="R71" t="n">
-        <v>7211664</v>
+        <v>7212490</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8532,12 +8532,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8552,57 +8552,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128998142</v>
+        <v>128997038</v>
       </c>
       <c r="B72" t="n">
-        <v>91519</v>
+        <v>97536</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1108</v>
+        <v>221941</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583800</v>
+        <v>583850</v>
       </c>
       <c r="R72" t="n">
-        <v>7212769</v>
+        <v>7212515</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8649,57 +8649,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128997038</v>
+        <v>128998142</v>
       </c>
       <c r="B73" t="n">
-        <v>97533</v>
+        <v>91522</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221941</v>
+        <v>1108</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583850</v>
+        <v>583800</v>
       </c>
       <c r="R73" t="n">
-        <v>7212515</v>
+        <v>7212769</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8746,57 +8746,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128998122</v>
+        <v>129000183</v>
       </c>
       <c r="B74" t="n">
-        <v>105704</v>
+        <v>79035</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583934</v>
+        <v>584220</v>
       </c>
       <c r="R74" t="n">
-        <v>7212490</v>
+        <v>7211664</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8843,12 +8843,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8955,7 +8955,7 @@
         <v>129000152</v>
       </c>
       <c r="B76" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9049,10 +9049,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128998124</v>
+        <v>128998131</v>
       </c>
       <c r="B77" t="n">
-        <v>91523</v>
+        <v>57720</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9060,21 +9060,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583784</v>
+        <v>584025</v>
       </c>
       <c r="R77" t="n">
-        <v>7212884</v>
+        <v>7212370</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9146,32 +9146,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128998131</v>
+        <v>128998135</v>
       </c>
       <c r="B78" t="n">
-        <v>57720</v>
+        <v>91896</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>584025</v>
+        <v>583778</v>
       </c>
       <c r="R78" t="n">
-        <v>7212370</v>
+        <v>7212890</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9243,32 +9243,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128998135</v>
+        <v>128998124</v>
       </c>
       <c r="B79" t="n">
-        <v>91893</v>
+        <v>91526</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583778</v>
+        <v>583784</v>
       </c>
       <c r="R79" t="n">
-        <v>7212890</v>
+        <v>7212884</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
         <v>128998147</v>
       </c>
       <c r="B80" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9437,10 +9437,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129000163</v>
+        <v>129000181</v>
       </c>
       <c r="B81" t="n">
-        <v>91519</v>
+        <v>79035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9448,21 +9448,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9472,10 +9472,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>584005</v>
+        <v>583824</v>
       </c>
       <c r="R81" t="n">
-        <v>7211652</v>
+        <v>7211526</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9534,10 +9534,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129000181</v>
+        <v>129000163</v>
       </c>
       <c r="B82" t="n">
-        <v>79034</v>
+        <v>91522</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9545,21 +9545,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9569,10 +9569,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>583824</v>
+        <v>584005</v>
       </c>
       <c r="R82" t="n">
-        <v>7211526</v>
+        <v>7211652</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9634,7 +9634,7 @@
         <v>129000141</v>
       </c>
       <c r="B83" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9728,32 +9728,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128998133</v>
+        <v>128998153</v>
       </c>
       <c r="B84" t="n">
-        <v>80140</v>
+        <v>80175</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9763,10 +9763,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>583743</v>
+        <v>583842</v>
       </c>
       <c r="R84" t="n">
-        <v>7212862</v>
+        <v>7212492</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9825,32 +9825,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128998153</v>
+        <v>128998133</v>
       </c>
       <c r="B85" t="n">
-        <v>80174</v>
+        <v>80141</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>583842</v>
+        <v>583743</v>
       </c>
       <c r="R85" t="n">
-        <v>7212492</v>
+        <v>7212862</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9925,7 +9925,7 @@
         <v>129000115</v>
       </c>
       <c r="B86" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>128998134</v>
       </c>
       <c r="B88" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128998127</v>
+        <v>128998152</v>
       </c>
       <c r="B89" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10224,42 +10224,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>583792</v>
+        <v>583744</v>
       </c>
       <c r="R89" t="n">
-        <v>7212761</v>
+        <v>7212703</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10292,11 +10284,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färskt bohål som sannolikt är från tretåig hackspett pga storleken på bohålet (ca 5 cm)</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10323,10 +10310,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128998152</v>
+        <v>128998127</v>
       </c>
       <c r="B90" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10334,34 +10321,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>583744</v>
+        <v>583792</v>
       </c>
       <c r="R90" t="n">
-        <v>7212703</v>
+        <v>7212761</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10394,6 +10389,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färskt bohål som sannolikt är från tretåig hackspett pga storleken på bohålet (ca 5 cm)</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10420,10 +10420,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128997040</v>
+        <v>128997035</v>
       </c>
       <c r="B91" t="n">
-        <v>91519</v>
+        <v>57883</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10431,21 +10431,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>583800</v>
+        <v>583868</v>
       </c>
       <c r="R91" t="n">
-        <v>7212621</v>
+        <v>7212926</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10517,45 +10517,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128998130</v>
+        <v>129000116</v>
       </c>
       <c r="B92" t="n">
-        <v>80168</v>
+        <v>57720</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>583781</v>
+        <v>584099</v>
       </c>
       <c r="R92" t="n">
-        <v>7212767</v>
+        <v>7211521</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10582,12 +10582,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Spillkråkehack på låga</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10602,22 +10607,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129000116</v>
+        <v>128997040</v>
       </c>
       <c r="B93" t="n">
-        <v>57720</v>
+        <v>91522</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10625,21 +10630,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10649,10 +10654,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>584099</v>
+        <v>583800</v>
       </c>
       <c r="R93" t="n">
-        <v>7211521</v>
+        <v>7212621</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10679,17 +10684,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Spillkråkehack på låga</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10704,57 +10704,57 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128997035</v>
+        <v>128998130</v>
       </c>
       <c r="B94" t="n">
-        <v>57883</v>
+        <v>80169</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>583868</v>
+        <v>583781</v>
       </c>
       <c r="R94" t="n">
-        <v>7212926</v>
+        <v>7212767</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10801,12 +10801,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10816,7 +10816,7 @@
         <v>129000165</v>
       </c>
       <c r="B95" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10910,10 +10910,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128998150</v>
+        <v>129000175</v>
       </c>
       <c r="B96" t="n">
-        <v>79034</v>
+        <v>91544</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10921,34 +10921,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>583862</v>
+        <v>583975</v>
       </c>
       <c r="R96" t="n">
-        <v>7212466</v>
+        <v>7211530</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10975,12 +10975,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10995,44 +10995,44 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128998155</v>
+        <v>128998146</v>
       </c>
       <c r="B97" t="n">
-        <v>80174</v>
+        <v>91544</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11042,10 +11042,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>583778</v>
+        <v>583700</v>
       </c>
       <c r="R97" t="n">
-        <v>7212766</v>
+        <v>7212870</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11104,10 +11104,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129000175</v>
+        <v>128998150</v>
       </c>
       <c r="B98" t="n">
-        <v>91541</v>
+        <v>79035</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11115,34 +11115,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>583975</v>
+        <v>583862</v>
       </c>
       <c r="R98" t="n">
-        <v>7211530</v>
+        <v>7212466</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11169,12 +11169,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11189,44 +11189,44 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128998146</v>
+        <v>128998155</v>
       </c>
       <c r="B99" t="n">
-        <v>91541</v>
+        <v>80175</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11236,10 +11236,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>583700</v>
+        <v>583778</v>
       </c>
       <c r="R99" t="n">
-        <v>7212870</v>
+        <v>7212766</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11298,45 +11298,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128998136</v>
+        <v>129000150</v>
       </c>
       <c r="B100" t="n">
-        <v>80175</v>
+        <v>91896</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6464</v>
+        <v>1506</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>583838</v>
+        <v>583951</v>
       </c>
       <c r="R100" t="n">
-        <v>7212502</v>
+        <v>7211500</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11363,12 +11363,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11383,12 +11383,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11492,45 +11492,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129000150</v>
+        <v>128998136</v>
       </c>
       <c r="B102" t="n">
-        <v>91893</v>
+        <v>80176</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1506</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>583951</v>
+        <v>583838</v>
       </c>
       <c r="R102" t="n">
-        <v>7211500</v>
+        <v>7212502</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11557,12 +11557,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11577,12 +11577,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11592,7 +11592,7 @@
         <v>129000107</v>
       </c>
       <c r="B103" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11796,10 +11796,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128997039</v>
+        <v>129000126</v>
       </c>
       <c r="B105" t="n">
-        <v>91519</v>
+        <v>83016</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11807,21 +11807,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11831,10 +11831,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>583807</v>
+        <v>583693</v>
       </c>
       <c r="R105" t="n">
-        <v>7212750</v>
+        <v>7211591</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11861,12 +11861,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11881,22 +11881,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129000126</v>
+        <v>129000130</v>
       </c>
       <c r="B106" t="n">
-        <v>83015</v>
+        <v>57723</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11904,21 +11904,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11928,10 +11928,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>583693</v>
+        <v>584350</v>
       </c>
       <c r="R106" t="n">
-        <v>7211591</v>
+        <v>7211690</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11964,6 +11964,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11990,10 +11995,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129000130</v>
+        <v>128997039</v>
       </c>
       <c r="B107" t="n">
-        <v>57723</v>
+        <v>91522</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12001,21 +12006,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12025,10 +12030,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>584350</v>
+        <v>583807</v>
       </c>
       <c r="R107" t="n">
-        <v>7211690</v>
+        <v>7212750</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12055,17 +12060,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Äldre och färska ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12080,12 +12080,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12095,7 +12095,7 @@
         <v>129000147</v>
       </c>
       <c r="B108" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12189,10 +12189,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129000187</v>
+        <v>128998149</v>
       </c>
       <c r="B109" t="n">
-        <v>88923</v>
+        <v>79035</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12200,34 +12200,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>583966</v>
+        <v>584059</v>
       </c>
       <c r="R109" t="n">
-        <v>7211510</v>
+        <v>7212428</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12254,12 +12254,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12274,57 +12274,57 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128998126</v>
+        <v>129000187</v>
       </c>
       <c r="B110" t="n">
-        <v>92223</v>
+        <v>88926</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3298</v>
+        <v>510</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>583748</v>
+        <v>583966</v>
       </c>
       <c r="R110" t="n">
-        <v>7212869</v>
+        <v>7211510</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12351,12 +12351,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12371,22 +12371,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128998149</v>
+        <v>129000146</v>
       </c>
       <c r="B111" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12394,34 +12394,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>584059</v>
+        <v>583819</v>
       </c>
       <c r="R111" t="n">
-        <v>7212428</v>
+        <v>7211689</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12448,12 +12448,17 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12468,57 +12473,57 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129000146</v>
+        <v>128998126</v>
       </c>
       <c r="B112" t="n">
-        <v>57723</v>
+        <v>92226</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>583819</v>
+        <v>583748</v>
       </c>
       <c r="R112" t="n">
-        <v>7211689</v>
+        <v>7212869</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12545,17 +12550,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12570,12 +12570,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -12682,7 +12682,7 @@
         <v>129000173</v>
       </c>
       <c r="B114" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>128998138</v>
       </c>
       <c r="B115" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12873,10 +12873,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129000182</v>
+        <v>129000135</v>
       </c>
       <c r="B116" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12884,21 +12884,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12908,10 +12908,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>584124</v>
+        <v>584139</v>
       </c>
       <c r="R116" t="n">
-        <v>7211556</v>
+        <v>7211559</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12944,6 +12944,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12973,7 +12978,7 @@
         <v>129000097</v>
       </c>
       <c r="B117" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13067,32 +13072,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129000119</v>
+        <v>129000182</v>
       </c>
       <c r="B118" t="n">
-        <v>83008</v>
+        <v>79035</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13102,10 +13107,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>583763</v>
+        <v>584124</v>
       </c>
       <c r="R118" t="n">
-        <v>7211568</v>
+        <v>7211556</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13164,32 +13169,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129000135</v>
+        <v>129000119</v>
       </c>
       <c r="B119" t="n">
-        <v>57723</v>
+        <v>83009</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13199,10 +13204,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>584139</v>
+        <v>583763</v>
       </c>
       <c r="R119" t="n">
-        <v>7211559</v>
+        <v>7211568</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13235,11 +13240,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13266,32 +13266,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128998129</v>
+        <v>128998148</v>
       </c>
       <c r="B120" t="n">
-        <v>80168</v>
+        <v>91544</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13301,10 +13301,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>583743</v>
+        <v>583764</v>
       </c>
       <c r="R120" t="n">
-        <v>7212862</v>
+        <v>7212875</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13363,27 +13363,27 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128998154</v>
+        <v>128998151</v>
       </c>
       <c r="B121" t="n">
-        <v>80174</v>
+        <v>79035</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -13398,10 +13398,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>583743</v>
+        <v>583830</v>
       </c>
       <c r="R121" t="n">
-        <v>7212862</v>
+        <v>7212605</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13460,32 +13460,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128998148</v>
+        <v>128998129</v>
       </c>
       <c r="B122" t="n">
-        <v>91541</v>
+        <v>80169</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13495,10 +13495,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>583764</v>
+        <v>583743</v>
       </c>
       <c r="R122" t="n">
-        <v>7212875</v>
+        <v>7212862</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13557,27 +13557,27 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128998151</v>
+        <v>128998154</v>
       </c>
       <c r="B123" t="n">
-        <v>79034</v>
+        <v>80175</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13592,10 +13592,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>583830</v>
+        <v>583743</v>
       </c>
       <c r="R123" t="n">
-        <v>7212605</v>
+        <v>7212862</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13759,7 +13759,7 @@
         <v>129000169</v>
       </c>
       <c r="B125" t="n">
-        <v>82993</v>
+        <v>82994</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13853,10 +13853,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129000180</v>
+        <v>128998141</v>
       </c>
       <c r="B126" t="n">
-        <v>79034</v>
+        <v>91522</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13864,34 +13864,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>583695</v>
+        <v>583789</v>
       </c>
       <c r="R126" t="n">
-        <v>7211621</v>
+        <v>7213129</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13918,12 +13918,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13938,12 +13938,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -14052,10 +14052,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128998141</v>
+        <v>129000180</v>
       </c>
       <c r="B128" t="n">
-        <v>91519</v>
+        <v>79035</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14063,34 +14063,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>583789</v>
+        <v>583695</v>
       </c>
       <c r="R128" t="n">
-        <v>7213129</v>
+        <v>7211621</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14117,12 +14117,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14137,22 +14137,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129000166</v>
+        <v>129000168</v>
       </c>
       <c r="B129" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14184,10 +14184,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>583796</v>
+        <v>584331</v>
       </c>
       <c r="R129" t="n">
-        <v>7211546</v>
+        <v>7211693</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14246,10 +14246,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129000168</v>
+        <v>129000184</v>
       </c>
       <c r="B130" t="n">
-        <v>91519</v>
+        <v>79035</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14257,21 +14257,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>584331</v>
+        <v>584333</v>
       </c>
       <c r="R130" t="n">
-        <v>7211693</v>
+        <v>7211688</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14343,48 +14343,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129000185</v>
+        <v>129000166</v>
       </c>
       <c r="B131" t="n">
-        <v>92852</v>
+        <v>91522</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5964</v>
+        <v>1108</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>584074</v>
+        <v>583796</v>
       </c>
       <c r="R131" t="n">
-        <v>7211675</v>
+        <v>7211546</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14425,7 +14422,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14444,45 +14440,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129000184</v>
+        <v>129000185</v>
       </c>
       <c r="B132" t="n">
-        <v>79034</v>
+        <v>92855</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>584333</v>
+        <v>584074</v>
       </c>
       <c r="R132" t="n">
-        <v>7211688</v>
+        <v>7211675</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14523,6 +14522,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14544,7 +14544,7 @@
         <v>129000167</v>
       </c>
       <c r="B133" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>129000174</v>
       </c>
       <c r="B134" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>129012557</v>
       </c>
       <c r="B136" t="n">
-        <v>88923</v>
+        <v>88926</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>129012558</v>
       </c>
       <c r="B137" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>129012556</v>
       </c>
       <c r="B138" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>129000128</v>
       </c>
       <c r="B139" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15229,10 +15229,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129000136</v>
+        <v>129000179</v>
       </c>
       <c r="B140" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15240,21 +15240,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15264,10 +15264,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>583699</v>
+        <v>583976</v>
       </c>
       <c r="R140" t="n">
-        <v>7212348</v>
+        <v>7212366</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15300,11 +15300,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15331,10 +15326,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129000179</v>
+        <v>129000136</v>
       </c>
       <c r="B141" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15342,21 +15337,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15366,10 +15361,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>583976</v>
+        <v>583699</v>
       </c>
       <c r="R141" t="n">
-        <v>7212366</v>
+        <v>7212348</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15402,6 +15397,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15527,7 +15527,7 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -15537,7 +15537,7 @@
         <v>129085098</v>
       </c>
       <c r="B143" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -15634,7 +15634,7 @@
         <v>129085077</v>
       </c>
       <c r="B144" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>129085080</v>
       </c>
       <c r="B145" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15927,32 +15927,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129000106</v>
+        <v>129000171</v>
       </c>
       <c r="B147" t="n">
-        <v>92223</v>
+        <v>91544</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15962,10 +15962,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>583634</v>
+        <v>583882</v>
       </c>
       <c r="R147" t="n">
-        <v>7212397</v>
+        <v>7212369</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16024,32 +16024,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129000171</v>
+        <v>129000106</v>
       </c>
       <c r="B148" t="n">
-        <v>91541</v>
+        <v>92226</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16059,10 +16059,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>583882</v>
+        <v>583634</v>
       </c>
       <c r="R148" t="n">
-        <v>7212369</v>
+        <v>7212397</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16121,10 +16121,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129085094</v>
+        <v>129000159</v>
       </c>
       <c r="B149" t="n">
-        <v>91519</v>
+        <v>56904</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16132,37 +16132,37 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>583526</v>
+        <v>583817</v>
       </c>
       <c r="R149" t="n">
-        <v>7212468</v>
+        <v>7212328</v>
       </c>
       <c r="S149" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16206,22 +16206,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129000159</v>
+        <v>129085094</v>
       </c>
       <c r="B150" t="n">
-        <v>56904</v>
+        <v>91522</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16229,37 +16229,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>583817</v>
+        <v>583526</v>
       </c>
       <c r="R150" t="n">
-        <v>7212328</v>
+        <v>7212468</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16303,12 +16303,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -16318,7 +16318,7 @@
         <v>129000178</v>
       </c>
       <c r="B151" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>129085088</v>
       </c>
       <c r="B152" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16509,48 +16509,48 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129000103</v>
+        <v>129085076</v>
       </c>
       <c r="B153" t="n">
-        <v>91523</v>
+        <v>91491</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>583841</v>
+        <v>583540</v>
       </c>
       <c r="R153" t="n">
-        <v>7212355</v>
+        <v>7212450</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16594,22 +16594,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129000189</v>
+        <v>129000149</v>
       </c>
       <c r="B154" t="n">
-        <v>80174</v>
+        <v>97536</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16617,21 +16617,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6463</v>
+        <v>221941</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16641,10 +16641,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>583856</v>
+        <v>583660</v>
       </c>
       <c r="R154" t="n">
-        <v>7212375</v>
+        <v>7212365</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16703,32 +16703,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129000149</v>
+        <v>129000103</v>
       </c>
       <c r="B155" t="n">
-        <v>97533</v>
+        <v>91526</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16738,10 +16738,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>583660</v>
+        <v>583841</v>
       </c>
       <c r="R155" t="n">
-        <v>7212365</v>
+        <v>7212355</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16800,10 +16800,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129085076</v>
+        <v>129000189</v>
       </c>
       <c r="B156" t="n">
-        <v>91488</v>
+        <v>80175</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16811,37 +16811,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>583540</v>
+        <v>583856</v>
       </c>
       <c r="R156" t="n">
-        <v>7212450</v>
+        <v>7212375</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16885,12 +16885,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -16900,7 +16900,7 @@
         <v>129085096</v>
       </c>
       <c r="B157" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16994,32 +16994,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129000094</v>
+        <v>129000188</v>
       </c>
       <c r="B158" t="n">
-        <v>83010</v>
+        <v>80175</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17029,10 +17029,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>583585</v>
+        <v>583606</v>
       </c>
       <c r="R158" t="n">
-        <v>7212671</v>
+        <v>7212484</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17091,32 +17091,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129000188</v>
+        <v>129000110</v>
       </c>
       <c r="B159" t="n">
-        <v>80174</v>
+        <v>57883</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17126,10 +17126,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>583606</v>
+        <v>583842</v>
       </c>
       <c r="R159" t="n">
-        <v>7212484</v>
+        <v>7212868</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17188,10 +17188,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129000110</v>
+        <v>129000094</v>
       </c>
       <c r="B160" t="n">
-        <v>57883</v>
+        <v>83011</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17199,21 +17199,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17223,10 +17223,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>583842</v>
+        <v>583585</v>
       </c>
       <c r="R160" t="n">
-        <v>7212868</v>
+        <v>7212671</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17288,7 +17288,7 @@
         <v>129000096</v>
       </c>
       <c r="B161" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>129000100</v>
       </c>
       <c r="B162" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>129073200</v>
       </c>
       <c r="B163" t="n">
-        <v>91698</v>
+        <v>91701</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17576,10 +17576,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129000177</v>
+        <v>129000153</v>
       </c>
       <c r="B164" t="n">
-        <v>79034</v>
+        <v>80140</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17587,34 +17587,37 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>583609</v>
+        <v>583768</v>
       </c>
       <c r="R164" t="n">
-        <v>7212495</v>
+        <v>7212826</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17655,8 +17658,24 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
@@ -17673,10 +17692,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129000153</v>
+        <v>129000177</v>
       </c>
       <c r="B165" t="n">
-        <v>80139</v>
+        <v>79035</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17684,37 +17703,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>583768</v>
+        <v>583609</v>
       </c>
       <c r="R165" t="n">
-        <v>7212826</v>
+        <v>7212495</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17755,24 +17771,8 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
@@ -17792,7 +17792,7 @@
         <v>129000114</v>
       </c>
       <c r="B166" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>129085074</v>
       </c>
       <c r="B167" t="n">
-        <v>105704</v>
+        <v>105707</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>129085075</v>
       </c>
       <c r="B168" t="n">
-        <v>105704</v>
+        <v>105707</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18080,10 +18080,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129085078</v>
+        <v>129000104</v>
       </c>
       <c r="B169" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18111,17 +18111,17 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>583677</v>
+        <v>584023</v>
       </c>
       <c r="R169" t="n">
-        <v>7212815</v>
+        <v>7212353</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18165,22 +18165,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129000104</v>
+        <v>129085078</v>
       </c>
       <c r="B170" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18208,17 +18208,17 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>584023</v>
+        <v>583677</v>
       </c>
       <c r="R170" t="n">
-        <v>7212353</v>
+        <v>7212815</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18262,22 +18262,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129000170</v>
+        <v>129085099</v>
       </c>
       <c r="B171" t="n">
-        <v>91537</v>
+        <v>79035</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18285,37 +18285,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>583844</v>
+        <v>583975</v>
       </c>
       <c r="R171" t="n">
-        <v>7212348</v>
+        <v>7212333</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18359,22 +18359,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129000122</v>
+        <v>129000170</v>
       </c>
       <c r="B172" t="n">
-        <v>80140</v>
+        <v>91540</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18382,21 +18382,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18406,10 +18406,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>583833</v>
+        <v>583844</v>
       </c>
       <c r="R172" t="n">
-        <v>7212856</v>
+        <v>7212348</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18468,10 +18468,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129085099</v>
+        <v>129000122</v>
       </c>
       <c r="B173" t="n">
-        <v>79034</v>
+        <v>80141</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18479,37 +18479,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>583975</v>
+        <v>583833</v>
       </c>
       <c r="R173" t="n">
-        <v>7212333</v>
+        <v>7212856</v>
       </c>
       <c r="S173" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18553,12 +18553,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -18568,7 +18568,7 @@
         <v>129000176</v>
       </c>
       <c r="B174" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18662,10 +18662,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129000124</v>
+        <v>129000172</v>
       </c>
       <c r="B175" t="n">
-        <v>83015</v>
+        <v>91544</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18673,21 +18673,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18697,10 +18697,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>583770</v>
+        <v>583719</v>
       </c>
       <c r="R175" t="n">
-        <v>7212830</v>
+        <v>7212791</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18759,10 +18759,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129000172</v>
+        <v>129000124</v>
       </c>
       <c r="B176" t="n">
-        <v>91541</v>
+        <v>83016</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18770,21 +18770,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18794,10 +18794,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>583719</v>
+        <v>583770</v>
       </c>
       <c r="R176" t="n">
-        <v>7212791</v>
+        <v>7212830</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18859,7 +18859,7 @@
         <v>129085097</v>
       </c>
       <c r="B177" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>129085083</v>
       </c>
       <c r="B178" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>129085079</v>
       </c>
       <c r="B179" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19147,32 +19147,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129073201</v>
+        <v>129073202</v>
       </c>
       <c r="B180" t="n">
-        <v>92313</v>
+        <v>95509</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>918</v>
+        <v>2387</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19182,10 +19182,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>583599</v>
+        <v>584165</v>
       </c>
       <c r="R180" t="n">
-        <v>7212710</v>
+        <v>7211601</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19212,12 +19212,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19244,48 +19244,48 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129073202</v>
+        <v>129085095</v>
       </c>
       <c r="B181" t="n">
-        <v>95506</v>
+        <v>91544</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>2387</v>
+        <v>5432</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>584165</v>
+        <v>583378</v>
       </c>
       <c r="R181" t="n">
-        <v>7211601</v>
+        <v>7212728</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19309,12 +19309,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19329,22 +19329,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129000101</v>
+        <v>129000129</v>
       </c>
       <c r="B182" t="n">
-        <v>91523</v>
+        <v>91811</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19352,21 +19352,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19376,10 +19376,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>583663</v>
+        <v>583810</v>
       </c>
       <c r="R182" t="n">
-        <v>7212429</v>
+        <v>7212852</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19438,10 +19438,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129000129</v>
+        <v>129000101</v>
       </c>
       <c r="B183" t="n">
-        <v>91808</v>
+        <v>91526</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19449,21 +19449,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19473,10 +19473,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>583810</v>
+        <v>583663</v>
       </c>
       <c r="R183" t="n">
-        <v>7212852</v>
+        <v>7212429</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19535,48 +19535,48 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129085095</v>
+        <v>129073201</v>
       </c>
       <c r="B184" t="n">
-        <v>91541</v>
+        <v>92316</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5432</v>
+        <v>918</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>583378</v>
+        <v>583599</v>
       </c>
       <c r="R184" t="n">
-        <v>7212728</v>
+        <v>7212710</v>
       </c>
       <c r="S184" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19620,22 +19620,22 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129000121</v>
+        <v>129000132</v>
       </c>
       <c r="B185" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19643,21 +19643,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19667,10 +19667,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>583770</v>
+        <v>583968</v>
       </c>
       <c r="R185" t="n">
-        <v>7212825</v>
+        <v>7212362</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19703,6 +19703,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19729,10 +19734,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129000132</v>
+        <v>129000121</v>
       </c>
       <c r="B186" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19740,21 +19745,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19764,10 +19769,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>583968</v>
+        <v>583770</v>
       </c>
       <c r="R186" t="n">
-        <v>7212362</v>
+        <v>7212825</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19800,11 +19805,6 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19831,48 +19831,48 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129085092</v>
+        <v>129000160</v>
       </c>
       <c r="B187" t="n">
-        <v>58093</v>
+        <v>91522</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>584017</v>
+        <v>583674</v>
       </c>
       <c r="R187" t="n">
-        <v>7212353</v>
+        <v>7212755</v>
       </c>
       <c r="S187" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19916,60 +19916,60 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129000160</v>
+        <v>129085082</v>
       </c>
       <c r="B188" t="n">
-        <v>91519</v>
+        <v>80169</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>583674</v>
+        <v>583926</v>
       </c>
       <c r="R188" t="n">
-        <v>7212755</v>
+        <v>7212799</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20013,57 +20013,61 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129085082</v>
+        <v>129085086</v>
       </c>
       <c r="B189" t="n">
-        <v>80168</v>
+        <v>57723</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>583926</v>
+        <v>583569</v>
       </c>
       <c r="R189" t="n">
-        <v>7212799</v>
+        <v>7212757</v>
       </c>
       <c r="S189" t="n">
         <v>15</v>
@@ -20096,6 +20100,11 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20122,27 +20131,27 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129085086</v>
+        <v>129085092</v>
       </c>
       <c r="B190" t="n">
-        <v>57723</v>
+        <v>58093</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -20151,20 +20160,16 @@
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>583569</v>
+        <v>584017</v>
       </c>
       <c r="R190" t="n">
-        <v>7212757</v>
+        <v>7212353</v>
       </c>
       <c r="S190" t="n">
         <v>15</v>
@@ -20199,11 +20204,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD190" t="b">
         <v>0</v>
       </c>
@@ -20221,7 +20221,7 @@
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
@@ -20231,7 +20231,7 @@
         <v>129000162</v>
       </c>
       <c r="B191" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>129000154</v>
       </c>
       <c r="B192" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>

--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -8467,32 +8467,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128998122</v>
+        <v>128998142</v>
       </c>
       <c r="B71" t="n">
-        <v>105707</v>
+        <v>91522</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221725</v>
+        <v>1108</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>583934</v>
+        <v>583800</v>
       </c>
       <c r="R71" t="n">
-        <v>7212490</v>
+        <v>7212769</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8661,32 +8661,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128998142</v>
+        <v>128998122</v>
       </c>
       <c r="B73" t="n">
-        <v>91522</v>
+        <v>105707</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1108</v>
+        <v>221725</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8696,10 +8696,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583800</v>
+        <v>583934</v>
       </c>
       <c r="R73" t="n">
-        <v>7212769</v>
+        <v>7212490</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9049,32 +9049,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128998131</v>
+        <v>128998135</v>
       </c>
       <c r="B77" t="n">
-        <v>57720</v>
+        <v>91896</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>584025</v>
+        <v>583778</v>
       </c>
       <c r="R77" t="n">
-        <v>7212370</v>
+        <v>7212890</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9146,32 +9146,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128998135</v>
+        <v>128998124</v>
       </c>
       <c r="B78" t="n">
-        <v>91896</v>
+        <v>91526</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>583778</v>
+        <v>583784</v>
       </c>
       <c r="R78" t="n">
-        <v>7212890</v>
+        <v>7212884</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9243,10 +9243,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128998124</v>
+        <v>128998131</v>
       </c>
       <c r="B79" t="n">
-        <v>91526</v>
+        <v>57720</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9254,21 +9254,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583784</v>
+        <v>584025</v>
       </c>
       <c r="R79" t="n">
-        <v>7212884</v>
+        <v>7212370</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9437,10 +9437,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129000181</v>
+        <v>129000163</v>
       </c>
       <c r="B81" t="n">
-        <v>79035</v>
+        <v>91522</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9448,21 +9448,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9472,10 +9472,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583824</v>
+        <v>584005</v>
       </c>
       <c r="R81" t="n">
-        <v>7211526</v>
+        <v>7211652</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9534,10 +9534,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129000163</v>
+        <v>129000181</v>
       </c>
       <c r="B82" t="n">
-        <v>91522</v>
+        <v>79035</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9545,21 +9545,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9569,10 +9569,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>584005</v>
+        <v>583824</v>
       </c>
       <c r="R82" t="n">
-        <v>7211652</v>
+        <v>7211526</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9728,45 +9728,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128998153</v>
+        <v>129000145</v>
       </c>
       <c r="B84" t="n">
-        <v>80175</v>
+        <v>57723</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>583842</v>
+        <v>583826</v>
       </c>
       <c r="R84" t="n">
-        <v>7212492</v>
+        <v>7211682</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9793,12 +9793,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9813,12 +9813,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9922,10 +9922,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129000115</v>
+        <v>128998153</v>
       </c>
       <c r="B86" t="n">
-        <v>80169</v>
+        <v>80175</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9933,34 +9933,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>583856</v>
+        <v>583842</v>
       </c>
       <c r="R86" t="n">
-        <v>7212374</v>
+        <v>7212492</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10007,44 +10007,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129000145</v>
+        <v>129000115</v>
       </c>
       <c r="B87" t="n">
-        <v>57723</v>
+        <v>80169</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10054,10 +10054,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>583826</v>
+        <v>583856</v>
       </c>
       <c r="R87" t="n">
-        <v>7211682</v>
+        <v>7212374</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10084,12 +10084,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10420,10 +10420,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128997035</v>
+        <v>128997040</v>
       </c>
       <c r="B91" t="n">
-        <v>57883</v>
+        <v>91522</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10431,21 +10431,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>583868</v>
+        <v>583800</v>
       </c>
       <c r="R91" t="n">
-        <v>7212926</v>
+        <v>7212621</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10517,45 +10517,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129000116</v>
+        <v>128998130</v>
       </c>
       <c r="B92" t="n">
-        <v>57720</v>
+        <v>80169</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>584099</v>
+        <v>583781</v>
       </c>
       <c r="R92" t="n">
-        <v>7211521</v>
+        <v>7212767</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10582,17 +10582,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Spillkråkehack på låga</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10607,22 +10602,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128997040</v>
+        <v>128997035</v>
       </c>
       <c r="B93" t="n">
-        <v>91522</v>
+        <v>57883</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10630,21 +10625,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10654,10 +10649,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>583800</v>
+        <v>583868</v>
       </c>
       <c r="R93" t="n">
-        <v>7212621</v>
+        <v>7212926</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10716,45 +10711,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128998130</v>
+        <v>129000165</v>
       </c>
       <c r="B94" t="n">
-        <v>80169</v>
+        <v>91522</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>583781</v>
+        <v>583888</v>
       </c>
       <c r="R94" t="n">
-        <v>7212767</v>
+        <v>7211663</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10781,12 +10776,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10801,22 +10796,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129000165</v>
+        <v>129000116</v>
       </c>
       <c r="B95" t="n">
-        <v>91522</v>
+        <v>57720</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10824,21 +10819,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10848,10 +10843,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>583888</v>
+        <v>584099</v>
       </c>
       <c r="R95" t="n">
-        <v>7211663</v>
+        <v>7211521</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10884,6 +10879,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Spillkråkehack på låga</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10910,7 +10910,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129000175</v>
+        <v>128998146</v>
       </c>
       <c r="B96" t="n">
         <v>91544</v>
@@ -10941,14 +10941,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>583975</v>
+        <v>583700</v>
       </c>
       <c r="R96" t="n">
-        <v>7211530</v>
+        <v>7212870</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10975,12 +10975,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10995,22 +10995,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128998146</v>
+        <v>128998150</v>
       </c>
       <c r="B97" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11018,21 +11018,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11042,10 +11042,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>583700</v>
+        <v>583862</v>
       </c>
       <c r="R97" t="n">
-        <v>7212870</v>
+        <v>7212466</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11104,27 +11104,27 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128998150</v>
+        <v>128998155</v>
       </c>
       <c r="B98" t="n">
-        <v>79035</v>
+        <v>80175</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -11139,10 +11139,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>583862</v>
+        <v>583778</v>
       </c>
       <c r="R98" t="n">
-        <v>7212466</v>
+        <v>7212766</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11201,45 +11201,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128998155</v>
+        <v>129000175</v>
       </c>
       <c r="B99" t="n">
-        <v>80175</v>
+        <v>91544</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>583778</v>
+        <v>583975</v>
       </c>
       <c r="R99" t="n">
-        <v>7212766</v>
+        <v>7211530</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11266,12 +11266,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11286,57 +11286,57 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129000150</v>
+        <v>128998136</v>
       </c>
       <c r="B100" t="n">
-        <v>91896</v>
+        <v>80176</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1506</v>
+        <v>6464</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>583951</v>
+        <v>583838</v>
       </c>
       <c r="R100" t="n">
-        <v>7211500</v>
+        <v>7212502</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11363,12 +11363,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11383,12 +11383,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11492,45 +11492,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128998136</v>
+        <v>129000150</v>
       </c>
       <c r="B102" t="n">
-        <v>80176</v>
+        <v>91896</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>1506</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>583838</v>
+        <v>583951</v>
       </c>
       <c r="R102" t="n">
-        <v>7212502</v>
+        <v>7211500</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11557,12 +11557,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11577,12 +11577,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11686,10 +11686,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128998250</v>
+        <v>128997039</v>
       </c>
       <c r="B104" t="n">
-        <v>57723</v>
+        <v>91522</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11697,42 +11697,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>583752</v>
+        <v>583807</v>
       </c>
       <c r="R104" t="n">
-        <v>7212679</v>
+        <v>7212750</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11767,11 +11759,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
@@ -11784,12 +11771,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -11995,32 +11982,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128997039</v>
+        <v>129000147</v>
       </c>
       <c r="B107" t="n">
-        <v>91522</v>
+        <v>97536</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1108</v>
+        <v>221941</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12030,10 +12017,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>583807</v>
+        <v>584141</v>
       </c>
       <c r="R107" t="n">
-        <v>7212750</v>
+        <v>7211590</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12060,12 +12047,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12080,57 +12067,65 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129000147</v>
+        <v>128998250</v>
       </c>
       <c r="B108" t="n">
-        <v>97536</v>
+        <v>57723</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>584141</v>
+        <v>583752</v>
       </c>
       <c r="R108" t="n">
-        <v>7211590</v>
+        <v>7212679</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12157,12 +12152,17 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12177,44 +12177,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128998149</v>
+        <v>128998126</v>
       </c>
       <c r="B109" t="n">
-        <v>79035</v>
+        <v>92226</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12224,10 +12224,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>584059</v>
+        <v>583748</v>
       </c>
       <c r="R109" t="n">
-        <v>7212428</v>
+        <v>7212869</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12286,10 +12286,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129000187</v>
+        <v>128998149</v>
       </c>
       <c r="B110" t="n">
-        <v>88926</v>
+        <v>79035</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12297,34 +12297,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>583966</v>
+        <v>584059</v>
       </c>
       <c r="R110" t="n">
-        <v>7211510</v>
+        <v>7212428</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12351,12 +12351,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12371,22 +12371,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129000146</v>
+        <v>129000187</v>
       </c>
       <c r="B111" t="n">
-        <v>57723</v>
+        <v>88926</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12394,21 +12394,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12418,10 +12418,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>583819</v>
+        <v>583966</v>
       </c>
       <c r="R111" t="n">
-        <v>7211689</v>
+        <v>7211510</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12454,11 +12454,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12485,45 +12480,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128998126</v>
+        <v>129000146</v>
       </c>
       <c r="B112" t="n">
-        <v>92226</v>
+        <v>57723</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>583748</v>
+        <v>583819</v>
       </c>
       <c r="R112" t="n">
-        <v>7212869</v>
+        <v>7211689</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12550,12 +12545,17 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12570,12 +12570,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -12679,45 +12679,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129000173</v>
+        <v>128998138</v>
       </c>
       <c r="B114" t="n">
-        <v>91544</v>
+        <v>80176</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>583879</v>
+        <v>583742</v>
       </c>
       <c r="R114" t="n">
-        <v>7211699</v>
+        <v>7213116</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12744,12 +12744,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12764,57 +12764,57 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128998138</v>
+        <v>129000173</v>
       </c>
       <c r="B115" t="n">
-        <v>80176</v>
+        <v>91544</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>583742</v>
+        <v>583879</v>
       </c>
       <c r="R115" t="n">
-        <v>7213116</v>
+        <v>7211699</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12841,12 +12841,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12861,44 +12861,44 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129000135</v>
+        <v>129000119</v>
       </c>
       <c r="B116" t="n">
-        <v>57723</v>
+        <v>83009</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12908,10 +12908,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>584139</v>
+        <v>583763</v>
       </c>
       <c r="R116" t="n">
-        <v>7211559</v>
+        <v>7211568</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12944,11 +12944,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12975,10 +12970,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129000097</v>
+        <v>129000182</v>
       </c>
       <c r="B117" t="n">
-        <v>83011</v>
+        <v>79035</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12986,21 +12981,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13010,10 +13005,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>584170</v>
+        <v>584124</v>
       </c>
       <c r="R117" t="n">
-        <v>7211600</v>
+        <v>7211556</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13072,10 +13067,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129000182</v>
+        <v>129000097</v>
       </c>
       <c r="B118" t="n">
-        <v>79035</v>
+        <v>83011</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13083,21 +13078,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13107,10 +13102,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>584124</v>
+        <v>584170</v>
       </c>
       <c r="R118" t="n">
-        <v>7211556</v>
+        <v>7211600</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13169,32 +13164,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129000119</v>
+        <v>129000135</v>
       </c>
       <c r="B119" t="n">
-        <v>83009</v>
+        <v>57723</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13204,10 +13199,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>583763</v>
+        <v>584139</v>
       </c>
       <c r="R119" t="n">
-        <v>7211568</v>
+        <v>7211559</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13240,6 +13235,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13266,32 +13266,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128998148</v>
+        <v>128998129</v>
       </c>
       <c r="B120" t="n">
-        <v>91544</v>
+        <v>80169</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13301,10 +13301,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>583764</v>
+        <v>583743</v>
       </c>
       <c r="R120" t="n">
-        <v>7212875</v>
+        <v>7212862</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13363,27 +13363,27 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128998151</v>
+        <v>128998154</v>
       </c>
       <c r="B121" t="n">
-        <v>79035</v>
+        <v>80175</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -13398,10 +13398,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>583830</v>
+        <v>583743</v>
       </c>
       <c r="R121" t="n">
-        <v>7212605</v>
+        <v>7212862</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13460,32 +13460,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128998129</v>
+        <v>128998148</v>
       </c>
       <c r="B122" t="n">
-        <v>80169</v>
+        <v>91544</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13495,10 +13495,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>583743</v>
+        <v>583764</v>
       </c>
       <c r="R122" t="n">
-        <v>7212862</v>
+        <v>7212875</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13557,27 +13557,27 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128998154</v>
+        <v>128998151</v>
       </c>
       <c r="B123" t="n">
-        <v>80175</v>
+        <v>79035</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13592,10 +13592,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>583743</v>
+        <v>583830</v>
       </c>
       <c r="R123" t="n">
-        <v>7212862</v>
+        <v>7212605</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13853,10 +13853,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128998141</v>
+        <v>129000180</v>
       </c>
       <c r="B126" t="n">
-        <v>91522</v>
+        <v>79035</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13864,34 +13864,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>583789</v>
+        <v>583695</v>
       </c>
       <c r="R126" t="n">
-        <v>7213129</v>
+        <v>7211621</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13918,12 +13918,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13938,12 +13938,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -14052,10 +14052,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129000180</v>
+        <v>128998141</v>
       </c>
       <c r="B128" t="n">
-        <v>79035</v>
+        <v>91522</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14063,34 +14063,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>583695</v>
+        <v>583789</v>
       </c>
       <c r="R128" t="n">
-        <v>7211621</v>
+        <v>7213129</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14117,12 +14117,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14137,22 +14137,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129000168</v>
+        <v>129000184</v>
       </c>
       <c r="B129" t="n">
-        <v>91522</v>
+        <v>79035</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14160,21 +14160,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14184,10 +14184,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>584331</v>
+        <v>584333</v>
       </c>
       <c r="R129" t="n">
-        <v>7211693</v>
+        <v>7211688</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14246,10 +14246,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129000184</v>
+        <v>129000166</v>
       </c>
       <c r="B130" t="n">
-        <v>79035</v>
+        <v>91522</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14257,21 +14257,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>584333</v>
+        <v>583796</v>
       </c>
       <c r="R130" t="n">
-        <v>7211688</v>
+        <v>7211546</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14343,7 +14343,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129000166</v>
+        <v>129000168</v>
       </c>
       <c r="B131" t="n">
         <v>91522</v>
@@ -14378,10 +14378,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>583796</v>
+        <v>584331</v>
       </c>
       <c r="R131" t="n">
-        <v>7211546</v>
+        <v>7211693</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15132,32 +15132,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129000128</v>
+        <v>129000179</v>
       </c>
       <c r="B139" t="n">
-        <v>91981</v>
+        <v>79035</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15167,10 +15167,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>583804</v>
+        <v>583976</v>
       </c>
       <c r="R139" t="n">
-        <v>7212351</v>
+        <v>7212366</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15229,10 +15229,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129000179</v>
+        <v>129000136</v>
       </c>
       <c r="B140" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15240,21 +15240,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15264,10 +15264,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>583976</v>
+        <v>583699</v>
       </c>
       <c r="R140" t="n">
-        <v>7212366</v>
+        <v>7212348</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15300,6 +15300,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15326,32 +15331,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129000136</v>
+        <v>129000128</v>
       </c>
       <c r="B141" t="n">
-        <v>57723</v>
+        <v>91981</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15361,10 +15366,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>583699</v>
+        <v>583804</v>
       </c>
       <c r="R141" t="n">
-        <v>7212348</v>
+        <v>7212351</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15397,11 +15402,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15527,7 +15527,7 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -15721,7 +15721,7 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -15927,10 +15927,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129000171</v>
+        <v>129085094</v>
       </c>
       <c r="B147" t="n">
-        <v>91544</v>
+        <v>91522</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15938,37 +15938,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>583882</v>
+        <v>583526</v>
       </c>
       <c r="R147" t="n">
-        <v>7212369</v>
+        <v>7212468</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16012,44 +16012,44 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129000106</v>
+        <v>129000159</v>
       </c>
       <c r="B148" t="n">
-        <v>92226</v>
+        <v>56904</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3298</v>
+        <v>102612</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16059,10 +16059,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>583634</v>
+        <v>583817</v>
       </c>
       <c r="R148" t="n">
-        <v>7212397</v>
+        <v>7212328</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16121,10 +16121,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129000159</v>
+        <v>129000171</v>
       </c>
       <c r="B149" t="n">
-        <v>56904</v>
+        <v>91544</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16132,21 +16132,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16156,10 +16156,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>583817</v>
+        <v>583882</v>
       </c>
       <c r="R149" t="n">
-        <v>7212328</v>
+        <v>7212369</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16218,48 +16218,48 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129085094</v>
+        <v>129000106</v>
       </c>
       <c r="B150" t="n">
-        <v>91522</v>
+        <v>92226</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>583526</v>
+        <v>583634</v>
       </c>
       <c r="R150" t="n">
-        <v>7212468</v>
+        <v>7212397</v>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16303,12 +16303,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -16509,48 +16509,48 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129085076</v>
+        <v>129000103</v>
       </c>
       <c r="B153" t="n">
-        <v>91491</v>
+        <v>91526</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>583540</v>
+        <v>583841</v>
       </c>
       <c r="R153" t="n">
-        <v>7212450</v>
+        <v>7212355</v>
       </c>
       <c r="S153" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16594,22 +16594,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129000149</v>
+        <v>129000189</v>
       </c>
       <c r="B154" t="n">
-        <v>97536</v>
+        <v>80175</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16617,21 +16617,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16641,10 +16641,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>583660</v>
+        <v>583856</v>
       </c>
       <c r="R154" t="n">
-        <v>7212365</v>
+        <v>7212375</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16703,48 +16703,48 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129000103</v>
+        <v>129085076</v>
       </c>
       <c r="B155" t="n">
-        <v>91526</v>
+        <v>91491</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>583841</v>
+        <v>583540</v>
       </c>
       <c r="R155" t="n">
-        <v>7212355</v>
+        <v>7212450</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16788,22 +16788,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129000189</v>
+        <v>129000149</v>
       </c>
       <c r="B156" t="n">
-        <v>80175</v>
+        <v>97536</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16811,21 +16811,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6463</v>
+        <v>221941</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16835,10 +16835,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>583856</v>
+        <v>583660</v>
       </c>
       <c r="R156" t="n">
-        <v>7212375</v>
+        <v>7212365</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16897,48 +16897,48 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129085096</v>
+        <v>129000188</v>
       </c>
       <c r="B157" t="n">
-        <v>91544</v>
+        <v>80175</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>583522</v>
+        <v>583606</v>
       </c>
       <c r="R157" t="n">
-        <v>7212551</v>
+        <v>7212484</v>
       </c>
       <c r="S157" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16982,60 +16982,60 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129000188</v>
+        <v>129085096</v>
       </c>
       <c r="B158" t="n">
-        <v>80175</v>
+        <v>91544</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>583606</v>
+        <v>583522</v>
       </c>
       <c r="R158" t="n">
-        <v>7212484</v>
+        <v>7212551</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17079,12 +17079,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -17285,32 +17285,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129000096</v>
+        <v>129000100</v>
       </c>
       <c r="B161" t="n">
-        <v>83011</v>
+        <v>91491</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17320,10 +17320,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>583980</v>
+        <v>583841</v>
       </c>
       <c r="R161" t="n">
-        <v>7212363</v>
+        <v>7212873</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17382,32 +17382,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129000100</v>
+        <v>129000096</v>
       </c>
       <c r="B162" t="n">
-        <v>91491</v>
+        <v>83011</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17417,10 +17417,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>583841</v>
+        <v>583980</v>
       </c>
       <c r="R162" t="n">
-        <v>7212873</v>
+        <v>7212363</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17576,10 +17576,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129000153</v>
+        <v>129000177</v>
       </c>
       <c r="B164" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17587,37 +17587,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>583768</v>
+        <v>583609</v>
       </c>
       <c r="R164" t="n">
-        <v>7212826</v>
+        <v>7212495</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17658,24 +17655,8 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
@@ -17692,10 +17673,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129000177</v>
+        <v>129000153</v>
       </c>
       <c r="B165" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17703,34 +17684,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>583609</v>
+        <v>583768</v>
       </c>
       <c r="R165" t="n">
-        <v>7212495</v>
+        <v>7212826</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17771,8 +17755,24 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
@@ -17976,7 +17976,7 @@
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
@@ -18267,17 +18267,17 @@
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129085099</v>
+        <v>129000170</v>
       </c>
       <c r="B171" t="n">
-        <v>79035</v>
+        <v>91540</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18285,37 +18285,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>583975</v>
+        <v>583844</v>
       </c>
       <c r="R171" t="n">
-        <v>7212333</v>
+        <v>7212348</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18359,22 +18359,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129000170</v>
+        <v>129000122</v>
       </c>
       <c r="B172" t="n">
-        <v>91540</v>
+        <v>80141</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18382,21 +18382,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18406,10 +18406,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>583844</v>
+        <v>583833</v>
       </c>
       <c r="R172" t="n">
-        <v>7212348</v>
+        <v>7212856</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18468,10 +18468,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129000122</v>
+        <v>129085099</v>
       </c>
       <c r="B173" t="n">
-        <v>80141</v>
+        <v>79035</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18479,37 +18479,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>583833</v>
+        <v>583975</v>
       </c>
       <c r="R173" t="n">
-        <v>7212856</v>
+        <v>7212333</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18553,12 +18553,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -18662,10 +18662,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129000172</v>
+        <v>129000124</v>
       </c>
       <c r="B175" t="n">
-        <v>91544</v>
+        <v>83016</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18673,21 +18673,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18697,10 +18697,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>583719</v>
+        <v>583770</v>
       </c>
       <c r="R175" t="n">
-        <v>7212791</v>
+        <v>7212830</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18759,10 +18759,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129000124</v>
+        <v>129000172</v>
       </c>
       <c r="B176" t="n">
-        <v>83016</v>
+        <v>91544</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18770,21 +18770,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18794,10 +18794,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>583770</v>
+        <v>583719</v>
       </c>
       <c r="R176" t="n">
-        <v>7212830</v>
+        <v>7212791</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19140,55 +19140,55 @@
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129073202</v>
+        <v>129085095</v>
       </c>
       <c r="B180" t="n">
-        <v>95509</v>
+        <v>91544</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>2387</v>
+        <v>5432</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>584165</v>
+        <v>583378</v>
       </c>
       <c r="R180" t="n">
-        <v>7211601</v>
+        <v>7212728</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19212,12 +19212,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19232,22 +19232,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129085095</v>
+        <v>129000101</v>
       </c>
       <c r="B181" t="n">
-        <v>91544</v>
+        <v>91526</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19255,37 +19255,37 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>583378</v>
+        <v>583663</v>
       </c>
       <c r="R181" t="n">
-        <v>7212728</v>
+        <v>7212429</v>
       </c>
       <c r="S181" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19329,12 +19329,12 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
@@ -19438,32 +19438,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129000101</v>
+        <v>129073201</v>
       </c>
       <c r="B183" t="n">
-        <v>91526</v>
+        <v>92316</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1202</v>
+        <v>918</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19473,10 +19473,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>583663</v>
+        <v>583599</v>
       </c>
       <c r="R183" t="n">
-        <v>7212429</v>
+        <v>7212710</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19528,39 +19528,39 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129073201</v>
+        <v>129073202</v>
       </c>
       <c r="B184" t="n">
-        <v>92316</v>
+        <v>95509</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>918</v>
+        <v>2387</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19570,10 +19570,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>583599</v>
+        <v>584165</v>
       </c>
       <c r="R184" t="n">
-        <v>7212710</v>
+        <v>7211601</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19600,12 +19600,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19734,48 +19734,48 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129000121</v>
+        <v>129085092</v>
       </c>
       <c r="B186" t="n">
-        <v>80141</v>
+        <v>58093</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2081</v>
+        <v>103015</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>583770</v>
+        <v>584017</v>
       </c>
       <c r="R186" t="n">
-        <v>7212825</v>
+        <v>7212353</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19819,12 +19819,12 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
@@ -19928,48 +19928,48 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129085082</v>
+        <v>129000121</v>
       </c>
       <c r="B188" t="n">
-        <v>80169</v>
+        <v>80141</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>583926</v>
+        <v>583770</v>
       </c>
       <c r="R188" t="n">
-        <v>7212799</v>
+        <v>7212825</v>
       </c>
       <c r="S188" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20013,61 +20013,57 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129085086</v>
+        <v>129085082</v>
       </c>
       <c r="B189" t="n">
-        <v>57723</v>
+        <v>80169</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>583569</v>
+        <v>583926</v>
       </c>
       <c r="R189" t="n">
-        <v>7212757</v>
+        <v>7212799</v>
       </c>
       <c r="S189" t="n">
         <v>15</v>
@@ -20100,11 +20096,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20131,27 +20122,27 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129085092</v>
+        <v>129085086</v>
       </c>
       <c r="B190" t="n">
-        <v>58093</v>
+        <v>57723</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -20160,16 +20151,20 @@
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>584017</v>
+        <v>583569</v>
       </c>
       <c r="R190" t="n">
-        <v>7212353</v>
+        <v>7212757</v>
       </c>
       <c r="S190" t="n">
         <v>15</v>
@@ -20204,6 +20199,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD190" t="b">
         <v>0</v>
       </c>
@@ -20221,7 +20221,7 @@
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>

--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -9340,10 +9340,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128998147</v>
+        <v>129000181</v>
       </c>
       <c r="B80" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9351,34 +9351,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583732</v>
+        <v>583824</v>
       </c>
       <c r="R80" t="n">
-        <v>7212858</v>
+        <v>7211526</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9425,22 +9425,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129000163</v>
+        <v>128998147</v>
       </c>
       <c r="B81" t="n">
-        <v>91522</v>
+        <v>91544</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9448,34 +9448,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>584005</v>
+        <v>583732</v>
       </c>
       <c r="R81" t="n">
-        <v>7211652</v>
+        <v>7212858</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9522,22 +9522,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129000181</v>
+        <v>129000163</v>
       </c>
       <c r="B82" t="n">
-        <v>79035</v>
+        <v>91522</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9545,21 +9545,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9569,10 +9569,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>583824</v>
+        <v>584005</v>
       </c>
       <c r="R82" t="n">
-        <v>7211526</v>
+        <v>7211652</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9728,10 +9728,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129000145</v>
+        <v>128998133</v>
       </c>
       <c r="B84" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9739,34 +9739,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>583826</v>
+        <v>583743</v>
       </c>
       <c r="R84" t="n">
-        <v>7211682</v>
+        <v>7212862</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9793,12 +9793,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9813,57 +9813,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128998133</v>
+        <v>129000115</v>
       </c>
       <c r="B85" t="n">
-        <v>80141</v>
+        <v>80169</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>583743</v>
+        <v>583856</v>
       </c>
       <c r="R85" t="n">
-        <v>7212862</v>
+        <v>7212374</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9910,57 +9910,57 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128998153</v>
+        <v>129000145</v>
       </c>
       <c r="B86" t="n">
-        <v>80175</v>
+        <v>57723</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>583842</v>
+        <v>583826</v>
       </c>
       <c r="R86" t="n">
-        <v>7212492</v>
+        <v>7211682</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9987,12 +9987,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10007,22 +10007,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129000115</v>
+        <v>128998153</v>
       </c>
       <c r="B87" t="n">
-        <v>80169</v>
+        <v>80175</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10030,34 +10030,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>583856</v>
+        <v>583842</v>
       </c>
       <c r="R87" t="n">
-        <v>7212374</v>
+        <v>7212492</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10104,12 +10104,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -13266,32 +13266,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128998129</v>
+        <v>128998151</v>
       </c>
       <c r="B120" t="n">
-        <v>80169</v>
+        <v>79035</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13301,10 +13301,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>583743</v>
+        <v>583830</v>
       </c>
       <c r="R120" t="n">
-        <v>7212862</v>
+        <v>7212605</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13363,10 +13363,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128998154</v>
+        <v>129000169</v>
       </c>
       <c r="B121" t="n">
-        <v>80175</v>
+        <v>82994</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13374,34 +13374,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6463</v>
+        <v>6439</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>583743</v>
+        <v>583695</v>
       </c>
       <c r="R121" t="n">
-        <v>7212862</v>
+        <v>7211591</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13428,12 +13428,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13448,12 +13448,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -13557,32 +13557,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128998151</v>
+        <v>128998129</v>
       </c>
       <c r="B123" t="n">
-        <v>79035</v>
+        <v>80169</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13592,10 +13592,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>583830</v>
+        <v>583743</v>
       </c>
       <c r="R123" t="n">
-        <v>7212605</v>
+        <v>7212862</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13654,45 +13654,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129000144</v>
+        <v>128998154</v>
       </c>
       <c r="B124" t="n">
-        <v>57723</v>
+        <v>80175</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>583832</v>
+        <v>583743</v>
       </c>
       <c r="R124" t="n">
-        <v>7211693</v>
+        <v>7212862</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13719,17 +13719,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13744,44 +13739,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129000169</v>
+        <v>129000144</v>
       </c>
       <c r="B125" t="n">
-        <v>82994</v>
+        <v>57723</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13791,10 +13786,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>583695</v>
+        <v>583832</v>
       </c>
       <c r="R125" t="n">
-        <v>7211591</v>
+        <v>7211693</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13827,6 +13822,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13853,10 +13853,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129000180</v>
+        <v>129000142</v>
       </c>
       <c r="B126" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13864,21 +13864,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13888,10 +13888,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>583695</v>
+        <v>583922</v>
       </c>
       <c r="R126" t="n">
-        <v>7211621</v>
+        <v>7211662</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13924,6 +13924,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13950,10 +13955,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129000142</v>
+        <v>128998141</v>
       </c>
       <c r="B127" t="n">
-        <v>57723</v>
+        <v>91522</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13961,34 +13966,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>583922</v>
+        <v>583789</v>
       </c>
       <c r="R127" t="n">
-        <v>7211662</v>
+        <v>7213129</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14015,17 +14020,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14040,22 +14040,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128998141</v>
+        <v>129000180</v>
       </c>
       <c r="B128" t="n">
-        <v>91522</v>
+        <v>79035</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14063,34 +14063,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>583789</v>
+        <v>583695</v>
       </c>
       <c r="R128" t="n">
-        <v>7213129</v>
+        <v>7211621</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14117,12 +14117,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14137,12 +14137,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -14638,10 +14638,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129000174</v>
+        <v>129000138</v>
       </c>
       <c r="B134" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14649,21 +14649,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14673,10 +14673,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>583934</v>
+        <v>583805</v>
       </c>
       <c r="R134" t="n">
-        <v>7211520</v>
+        <v>7211693</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14709,6 +14709,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14735,10 +14740,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129000138</v>
+        <v>129000174</v>
       </c>
       <c r="B135" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14746,21 +14751,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14770,10 +14775,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>583805</v>
+        <v>583934</v>
       </c>
       <c r="R135" t="n">
-        <v>7211693</v>
+        <v>7211520</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14806,11 +14811,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15132,32 +15132,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129000179</v>
+        <v>129000128</v>
       </c>
       <c r="B139" t="n">
-        <v>79035</v>
+        <v>91981</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15167,10 +15167,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>583976</v>
+        <v>583804</v>
       </c>
       <c r="R139" t="n">
-        <v>7212366</v>
+        <v>7212351</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15229,10 +15229,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129000136</v>
+        <v>129000179</v>
       </c>
       <c r="B140" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15240,21 +15240,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15264,10 +15264,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>583699</v>
+        <v>583976</v>
       </c>
       <c r="R140" t="n">
-        <v>7212348</v>
+        <v>7212366</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15300,11 +15300,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15331,32 +15326,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129000128</v>
+        <v>129000136</v>
       </c>
       <c r="B141" t="n">
-        <v>91981</v>
+        <v>57723</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15366,10 +15361,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>583804</v>
+        <v>583699</v>
       </c>
       <c r="R141" t="n">
-        <v>7212351</v>
+        <v>7212348</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15402,6 +15397,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15631,10 +15631,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129085077</v>
+        <v>129000137</v>
       </c>
       <c r="B144" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15642,37 +15642,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>583874</v>
+        <v>583784</v>
       </c>
       <c r="R144" t="n">
-        <v>7212775</v>
+        <v>7212338</v>
       </c>
       <c r="S144" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15702,6 +15702,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15716,19 +15721,19 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129085080</v>
+        <v>129085077</v>
       </c>
       <c r="B145" t="n">
         <v>91526</v>
@@ -15763,10 +15768,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>583726</v>
+        <v>583874</v>
       </c>
       <c r="R145" t="n">
-        <v>7212315</v>
+        <v>7212775</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15825,10 +15830,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129000137</v>
+        <v>129085080</v>
       </c>
       <c r="B146" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15836,37 +15841,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>583784</v>
+        <v>583726</v>
       </c>
       <c r="R146" t="n">
-        <v>7212338</v>
+        <v>7212315</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15896,11 +15901,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15915,22 +15915,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129085094</v>
+        <v>129000171</v>
       </c>
       <c r="B147" t="n">
-        <v>91522</v>
+        <v>91544</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15938,37 +15938,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>583526</v>
+        <v>583882</v>
       </c>
       <c r="R147" t="n">
-        <v>7212468</v>
+        <v>7212369</v>
       </c>
       <c r="S147" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16012,22 +16012,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129000159</v>
+        <v>129085094</v>
       </c>
       <c r="B148" t="n">
-        <v>56904</v>
+        <v>91522</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16035,37 +16035,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>583817</v>
+        <v>583526</v>
       </c>
       <c r="R148" t="n">
-        <v>7212328</v>
+        <v>7212468</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16109,44 +16109,44 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129000171</v>
+        <v>129000106</v>
       </c>
       <c r="B149" t="n">
-        <v>91544</v>
+        <v>92226</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16156,10 +16156,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>583882</v>
+        <v>583634</v>
       </c>
       <c r="R149" t="n">
-        <v>7212369</v>
+        <v>7212397</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16218,32 +16218,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129000106</v>
+        <v>129000159</v>
       </c>
       <c r="B150" t="n">
-        <v>92226</v>
+        <v>56904</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3298</v>
+        <v>102612</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16253,10 +16253,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>583634</v>
+        <v>583817</v>
       </c>
       <c r="R150" t="n">
-        <v>7212397</v>
+        <v>7212328</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16703,10 +16703,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129085076</v>
+        <v>129000149</v>
       </c>
       <c r="B155" t="n">
-        <v>91491</v>
+        <v>97536</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16714,37 +16714,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>583540</v>
+        <v>583660</v>
       </c>
       <c r="R155" t="n">
-        <v>7212450</v>
+        <v>7212365</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16788,22 +16788,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129000149</v>
+        <v>129085076</v>
       </c>
       <c r="B156" t="n">
-        <v>97536</v>
+        <v>91491</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16811,37 +16811,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>583660</v>
+        <v>583540</v>
       </c>
       <c r="R156" t="n">
-        <v>7212365</v>
+        <v>7212450</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16885,60 +16885,60 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129000188</v>
+        <v>129085096</v>
       </c>
       <c r="B157" t="n">
-        <v>80175</v>
+        <v>91544</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>583606</v>
+        <v>583522</v>
       </c>
       <c r="R157" t="n">
-        <v>7212484</v>
+        <v>7212551</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16982,22 +16982,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129085096</v>
+        <v>129000094</v>
       </c>
       <c r="B158" t="n">
-        <v>91544</v>
+        <v>83011</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17005,37 +17005,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>583522</v>
+        <v>583585</v>
       </c>
       <c r="R158" t="n">
-        <v>7212551</v>
+        <v>7212671</v>
       </c>
       <c r="S158" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17079,44 +17079,44 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129000110</v>
+        <v>129000188</v>
       </c>
       <c r="B159" t="n">
-        <v>57883</v>
+        <v>80175</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17126,10 +17126,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>583842</v>
+        <v>583606</v>
       </c>
       <c r="R159" t="n">
-        <v>7212868</v>
+        <v>7212484</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17188,10 +17188,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129000094</v>
+        <v>129000110</v>
       </c>
       <c r="B160" t="n">
-        <v>83011</v>
+        <v>57883</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17199,21 +17199,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17223,10 +17223,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>583585</v>
+        <v>583842</v>
       </c>
       <c r="R160" t="n">
-        <v>7212671</v>
+        <v>7212868</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17576,10 +17576,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129000177</v>
+        <v>129000153</v>
       </c>
       <c r="B164" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17587,34 +17587,37 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>583609</v>
+        <v>583768</v>
       </c>
       <c r="R164" t="n">
-        <v>7212495</v>
+        <v>7212826</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17655,8 +17658,24 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
@@ -17673,10 +17692,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129000153</v>
+        <v>129000177</v>
       </c>
       <c r="B165" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17684,37 +17703,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>583768</v>
+        <v>583609</v>
       </c>
       <c r="R165" t="n">
-        <v>7212826</v>
+        <v>7212495</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17755,24 +17771,8 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
@@ -18080,7 +18080,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129000104</v>
+        <v>129085078</v>
       </c>
       <c r="B169" t="n">
         <v>91526</v>
@@ -18111,17 +18111,17 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>584023</v>
+        <v>583677</v>
       </c>
       <c r="R169" t="n">
-        <v>7212353</v>
+        <v>7212815</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18165,19 +18165,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129085078</v>
+        <v>129000104</v>
       </c>
       <c r="B170" t="n">
         <v>91526</v>
@@ -18208,17 +18208,17 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>583677</v>
+        <v>584023</v>
       </c>
       <c r="R170" t="n">
-        <v>7212815</v>
+        <v>7212353</v>
       </c>
       <c r="S170" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18262,12 +18262,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -19147,10 +19147,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129085095</v>
+        <v>129000101</v>
       </c>
       <c r="B180" t="n">
-        <v>91544</v>
+        <v>91526</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19158,37 +19158,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>583378</v>
+        <v>583663</v>
       </c>
       <c r="R180" t="n">
-        <v>7212728</v>
+        <v>7212429</v>
       </c>
       <c r="S180" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19232,22 +19232,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129000101</v>
+        <v>129000129</v>
       </c>
       <c r="B181" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19255,21 +19255,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19279,10 +19279,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>583663</v>
+        <v>583810</v>
       </c>
       <c r="R181" t="n">
-        <v>7212429</v>
+        <v>7212852</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19341,32 +19341,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129000129</v>
+        <v>129073201</v>
       </c>
       <c r="B182" t="n">
-        <v>91811</v>
+        <v>92316</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>658</v>
+        <v>918</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19376,10 +19376,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>583810</v>
+        <v>583599</v>
       </c>
       <c r="R182" t="n">
-        <v>7212852</v>
+        <v>7212710</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19431,55 +19431,55 @@
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129073201</v>
+        <v>129085095</v>
       </c>
       <c r="B183" t="n">
-        <v>92316</v>
+        <v>91544</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>918</v>
+        <v>5432</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>583599</v>
+        <v>583378</v>
       </c>
       <c r="R183" t="n">
-        <v>7212710</v>
+        <v>7212728</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -19523,12 +19523,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>

--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -8171,32 +8171,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128998140</v>
+        <v>128998144</v>
       </c>
       <c r="B68" t="n">
-        <v>91522</v>
+        <v>82994</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1108</v>
+        <v>6439</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8206,10 +8206,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583855</v>
+        <v>583765</v>
       </c>
       <c r="R68" t="n">
-        <v>7213081</v>
+        <v>7212611</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8268,45 +8268,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128998144</v>
+        <v>129000140</v>
       </c>
       <c r="B69" t="n">
-        <v>82994</v>
+        <v>57723</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>583765</v>
+        <v>584092</v>
       </c>
       <c r="R69" t="n">
-        <v>7212611</v>
+        <v>7211517</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8333,12 +8333,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8353,22 +8358,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129000140</v>
+        <v>128998140</v>
       </c>
       <c r="B70" t="n">
-        <v>57723</v>
+        <v>91522</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8376,34 +8381,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>584092</v>
+        <v>583855</v>
       </c>
       <c r="R70" t="n">
-        <v>7211517</v>
+        <v>7213081</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8430,17 +8435,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8455,12 +8455,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8564,32 +8564,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128997038</v>
+        <v>129000183</v>
       </c>
       <c r="B72" t="n">
-        <v>97536</v>
+        <v>79035</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8599,10 +8599,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583850</v>
+        <v>584220</v>
       </c>
       <c r="R72" t="n">
-        <v>7212515</v>
+        <v>7211664</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8629,12 +8629,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8649,22 +8649,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128998122</v>
+        <v>128997038</v>
       </c>
       <c r="B73" t="n">
-        <v>105707</v>
+        <v>97536</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8672,34 +8672,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221725</v>
+        <v>221941</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583934</v>
+        <v>583850</v>
       </c>
       <c r="R73" t="n">
-        <v>7212490</v>
+        <v>7212515</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8746,57 +8746,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129000183</v>
+        <v>128998122</v>
       </c>
       <c r="B74" t="n">
-        <v>79035</v>
+        <v>105707</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>584220</v>
+        <v>583934</v>
       </c>
       <c r="R74" t="n">
-        <v>7211664</v>
+        <v>7212490</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8843,57 +8843,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128998128</v>
+        <v>129000152</v>
       </c>
       <c r="B75" t="n">
-        <v>57883</v>
+        <v>80168</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583799</v>
+        <v>584338</v>
       </c>
       <c r="R75" t="n">
-        <v>7212748</v>
+        <v>7211689</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8940,57 +8940,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129000152</v>
+        <v>128998128</v>
       </c>
       <c r="B76" t="n">
-        <v>80168</v>
+        <v>57883</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>584338</v>
+        <v>583799</v>
       </c>
       <c r="R76" t="n">
-        <v>7211689</v>
+        <v>7212748</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9017,12 +9017,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9037,44 +9037,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128998135</v>
+        <v>128998124</v>
       </c>
       <c r="B77" t="n">
-        <v>91896</v>
+        <v>91526</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583778</v>
+        <v>583784</v>
       </c>
       <c r="R77" t="n">
-        <v>7212890</v>
+        <v>7212884</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9146,32 +9146,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128998124</v>
+        <v>128998135</v>
       </c>
       <c r="B78" t="n">
-        <v>91526</v>
+        <v>91896</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>1506</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>583784</v>
+        <v>583778</v>
       </c>
       <c r="R78" t="n">
-        <v>7212884</v>
+        <v>7212890</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9340,10 +9340,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129000181</v>
+        <v>129000163</v>
       </c>
       <c r="B80" t="n">
-        <v>79035</v>
+        <v>91522</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9351,21 +9351,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9375,10 +9375,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583824</v>
+        <v>584005</v>
       </c>
       <c r="R80" t="n">
-        <v>7211526</v>
+        <v>7211652</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9437,10 +9437,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128998147</v>
+        <v>129000181</v>
       </c>
       <c r="B81" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9448,34 +9448,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583732</v>
+        <v>583824</v>
       </c>
       <c r="R81" t="n">
-        <v>7212858</v>
+        <v>7211526</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9522,22 +9522,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129000163</v>
+        <v>128998147</v>
       </c>
       <c r="B82" t="n">
-        <v>91522</v>
+        <v>91544</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9545,34 +9545,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>584005</v>
+        <v>583732</v>
       </c>
       <c r="R82" t="n">
-        <v>7211652</v>
+        <v>7212858</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9599,12 +9599,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9619,12 +9619,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9728,45 +9728,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128998133</v>
+        <v>129000115</v>
       </c>
       <c r="B84" t="n">
-        <v>80141</v>
+        <v>80169</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>583743</v>
+        <v>583856</v>
       </c>
       <c r="R84" t="n">
-        <v>7212862</v>
+        <v>7212374</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9813,44 +9813,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129000115</v>
+        <v>129000145</v>
       </c>
       <c r="B85" t="n">
-        <v>80169</v>
+        <v>57723</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>583856</v>
+        <v>583826</v>
       </c>
       <c r="R85" t="n">
-        <v>7212374</v>
+        <v>7211682</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9890,12 +9890,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9922,10 +9922,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129000145</v>
+        <v>128998133</v>
       </c>
       <c r="B86" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9933,34 +9933,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>583826</v>
+        <v>583743</v>
       </c>
       <c r="R86" t="n">
-        <v>7211682</v>
+        <v>7212862</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9987,12 +9987,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10007,12 +10007,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10420,7 +10420,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128997040</v>
+        <v>129000165</v>
       </c>
       <c r="B91" t="n">
         <v>91522</v>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>583800</v>
+        <v>583888</v>
       </c>
       <c r="R91" t="n">
-        <v>7212621</v>
+        <v>7211663</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10485,12 +10485,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10505,57 +10505,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128998130</v>
+        <v>129000116</v>
       </c>
       <c r="B92" t="n">
-        <v>80169</v>
+        <v>57720</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>583781</v>
+        <v>584099</v>
       </c>
       <c r="R92" t="n">
-        <v>7212767</v>
+        <v>7211521</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10582,12 +10582,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Spillkråkehack på låga</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10602,22 +10607,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128997035</v>
+        <v>128997040</v>
       </c>
       <c r="B93" t="n">
-        <v>57883</v>
+        <v>91522</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10625,21 +10630,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10649,10 +10654,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>583868</v>
+        <v>583800</v>
       </c>
       <c r="R93" t="n">
-        <v>7212926</v>
+        <v>7212621</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10711,45 +10716,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129000165</v>
+        <v>128998130</v>
       </c>
       <c r="B94" t="n">
-        <v>91522</v>
+        <v>80169</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>583888</v>
+        <v>583781</v>
       </c>
       <c r="R94" t="n">
-        <v>7211663</v>
+        <v>7212767</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10776,12 +10781,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10796,22 +10801,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129000116</v>
+        <v>128997035</v>
       </c>
       <c r="B95" t="n">
-        <v>57720</v>
+        <v>57883</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10819,21 +10824,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10843,10 +10848,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>584099</v>
+        <v>583868</v>
       </c>
       <c r="R95" t="n">
-        <v>7211521</v>
+        <v>7212926</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10873,17 +10878,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Spillkråkehack på låga</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10898,19 +10898,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128998146</v>
+        <v>129000175</v>
       </c>
       <c r="B96" t="n">
         <v>91544</v>
@@ -10941,14 +10941,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>583700</v>
+        <v>583975</v>
       </c>
       <c r="R96" t="n">
-        <v>7212870</v>
+        <v>7211530</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10975,12 +10975,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10995,22 +10995,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128998150</v>
+        <v>128998146</v>
       </c>
       <c r="B97" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11018,21 +11018,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11042,10 +11042,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>583862</v>
+        <v>583700</v>
       </c>
       <c r="R97" t="n">
-        <v>7212466</v>
+        <v>7212870</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11201,10 +11201,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129000175</v>
+        <v>128998150</v>
       </c>
       <c r="B99" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11212,34 +11212,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>583975</v>
+        <v>583862</v>
       </c>
       <c r="R99" t="n">
-        <v>7211530</v>
+        <v>7212466</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11266,12 +11266,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11286,44 +11286,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128998136</v>
+        <v>128998132</v>
       </c>
       <c r="B100" t="n">
-        <v>80176</v>
+        <v>57720</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11333,10 +11333,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>583838</v>
+        <v>583834</v>
       </c>
       <c r="R100" t="n">
-        <v>7212502</v>
+        <v>7212585</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11395,45 +11395,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128998132</v>
+        <v>129000150</v>
       </c>
       <c r="B101" t="n">
-        <v>57720</v>
+        <v>91896</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>583834</v>
+        <v>583951</v>
       </c>
       <c r="R101" t="n">
-        <v>7212585</v>
+        <v>7211500</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11480,44 +11480,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129000150</v>
+        <v>129000107</v>
       </c>
       <c r="B102" t="n">
-        <v>91896</v>
+        <v>92226</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1506</v>
+        <v>3298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11527,10 +11527,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>583951</v>
+        <v>583938</v>
       </c>
       <c r="R102" t="n">
-        <v>7211500</v>
+        <v>7211643</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11589,10 +11589,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129000107</v>
+        <v>128998136</v>
       </c>
       <c r="B103" t="n">
-        <v>92226</v>
+        <v>80176</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11600,34 +11600,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>583938</v>
+        <v>583838</v>
       </c>
       <c r="R103" t="n">
-        <v>7211643</v>
+        <v>7212502</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11654,12 +11654,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11674,22 +11674,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128997039</v>
+        <v>129000126</v>
       </c>
       <c r="B104" t="n">
-        <v>91522</v>
+        <v>83016</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11697,21 +11697,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11721,10 +11721,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>583807</v>
+        <v>583693</v>
       </c>
       <c r="R104" t="n">
-        <v>7212750</v>
+        <v>7211591</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11751,12 +11751,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11771,22 +11771,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129000126</v>
+        <v>128997039</v>
       </c>
       <c r="B105" t="n">
-        <v>83016</v>
+        <v>91522</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11794,21 +11794,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11818,10 +11818,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>583693</v>
+        <v>583807</v>
       </c>
       <c r="R105" t="n">
-        <v>7211591</v>
+        <v>7212750</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11848,12 +11848,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11868,12 +11868,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11982,45 +11982,53 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129000147</v>
+        <v>128998250</v>
       </c>
       <c r="B107" t="n">
-        <v>97536</v>
+        <v>57723</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>584141</v>
+        <v>583752</v>
       </c>
       <c r="R107" t="n">
-        <v>7211590</v>
+        <v>7212679</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12047,12 +12055,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12067,65 +12080,57 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128998250</v>
+        <v>129000147</v>
       </c>
       <c r="B108" t="n">
-        <v>57723</v>
+        <v>97536</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>583752</v>
+        <v>584141</v>
       </c>
       <c r="R108" t="n">
-        <v>7212679</v>
+        <v>7211590</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12152,17 +12157,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12177,57 +12177,57 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128998126</v>
+        <v>129000187</v>
       </c>
       <c r="B109" t="n">
-        <v>92226</v>
+        <v>88926</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3298</v>
+        <v>510</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>583748</v>
+        <v>583966</v>
       </c>
       <c r="R109" t="n">
-        <v>7212869</v>
+        <v>7211510</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12254,12 +12254,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12274,44 +12274,44 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128998149</v>
+        <v>128998126</v>
       </c>
       <c r="B110" t="n">
-        <v>79035</v>
+        <v>92226</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12321,10 +12321,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>584059</v>
+        <v>583748</v>
       </c>
       <c r="R110" t="n">
-        <v>7212428</v>
+        <v>7212869</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12383,10 +12383,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129000187</v>
+        <v>128998149</v>
       </c>
       <c r="B111" t="n">
-        <v>88926</v>
+        <v>79035</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12394,34 +12394,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>583966</v>
+        <v>584059</v>
       </c>
       <c r="R111" t="n">
-        <v>7211510</v>
+        <v>7212428</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12448,12 +12448,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12468,12 +12468,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -13266,45 +13266,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128998151</v>
+        <v>129000169</v>
       </c>
       <c r="B120" t="n">
-        <v>79035</v>
+        <v>82994</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>583830</v>
+        <v>583695</v>
       </c>
       <c r="R120" t="n">
-        <v>7212605</v>
+        <v>7211591</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13331,12 +13331,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13351,57 +13351,57 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129000169</v>
+        <v>128998151</v>
       </c>
       <c r="B121" t="n">
-        <v>82994</v>
+        <v>79035</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>583695</v>
+        <v>583830</v>
       </c>
       <c r="R121" t="n">
-        <v>7211591</v>
+        <v>7212605</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13428,12 +13428,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13448,12 +13448,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -14149,45 +14149,48 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129000184</v>
+        <v>129000185</v>
       </c>
       <c r="B129" t="n">
-        <v>79035</v>
+        <v>92855</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>584333</v>
+        <v>584074</v>
       </c>
       <c r="R129" t="n">
-        <v>7211688</v>
+        <v>7211675</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14228,6 +14231,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -14246,10 +14250,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129000166</v>
+        <v>129000184</v>
       </c>
       <c r="B130" t="n">
-        <v>91522</v>
+        <v>79035</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14257,21 +14261,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14281,10 +14285,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>583796</v>
+        <v>584333</v>
       </c>
       <c r="R130" t="n">
-        <v>7211546</v>
+        <v>7211688</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14343,7 +14347,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129000168</v>
+        <v>129000166</v>
       </c>
       <c r="B131" t="n">
         <v>91522</v>
@@ -14378,10 +14382,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>584331</v>
+        <v>583796</v>
       </c>
       <c r="R131" t="n">
-        <v>7211693</v>
+        <v>7211546</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14440,48 +14444,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129000185</v>
+        <v>129000168</v>
       </c>
       <c r="B132" t="n">
-        <v>92855</v>
+        <v>91522</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5964</v>
+        <v>1108</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>584074</v>
+        <v>584331</v>
       </c>
       <c r="R132" t="n">
-        <v>7211675</v>
+        <v>7211693</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14522,7 +14523,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14541,10 +14541,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129000167</v>
+        <v>129000174</v>
       </c>
       <c r="B133" t="n">
-        <v>91522</v>
+        <v>91544</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14552,21 +14552,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14576,10 +14576,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>584144</v>
+        <v>583934</v>
       </c>
       <c r="R133" t="n">
-        <v>7211566</v>
+        <v>7211520</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14740,10 +14740,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129000174</v>
+        <v>129000167</v>
       </c>
       <c r="B135" t="n">
-        <v>91544</v>
+        <v>91522</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14751,21 +14751,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14775,10 +14775,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>583934</v>
+        <v>584144</v>
       </c>
       <c r="R135" t="n">
-        <v>7211520</v>
+        <v>7211566</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15132,32 +15132,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129000128</v>
+        <v>129000136</v>
       </c>
       <c r="B139" t="n">
-        <v>91981</v>
+        <v>57723</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15167,10 +15167,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>583804</v>
+        <v>583699</v>
       </c>
       <c r="R139" t="n">
-        <v>7212351</v>
+        <v>7212348</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15203,6 +15203,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15229,32 +15234,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129000179</v>
+        <v>129000128</v>
       </c>
       <c r="B140" t="n">
-        <v>79035</v>
+        <v>91981</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15264,10 +15269,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>583976</v>
+        <v>583804</v>
       </c>
       <c r="R140" t="n">
-        <v>7212366</v>
+        <v>7212351</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15326,10 +15331,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129000136</v>
+        <v>129000179</v>
       </c>
       <c r="B141" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15337,21 +15342,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15361,10 +15366,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>583699</v>
+        <v>583976</v>
       </c>
       <c r="R141" t="n">
-        <v>7212348</v>
+        <v>7212366</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15397,11 +15402,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15631,10 +15631,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129000137</v>
+        <v>129085080</v>
       </c>
       <c r="B144" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15642,37 +15642,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>583784</v>
+        <v>583726</v>
       </c>
       <c r="R144" t="n">
-        <v>7212338</v>
+        <v>7212315</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15702,11 +15702,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15721,12 +15716,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -15823,17 +15818,17 @@
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129085080</v>
+        <v>129000137</v>
       </c>
       <c r="B146" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15841,37 +15836,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>583726</v>
+        <v>583784</v>
       </c>
       <c r="R146" t="n">
-        <v>7212315</v>
+        <v>7212338</v>
       </c>
       <c r="S146" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15901,6 +15896,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15915,22 +15915,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129000171</v>
+        <v>129085094</v>
       </c>
       <c r="B147" t="n">
-        <v>91544</v>
+        <v>91522</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15938,37 +15938,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>583882</v>
+        <v>583526</v>
       </c>
       <c r="R147" t="n">
-        <v>7212369</v>
+        <v>7212468</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16012,22 +16012,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129085094</v>
+        <v>129000159</v>
       </c>
       <c r="B148" t="n">
-        <v>91522</v>
+        <v>56904</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16035,37 +16035,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>583526</v>
+        <v>583817</v>
       </c>
       <c r="R148" t="n">
-        <v>7212468</v>
+        <v>7212328</v>
       </c>
       <c r="S148" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16109,12 +16109,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -16218,10 +16218,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129000159</v>
+        <v>129000171</v>
       </c>
       <c r="B150" t="n">
-        <v>56904</v>
+        <v>91544</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16229,21 +16229,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16253,10 +16253,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>583817</v>
+        <v>583882</v>
       </c>
       <c r="R150" t="n">
-        <v>7212328</v>
+        <v>7212369</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16315,48 +16315,48 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129000178</v>
+        <v>129085088</v>
       </c>
       <c r="B151" t="n">
-        <v>79035</v>
+        <v>97530</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>583707</v>
+        <v>583895</v>
       </c>
       <c r="R151" t="n">
-        <v>7212347</v>
+        <v>7212319</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16400,60 +16400,60 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129085088</v>
+        <v>129000178</v>
       </c>
       <c r="B152" t="n">
-        <v>97530</v>
+        <v>79035</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>583895</v>
+        <v>583707</v>
       </c>
       <c r="R152" t="n">
-        <v>7212319</v>
+        <v>7212347</v>
       </c>
       <c r="S152" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16497,12 +16497,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16606,10 +16606,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129000189</v>
+        <v>129085076</v>
       </c>
       <c r="B154" t="n">
-        <v>80175</v>
+        <v>91491</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16617,37 +16617,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>583856</v>
+        <v>583540</v>
       </c>
       <c r="R154" t="n">
-        <v>7212375</v>
+        <v>7212450</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16691,22 +16691,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129000149</v>
+        <v>129000189</v>
       </c>
       <c r="B155" t="n">
-        <v>97536</v>
+        <v>80175</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16714,21 +16714,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16738,10 +16738,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>583660</v>
+        <v>583856</v>
       </c>
       <c r="R155" t="n">
-        <v>7212365</v>
+        <v>7212375</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16800,10 +16800,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129085076</v>
+        <v>129000149</v>
       </c>
       <c r="B156" t="n">
-        <v>91491</v>
+        <v>97536</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16811,37 +16811,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>583540</v>
+        <v>583660</v>
       </c>
       <c r="R156" t="n">
-        <v>7212450</v>
+        <v>7212365</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16885,12 +16885,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -16994,32 +16994,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129000094</v>
+        <v>129000188</v>
       </c>
       <c r="B158" t="n">
-        <v>83011</v>
+        <v>80175</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17029,10 +17029,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>583585</v>
+        <v>583606</v>
       </c>
       <c r="R158" t="n">
-        <v>7212671</v>
+        <v>7212484</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17091,32 +17091,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129000188</v>
+        <v>129000094</v>
       </c>
       <c r="B159" t="n">
-        <v>80175</v>
+        <v>83011</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17126,10 +17126,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>583606</v>
+        <v>583585</v>
       </c>
       <c r="R159" t="n">
-        <v>7212484</v>
+        <v>7212671</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17285,32 +17285,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129000100</v>
+        <v>129000096</v>
       </c>
       <c r="B161" t="n">
-        <v>91491</v>
+        <v>83011</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17320,10 +17320,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>583841</v>
+        <v>583980</v>
       </c>
       <c r="R161" t="n">
-        <v>7212873</v>
+        <v>7212363</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17382,10 +17382,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129000096</v>
+        <v>129073200</v>
       </c>
       <c r="B162" t="n">
-        <v>83011</v>
+        <v>91701</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17393,21 +17393,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6440</v>
+        <v>1588</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17417,10 +17417,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>583980</v>
+        <v>583712</v>
       </c>
       <c r="R162" t="n">
-        <v>7212363</v>
+        <v>7211578</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17447,12 +17447,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17472,39 +17472,39 @@
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129073200</v>
+        <v>129000100</v>
       </c>
       <c r="B163" t="n">
-        <v>91701</v>
+        <v>91491</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1588</v>
+        <v>5447</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17514,10 +17514,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>583712</v>
+        <v>583841</v>
       </c>
       <c r="R163" t="n">
-        <v>7211578</v>
+        <v>7212873</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17544,12 +17544,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17569,7 +17569,7 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
@@ -17976,7 +17976,7 @@
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
@@ -18170,7 +18170,7 @@
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
@@ -19140,39 +19140,39 @@
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Embla Berg, Elin Kannerby, Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129000101</v>
+        <v>129073201</v>
       </c>
       <c r="B180" t="n">
-        <v>91526</v>
+        <v>92316</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1202</v>
+        <v>918</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19182,10 +19182,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>583663</v>
+        <v>583599</v>
       </c>
       <c r="R180" t="n">
-        <v>7212429</v>
+        <v>7212710</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19237,7 +19237,7 @@
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
@@ -19341,32 +19341,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129073201</v>
+        <v>129073202</v>
       </c>
       <c r="B182" t="n">
-        <v>92316</v>
+        <v>95509</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>918</v>
+        <v>2387</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19376,10 +19376,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>583599</v>
+        <v>584165</v>
       </c>
       <c r="R182" t="n">
-        <v>7212710</v>
+        <v>7211601</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19406,12 +19406,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19438,10 +19438,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129085095</v>
+        <v>129000101</v>
       </c>
       <c r="B183" t="n">
-        <v>91544</v>
+        <v>91526</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19449,37 +19449,37 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>583378</v>
+        <v>583663</v>
       </c>
       <c r="R183" t="n">
-        <v>7212728</v>
+        <v>7212429</v>
       </c>
       <c r="S183" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -19523,60 +19523,60 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129073202</v>
+        <v>129085095</v>
       </c>
       <c r="B184" t="n">
-        <v>95509</v>
+        <v>91544</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2387</v>
+        <v>5432</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>584165</v>
+        <v>583378</v>
       </c>
       <c r="R184" t="n">
-        <v>7211601</v>
+        <v>7212728</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19600,12 +19600,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19620,39 +19620,39 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129000132</v>
+        <v>129085092</v>
       </c>
       <c r="B185" t="n">
-        <v>57723</v>
+        <v>58093</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -19663,17 +19663,17 @@
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>583968</v>
+        <v>584017</v>
       </c>
       <c r="R185" t="n">
-        <v>7212362</v>
+        <v>7212353</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19703,11 +19703,6 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19722,60 +19717,60 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129085092</v>
+        <v>129000160</v>
       </c>
       <c r="B186" t="n">
-        <v>58093</v>
+        <v>91522</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>584017</v>
+        <v>583674</v>
       </c>
       <c r="R186" t="n">
-        <v>7212353</v>
+        <v>7212755</v>
       </c>
       <c r="S186" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19819,22 +19814,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129000160</v>
+        <v>129000121</v>
       </c>
       <c r="B187" t="n">
-        <v>91522</v>
+        <v>80141</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19842,21 +19837,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19866,10 +19861,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>583674</v>
+        <v>583770</v>
       </c>
       <c r="R187" t="n">
-        <v>7212755</v>
+        <v>7212825</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19928,48 +19923,48 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129000121</v>
+        <v>129085082</v>
       </c>
       <c r="B188" t="n">
-        <v>80141</v>
+        <v>80169</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>583770</v>
+        <v>583926</v>
       </c>
       <c r="R188" t="n">
-        <v>7212825</v>
+        <v>7212799</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20013,60 +20008,60 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129085082</v>
+        <v>129000132</v>
       </c>
       <c r="B189" t="n">
-        <v>80169</v>
+        <v>57723</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>583926</v>
+        <v>583968</v>
       </c>
       <c r="R189" t="n">
-        <v>7212799</v>
+        <v>7212362</v>
       </c>
       <c r="S189" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20096,6 +20091,11 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20110,12 +20110,12 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>

--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -8171,45 +8171,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128998144</v>
+        <v>129000140</v>
       </c>
       <c r="B68" t="n">
-        <v>82994</v>
+        <v>57725</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583765</v>
+        <v>584092</v>
       </c>
       <c r="R68" t="n">
-        <v>7212611</v>
+        <v>7211517</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8236,12 +8236,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8256,57 +8261,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129000140</v>
+        <v>128998144</v>
       </c>
       <c r="B69" t="n">
-        <v>57723</v>
+        <v>82998</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>584092</v>
+        <v>583765</v>
       </c>
       <c r="R69" t="n">
-        <v>7211517</v>
+        <v>7212611</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8333,17 +8338,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8358,12 +8358,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8373,7 +8373,7 @@
         <v>128998140</v>
       </c>
       <c r="B70" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>128998142</v>
       </c>
       <c r="B71" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8564,32 +8564,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129000183</v>
+        <v>128997038</v>
       </c>
       <c r="B72" t="n">
-        <v>79035</v>
+        <v>97546</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8599,10 +8599,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>584220</v>
+        <v>583850</v>
       </c>
       <c r="R72" t="n">
-        <v>7211664</v>
+        <v>7212515</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8629,12 +8629,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8649,22 +8649,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128997038</v>
+        <v>128998122</v>
       </c>
       <c r="B73" t="n">
-        <v>97536</v>
+        <v>105717</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8672,34 +8672,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583850</v>
+        <v>583934</v>
       </c>
       <c r="R73" t="n">
-        <v>7212515</v>
+        <v>7212490</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8746,57 +8746,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128998122</v>
+        <v>129000183</v>
       </c>
       <c r="B74" t="n">
-        <v>105707</v>
+        <v>79039</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583934</v>
+        <v>584220</v>
       </c>
       <c r="R74" t="n">
-        <v>7212490</v>
+        <v>7211664</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8843,12 +8843,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8858,7 +8858,7 @@
         <v>129000152</v>
       </c>
       <c r="B75" t="n">
-        <v>80168</v>
+        <v>80172</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>128998128</v>
       </c>
       <c r="B76" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9049,10 +9049,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128998124</v>
+        <v>128998131</v>
       </c>
       <c r="B77" t="n">
-        <v>91526</v>
+        <v>57722</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9060,21 +9060,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583784</v>
+        <v>584025</v>
       </c>
       <c r="R77" t="n">
-        <v>7212884</v>
+        <v>7212370</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9146,32 +9146,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128998135</v>
+        <v>128998124</v>
       </c>
       <c r="B78" t="n">
-        <v>91896</v>
+        <v>91533</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>583778</v>
+        <v>583784</v>
       </c>
       <c r="R78" t="n">
-        <v>7212890</v>
+        <v>7212884</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9243,32 +9243,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128998131</v>
+        <v>128998135</v>
       </c>
       <c r="B79" t="n">
-        <v>57720</v>
+        <v>91903</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>584025</v>
+        <v>583778</v>
       </c>
       <c r="R79" t="n">
-        <v>7212370</v>
+        <v>7212890</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
         <v>129000163</v>
       </c>
       <c r="B80" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>129000181</v>
       </c>
       <c r="B81" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>128998147</v>
       </c>
       <c r="B82" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>129000141</v>
       </c>
       <c r="B83" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>129000115</v>
       </c>
       <c r="B84" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>129000145</v>
       </c>
       <c r="B85" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>128998133</v>
       </c>
       <c r="B86" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>128998153</v>
       </c>
       <c r="B87" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>128998134</v>
       </c>
       <c r="B88" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>128998152</v>
       </c>
       <c r="B89" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>128998127</v>
       </c>
       <c r="B90" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>129000165</v>
       </c>
       <c r="B91" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>129000116</v>
       </c>
       <c r="B92" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10619,45 +10619,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128997040</v>
+        <v>128998130</v>
       </c>
       <c r="B93" t="n">
-        <v>91522</v>
+        <v>80173</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>583800</v>
+        <v>583781</v>
       </c>
       <c r="R93" t="n">
-        <v>7212621</v>
+        <v>7212767</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10704,57 +10704,57 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128998130</v>
+        <v>128997040</v>
       </c>
       <c r="B94" t="n">
-        <v>80169</v>
+        <v>91529</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>583781</v>
+        <v>583800</v>
       </c>
       <c r="R94" t="n">
-        <v>7212767</v>
+        <v>7212621</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10801,12 +10801,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10816,7 +10816,7 @@
         <v>128997035</v>
       </c>
       <c r="B95" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>129000175</v>
       </c>
       <c r="B96" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11007,32 +11007,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128998146</v>
+        <v>128998155</v>
       </c>
       <c r="B97" t="n">
-        <v>91544</v>
+        <v>80179</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11042,10 +11042,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>583700</v>
+        <v>583778</v>
       </c>
       <c r="R97" t="n">
-        <v>7212870</v>
+        <v>7212766</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11104,32 +11104,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128998155</v>
+        <v>128998146</v>
       </c>
       <c r="B98" t="n">
-        <v>80175</v>
+        <v>91551</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11139,10 +11139,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>583778</v>
+        <v>583700</v>
       </c>
       <c r="R98" t="n">
-        <v>7212766</v>
+        <v>7212870</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11204,7 +11204,7 @@
         <v>128998150</v>
       </c>
       <c r="B99" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>128998132</v>
       </c>
       <c r="B100" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11395,45 +11395,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129000150</v>
+        <v>128998136</v>
       </c>
       <c r="B101" t="n">
-        <v>91896</v>
+        <v>80180</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1506</v>
+        <v>6464</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>583951</v>
+        <v>583838</v>
       </c>
       <c r="R101" t="n">
-        <v>7211500</v>
+        <v>7212502</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11480,44 +11480,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129000107</v>
+        <v>129000150</v>
       </c>
       <c r="B102" t="n">
-        <v>92226</v>
+        <v>91903</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>3298</v>
+        <v>1506</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11527,10 +11527,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>583938</v>
+        <v>583951</v>
       </c>
       <c r="R102" t="n">
-        <v>7211643</v>
+        <v>7211500</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11589,10 +11589,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128998136</v>
+        <v>129000107</v>
       </c>
       <c r="B103" t="n">
-        <v>80176</v>
+        <v>92233</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11600,34 +11600,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>583838</v>
+        <v>583938</v>
       </c>
       <c r="R103" t="n">
-        <v>7212502</v>
+        <v>7211643</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11654,12 +11654,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11674,22 +11674,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129000126</v>
+        <v>129000130</v>
       </c>
       <c r="B104" t="n">
-        <v>83016</v>
+        <v>57725</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11697,21 +11697,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11721,10 +11721,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>583693</v>
+        <v>584350</v>
       </c>
       <c r="R104" t="n">
-        <v>7211591</v>
+        <v>7211690</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11757,6 +11757,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11783,32 +11788,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128997039</v>
+        <v>129000147</v>
       </c>
       <c r="B105" t="n">
-        <v>91522</v>
+        <v>97546</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1108</v>
+        <v>221941</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11818,10 +11823,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>583807</v>
+        <v>584141</v>
       </c>
       <c r="R105" t="n">
-        <v>7212750</v>
+        <v>7211590</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11848,12 +11853,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11868,22 +11873,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129000130</v>
+        <v>128998250</v>
       </c>
       <c r="B106" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11909,16 +11914,24 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>584350</v>
+        <v>583752</v>
       </c>
       <c r="R106" t="n">
-        <v>7211690</v>
+        <v>7212679</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11945,17 +11958,17 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Äldre och färska ringhack</t>
+          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11970,22 +11983,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128998250</v>
+        <v>128997039</v>
       </c>
       <c r="B107" t="n">
-        <v>57723</v>
+        <v>91529</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11993,42 +12006,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>583752</v>
+        <v>583807</v>
       </c>
       <c r="R107" t="n">
-        <v>7212679</v>
+        <v>7212750</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12063,11 +12068,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12080,44 +12080,44 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129000147</v>
+        <v>129000126</v>
       </c>
       <c r="B108" t="n">
-        <v>97536</v>
+        <v>83020</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221941</v>
+        <v>1467</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12127,10 +12127,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>584141</v>
+        <v>583693</v>
       </c>
       <c r="R108" t="n">
-        <v>7211590</v>
+        <v>7211591</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12189,10 +12189,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129000187</v>
+        <v>129000146</v>
       </c>
       <c r="B109" t="n">
-        <v>88926</v>
+        <v>57725</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12200,21 +12200,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12224,10 +12224,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>583966</v>
+        <v>583819</v>
       </c>
       <c r="R109" t="n">
-        <v>7211510</v>
+        <v>7211689</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12260,6 +12260,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12286,10 +12291,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128998126</v>
+        <v>129000157</v>
       </c>
       <c r="B110" t="n">
-        <v>92226</v>
+        <v>57829</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12297,34 +12302,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3298</v>
+        <v>103031</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>583748</v>
+        <v>583712</v>
       </c>
       <c r="R110" t="n">
-        <v>7212869</v>
+        <v>7211576</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12351,12 +12356,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12371,44 +12376,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128998149</v>
+        <v>128998126</v>
       </c>
       <c r="B111" t="n">
-        <v>79035</v>
+        <v>92233</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12418,10 +12423,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>584059</v>
+        <v>583748</v>
       </c>
       <c r="R111" t="n">
-        <v>7212428</v>
+        <v>7212869</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12480,10 +12485,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129000146</v>
+        <v>129000187</v>
       </c>
       <c r="B112" t="n">
-        <v>57723</v>
+        <v>88930</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12491,21 +12496,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12515,10 +12520,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>583819</v>
+        <v>583966</v>
       </c>
       <c r="R112" t="n">
-        <v>7211689</v>
+        <v>7211510</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12551,11 +12556,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12582,45 +12582,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129000157</v>
+        <v>128998149</v>
       </c>
       <c r="B113" t="n">
-        <v>57827</v>
+        <v>79039</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>583712</v>
+        <v>584059</v>
       </c>
       <c r="R113" t="n">
-        <v>7211576</v>
+        <v>7212428</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12647,12 +12647,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12667,57 +12667,57 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128998138</v>
+        <v>129000173</v>
       </c>
       <c r="B114" t="n">
-        <v>80176</v>
+        <v>91551</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>583742</v>
+        <v>583879</v>
       </c>
       <c r="R114" t="n">
-        <v>7213116</v>
+        <v>7211699</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12744,12 +12744,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12764,57 +12764,57 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129000173</v>
+        <v>128998138</v>
       </c>
       <c r="B115" t="n">
-        <v>91544</v>
+        <v>80180</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>583879</v>
+        <v>583742</v>
       </c>
       <c r="R115" t="n">
-        <v>7211699</v>
+        <v>7213116</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12841,12 +12841,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12861,44 +12861,44 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129000119</v>
+        <v>129000182</v>
       </c>
       <c r="B116" t="n">
-        <v>83009</v>
+        <v>79039</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12908,10 +12908,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>583763</v>
+        <v>584124</v>
       </c>
       <c r="R116" t="n">
-        <v>7211568</v>
+        <v>7211556</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12970,10 +12970,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129000182</v>
+        <v>129000097</v>
       </c>
       <c r="B117" t="n">
-        <v>79035</v>
+        <v>83015</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12981,21 +12981,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13005,10 +13005,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>584124</v>
+        <v>584170</v>
       </c>
       <c r="R117" t="n">
-        <v>7211556</v>
+        <v>7211600</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13067,10 +13067,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129000097</v>
+        <v>129000135</v>
       </c>
       <c r="B118" t="n">
-        <v>83011</v>
+        <v>57725</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13078,21 +13078,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13102,10 +13102,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>584170</v>
+        <v>584139</v>
       </c>
       <c r="R118" t="n">
-        <v>7211600</v>
+        <v>7211559</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13138,6 +13138,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13164,32 +13169,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129000135</v>
+        <v>129000119</v>
       </c>
       <c r="B119" t="n">
-        <v>57723</v>
+        <v>83013</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13199,10 +13204,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>584139</v>
+        <v>583763</v>
       </c>
       <c r="R119" t="n">
-        <v>7211559</v>
+        <v>7211568</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13235,11 +13240,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13269,7 +13269,7 @@
         <v>129000169</v>
       </c>
       <c r="B120" t="n">
-        <v>82994</v>
+        <v>82998</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13363,10 +13363,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128998151</v>
+        <v>129000144</v>
       </c>
       <c r="B121" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13374,34 +13374,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>583830</v>
+        <v>583832</v>
       </c>
       <c r="R121" t="n">
-        <v>7212605</v>
+        <v>7211693</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13428,12 +13428,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13448,44 +13453,44 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128998148</v>
+        <v>128998129</v>
       </c>
       <c r="B122" t="n">
-        <v>91544</v>
+        <v>80173</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13495,10 +13500,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>583764</v>
+        <v>583743</v>
       </c>
       <c r="R122" t="n">
-        <v>7212875</v>
+        <v>7212862</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13557,10 +13562,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128998129</v>
+        <v>128998154</v>
       </c>
       <c r="B123" t="n">
-        <v>80169</v>
+        <v>80179</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13568,21 +13573,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13654,27 +13659,27 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128998154</v>
+        <v>128998151</v>
       </c>
       <c r="B124" t="n">
-        <v>80175</v>
+        <v>79039</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -13689,10 +13694,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>583743</v>
+        <v>583830</v>
       </c>
       <c r="R124" t="n">
-        <v>7212862</v>
+        <v>7212605</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13751,10 +13756,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129000144</v>
+        <v>128998148</v>
       </c>
       <c r="B125" t="n">
-        <v>57723</v>
+        <v>91551</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13762,34 +13767,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>583832</v>
+        <v>583764</v>
       </c>
       <c r="R125" t="n">
-        <v>7211693</v>
+        <v>7212875</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13816,17 +13821,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13841,22 +13841,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129000142</v>
+        <v>129000180</v>
       </c>
       <c r="B126" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13864,21 +13864,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13888,10 +13888,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>583922</v>
+        <v>583695</v>
       </c>
       <c r="R126" t="n">
-        <v>7211662</v>
+        <v>7211621</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13924,11 +13924,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13955,10 +13950,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128998141</v>
+        <v>129000142</v>
       </c>
       <c r="B127" t="n">
-        <v>91522</v>
+        <v>57725</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13966,34 +13961,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>583789</v>
+        <v>583922</v>
       </c>
       <c r="R127" t="n">
-        <v>7213129</v>
+        <v>7211662</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14020,12 +14015,17 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14040,22 +14040,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129000180</v>
+        <v>128998141</v>
       </c>
       <c r="B128" t="n">
-        <v>79035</v>
+        <v>91529</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14063,34 +14063,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>583695</v>
+        <v>583789</v>
       </c>
       <c r="R128" t="n">
-        <v>7211621</v>
+        <v>7213129</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14117,12 +14117,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14137,60 +14137,57 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129000185</v>
+        <v>129000166</v>
       </c>
       <c r="B129" t="n">
-        <v>92855</v>
+        <v>91529</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5964</v>
+        <v>1108</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>584074</v>
+        <v>583796</v>
       </c>
       <c r="R129" t="n">
-        <v>7211675</v>
+        <v>7211546</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14231,7 +14228,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -14250,10 +14246,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129000184</v>
+        <v>129000168</v>
       </c>
       <c r="B130" t="n">
-        <v>79035</v>
+        <v>91529</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14261,21 +14257,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14285,10 +14281,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>584333</v>
+        <v>584331</v>
       </c>
       <c r="R130" t="n">
-        <v>7211688</v>
+        <v>7211693</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14347,10 +14343,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129000166</v>
+        <v>129000184</v>
       </c>
       <c r="B131" t="n">
-        <v>91522</v>
+        <v>79039</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14358,21 +14354,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14382,10 +14378,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>583796</v>
+        <v>584333</v>
       </c>
       <c r="R131" t="n">
-        <v>7211546</v>
+        <v>7211688</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14444,45 +14440,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129000168</v>
+        <v>129000185</v>
       </c>
       <c r="B132" t="n">
-        <v>91522</v>
+        <v>92862</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1108</v>
+        <v>5964</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>584331</v>
+        <v>584074</v>
       </c>
       <c r="R132" t="n">
-        <v>7211693</v>
+        <v>7211675</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14523,6 +14522,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14541,10 +14541,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129000174</v>
+        <v>129000138</v>
       </c>
       <c r="B133" t="n">
-        <v>91544</v>
+        <v>57725</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14552,21 +14552,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14576,10 +14576,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>583934</v>
+        <v>583805</v>
       </c>
       <c r="R133" t="n">
-        <v>7211520</v>
+        <v>7211693</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14612,6 +14612,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14638,10 +14643,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129000138</v>
+        <v>129000167</v>
       </c>
       <c r="B134" t="n">
-        <v>57723</v>
+        <v>91529</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14649,21 +14654,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14673,10 +14678,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>583805</v>
+        <v>584144</v>
       </c>
       <c r="R134" t="n">
-        <v>7211693</v>
+        <v>7211566</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14709,11 +14714,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14740,10 +14740,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129000167</v>
+        <v>129000174</v>
       </c>
       <c r="B135" t="n">
-        <v>91522</v>
+        <v>91551</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14751,21 +14751,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14775,10 +14775,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>584144</v>
+        <v>583934</v>
       </c>
       <c r="R135" t="n">
-        <v>7211566</v>
+        <v>7211520</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14840,7 +14840,7 @@
         <v>129012557</v>
       </c>
       <c r="B136" t="n">
-        <v>88926</v>
+        <v>88930</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>129012558</v>
       </c>
       <c r="B137" t="n">
-        <v>92199</v>
+        <v>92206</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>129012556</v>
       </c>
       <c r="B138" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15132,32 +15132,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129000136</v>
+        <v>129000128</v>
       </c>
       <c r="B139" t="n">
-        <v>57723</v>
+        <v>91988</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15167,10 +15167,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>583699</v>
+        <v>583804</v>
       </c>
       <c r="R139" t="n">
-        <v>7212348</v>
+        <v>7212351</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15203,11 +15203,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15234,32 +15229,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129000128</v>
+        <v>129000179</v>
       </c>
       <c r="B140" t="n">
-        <v>91981</v>
+        <v>79039</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15269,10 +15264,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>583804</v>
+        <v>583976</v>
       </c>
       <c r="R140" t="n">
-        <v>7212351</v>
+        <v>7212366</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15331,10 +15326,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129000179</v>
+        <v>129000136</v>
       </c>
       <c r="B141" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15342,21 +15337,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15366,10 +15361,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>583976</v>
+        <v>583699</v>
       </c>
       <c r="R141" t="n">
-        <v>7212366</v>
+        <v>7212348</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15402,6 +15397,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15431,7 +15431,7 @@
         <v>129085087</v>
       </c>
       <c r="B142" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>129085098</v>
       </c>
       <c r="B143" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15631,10 +15631,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129085080</v>
+        <v>129000137</v>
       </c>
       <c r="B144" t="n">
-        <v>91526</v>
+        <v>57725</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15642,37 +15642,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>583726</v>
+        <v>583784</v>
       </c>
       <c r="R144" t="n">
-        <v>7212315</v>
+        <v>7212338</v>
       </c>
       <c r="S144" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15702,6 +15702,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15716,22 +15721,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129085077</v>
+        <v>129085080</v>
       </c>
       <c r="B145" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15763,10 +15768,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>583874</v>
+        <v>583726</v>
       </c>
       <c r="R145" t="n">
-        <v>7212775</v>
+        <v>7212315</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15825,10 +15830,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129000137</v>
+        <v>129085077</v>
       </c>
       <c r="B146" t="n">
-        <v>57723</v>
+        <v>91533</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15836,37 +15841,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>583784</v>
+        <v>583874</v>
       </c>
       <c r="R146" t="n">
-        <v>7212338</v>
+        <v>7212775</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15896,11 +15901,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15915,22 +15915,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129085094</v>
+        <v>129000171</v>
       </c>
       <c r="B147" t="n">
-        <v>91522</v>
+        <v>91551</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15938,37 +15938,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>583526</v>
+        <v>583882</v>
       </c>
       <c r="R147" t="n">
-        <v>7212468</v>
+        <v>7212369</v>
       </c>
       <c r="S147" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16012,12 +16012,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
@@ -16027,7 +16027,7 @@
         <v>129000159</v>
       </c>
       <c r="B148" t="n">
-        <v>56904</v>
+        <v>56906</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16121,48 +16121,48 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129000106</v>
+        <v>129085094</v>
       </c>
       <c r="B149" t="n">
-        <v>92226</v>
+        <v>91529</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>583634</v>
+        <v>583526</v>
       </c>
       <c r="R149" t="n">
-        <v>7212397</v>
+        <v>7212468</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16206,44 +16206,44 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129000171</v>
+        <v>129000106</v>
       </c>
       <c r="B150" t="n">
-        <v>91544</v>
+        <v>92233</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16253,10 +16253,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>583882</v>
+        <v>583634</v>
       </c>
       <c r="R150" t="n">
-        <v>7212369</v>
+        <v>7212397</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16318,7 +16318,7 @@
         <v>129085088</v>
       </c>
       <c r="B151" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>129000178</v>
       </c>
       <c r="B152" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>129000103</v>
       </c>
       <c r="B153" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16606,10 +16606,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129085076</v>
+        <v>129000189</v>
       </c>
       <c r="B154" t="n">
-        <v>91491</v>
+        <v>80179</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16617,37 +16617,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>583540</v>
+        <v>583856</v>
       </c>
       <c r="R154" t="n">
-        <v>7212450</v>
+        <v>7212375</v>
       </c>
       <c r="S154" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16691,22 +16691,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129000189</v>
+        <v>129085076</v>
       </c>
       <c r="B155" t="n">
-        <v>80175</v>
+        <v>91497</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16714,37 +16714,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>583856</v>
+        <v>583540</v>
       </c>
       <c r="R155" t="n">
-        <v>7212375</v>
+        <v>7212450</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16788,12 +16788,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
@@ -16803,7 +16803,7 @@
         <v>129000149</v>
       </c>
       <c r="B156" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>129085096</v>
       </c>
       <c r="B157" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>129000188</v>
       </c>
       <c r="B158" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>129000094</v>
       </c>
       <c r="B159" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>129000110</v>
       </c>
       <c r="B160" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17285,32 +17285,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129000096</v>
+        <v>129000100</v>
       </c>
       <c r="B161" t="n">
-        <v>83011</v>
+        <v>91497</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17320,10 +17320,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>583980</v>
+        <v>583841</v>
       </c>
       <c r="R161" t="n">
-        <v>7212363</v>
+        <v>7212873</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17382,10 +17382,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129073200</v>
+        <v>129000096</v>
       </c>
       <c r="B162" t="n">
-        <v>91701</v>
+        <v>83015</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17393,21 +17393,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1588</v>
+        <v>6440</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17417,10 +17417,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>583712</v>
+        <v>583980</v>
       </c>
       <c r="R162" t="n">
-        <v>7211578</v>
+        <v>7212363</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17447,12 +17447,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17472,39 +17472,39 @@
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129000100</v>
+        <v>129073200</v>
       </c>
       <c r="B163" t="n">
-        <v>91491</v>
+        <v>91708</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5447</v>
+        <v>1588</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17514,10 +17514,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>583841</v>
+        <v>583712</v>
       </c>
       <c r="R163" t="n">
-        <v>7212873</v>
+        <v>7211578</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17544,12 +17544,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17569,7 +17569,7 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
@@ -17579,7 +17579,7 @@
         <v>129000153</v>
       </c>
       <c r="B164" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>129000177</v>
       </c>
       <c r="B165" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>129000114</v>
       </c>
       <c r="B166" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>129085074</v>
       </c>
       <c r="B167" t="n">
-        <v>105707</v>
+        <v>105717</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>129085075</v>
       </c>
       <c r="B168" t="n">
-        <v>105707</v>
+        <v>105717</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>129085078</v>
       </c>
       <c r="B169" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>129000104</v>
       </c>
       <c r="B170" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18274,10 +18274,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129000170</v>
+        <v>129085099</v>
       </c>
       <c r="B171" t="n">
-        <v>91540</v>
+        <v>79039</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18285,37 +18285,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>583844</v>
+        <v>583975</v>
       </c>
       <c r="R171" t="n">
-        <v>7212348</v>
+        <v>7212333</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18359,22 +18359,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129000122</v>
+        <v>129000170</v>
       </c>
       <c r="B172" t="n">
-        <v>80141</v>
+        <v>91547</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18382,21 +18382,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18406,10 +18406,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>583833</v>
+        <v>583844</v>
       </c>
       <c r="R172" t="n">
-        <v>7212856</v>
+        <v>7212348</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18468,10 +18468,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129085099</v>
+        <v>129000122</v>
       </c>
       <c r="B173" t="n">
-        <v>79035</v>
+        <v>80145</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18479,37 +18479,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>583975</v>
+        <v>583833</v>
       </c>
       <c r="R173" t="n">
-        <v>7212333</v>
+        <v>7212856</v>
       </c>
       <c r="S173" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18553,12 +18553,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -18568,7 +18568,7 @@
         <v>129000176</v>
       </c>
       <c r="B174" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18662,10 +18662,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129000124</v>
+        <v>129085097</v>
       </c>
       <c r="B175" t="n">
-        <v>83016</v>
+        <v>79039</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18673,37 +18673,37 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>583770</v>
+        <v>583788</v>
       </c>
       <c r="R175" t="n">
-        <v>7212830</v>
+        <v>7212781</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18747,60 +18747,60 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129000172</v>
+        <v>129085083</v>
       </c>
       <c r="B176" t="n">
-        <v>91544</v>
+        <v>80173</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>583719</v>
+        <v>583520</v>
       </c>
       <c r="R176" t="n">
-        <v>7212791</v>
+        <v>7212517</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -18844,22 +18844,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129085097</v>
+        <v>129000124</v>
       </c>
       <c r="B177" t="n">
-        <v>79035</v>
+        <v>83020</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18867,37 +18867,37 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>583788</v>
+        <v>583770</v>
       </c>
       <c r="R177" t="n">
-        <v>7212781</v>
+        <v>7212830</v>
       </c>
       <c r="S177" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -18941,60 +18941,60 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129085083</v>
+        <v>129000172</v>
       </c>
       <c r="B178" t="n">
-        <v>80169</v>
+        <v>91551</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>583520</v>
+        <v>583719</v>
       </c>
       <c r="R178" t="n">
-        <v>7212517</v>
+        <v>7212791</v>
       </c>
       <c r="S178" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19038,12 +19038,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
@@ -19053,7 +19053,7 @@
         <v>129085079</v>
       </c>
       <c r="B179" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19147,32 +19147,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129073201</v>
+        <v>129000129</v>
       </c>
       <c r="B180" t="n">
-        <v>92316</v>
+        <v>91818</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>918</v>
+        <v>658</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19182,10 +19182,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>583599</v>
+        <v>583810</v>
       </c>
       <c r="R180" t="n">
-        <v>7212710</v>
+        <v>7212852</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19237,39 +19237,39 @@
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129000129</v>
+        <v>129073201</v>
       </c>
       <c r="B181" t="n">
-        <v>91811</v>
+        <v>92323</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>658</v>
+        <v>918</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19279,10 +19279,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>583810</v>
+        <v>583599</v>
       </c>
       <c r="R181" t="n">
-        <v>7212852</v>
+        <v>7212710</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19334,55 +19334,55 @@
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129073202</v>
+        <v>129085095</v>
       </c>
       <c r="B182" t="n">
-        <v>95509</v>
+        <v>91551</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2387</v>
+        <v>5432</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>584165</v>
+        <v>583378</v>
       </c>
       <c r="R182" t="n">
-        <v>7211601</v>
+        <v>7212728</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19406,12 +19406,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19426,12 +19426,12 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
@@ -19441,7 +19441,7 @@
         <v>129000101</v>
       </c>
       <c r="B183" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19535,48 +19535,48 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129085095</v>
+        <v>129073202</v>
       </c>
       <c r="B184" t="n">
-        <v>91544</v>
+        <v>95519</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5432</v>
+        <v>2387</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>583378</v>
+        <v>584165</v>
       </c>
       <c r="R184" t="n">
-        <v>7212728</v>
+        <v>7211601</v>
       </c>
       <c r="S184" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19600,12 +19600,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19620,22 +19620,22 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129085092</v>
+        <v>129085082</v>
       </c>
       <c r="B185" t="n">
-        <v>58093</v>
+        <v>80173</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19643,21 +19643,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19667,10 +19667,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>584017</v>
+        <v>583926</v>
       </c>
       <c r="R185" t="n">
-        <v>7212353</v>
+        <v>7212799</v>
       </c>
       <c r="S185" t="n">
         <v>15</v>
@@ -19722,17 +19722,17 @@
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129000160</v>
+        <v>129000121</v>
       </c>
       <c r="B186" t="n">
-        <v>91522</v>
+        <v>80145</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19740,21 +19740,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19764,10 +19764,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>583674</v>
+        <v>583770</v>
       </c>
       <c r="R186" t="n">
-        <v>7212755</v>
+        <v>7212825</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19826,10 +19826,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129000121</v>
+        <v>129000160</v>
       </c>
       <c r="B187" t="n">
-        <v>80141</v>
+        <v>91529</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19837,21 +19837,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19861,10 +19861,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>583770</v>
+        <v>583674</v>
       </c>
       <c r="R187" t="n">
-        <v>7212825</v>
+        <v>7212755</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19923,48 +19923,48 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129085082</v>
+        <v>129000132</v>
       </c>
       <c r="B188" t="n">
-        <v>80169</v>
+        <v>57725</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>583926</v>
+        <v>583968</v>
       </c>
       <c r="R188" t="n">
-        <v>7212799</v>
+        <v>7212362</v>
       </c>
       <c r="S188" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19994,6 +19994,11 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20008,22 +20013,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129000132</v>
+        <v>129085086</v>
       </c>
       <c r="B189" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20049,19 +20054,23 @@
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>583968</v>
+        <v>583569</v>
       </c>
       <c r="R189" t="n">
-        <v>7212362</v>
+        <v>7212757</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20095,7 +20104,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20110,39 +20119,39 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129085086</v>
+        <v>129085092</v>
       </c>
       <c r="B190" t="n">
-        <v>57723</v>
+        <v>58095</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -20151,20 +20160,16 @@
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>583569</v>
+        <v>584017</v>
       </c>
       <c r="R190" t="n">
-        <v>7212757</v>
+        <v>7212353</v>
       </c>
       <c r="S190" t="n">
         <v>15</v>
@@ -20199,11 +20204,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD190" t="b">
         <v>0</v>
       </c>
@@ -20221,39 +20221,39 @@
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129000162</v>
+        <v>129000154</v>
       </c>
       <c r="B191" t="n">
-        <v>91522</v>
+        <v>80180</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20263,10 +20263,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>583583</v>
+        <v>583832</v>
       </c>
       <c r="R191" t="n">
-        <v>7212676</v>
+        <v>7212853</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20325,32 +20325,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129000154</v>
+        <v>129000162</v>
       </c>
       <c r="B192" t="n">
-        <v>80176</v>
+        <v>91529</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20360,10 +20360,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>583832</v>
+        <v>583583</v>
       </c>
       <c r="R192" t="n">
-        <v>7212853</v>
+        <v>7212676</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>

--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -8467,10 +8467,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128998142</v>
+        <v>129000183</v>
       </c>
       <c r="B71" t="n">
-        <v>91529</v>
+        <v>79039</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8478,34 +8478,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>583800</v>
+        <v>584220</v>
       </c>
       <c r="R71" t="n">
-        <v>7212769</v>
+        <v>7211664</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8532,12 +8532,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8552,57 +8552,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128997038</v>
+        <v>128998142</v>
       </c>
       <c r="B72" t="n">
-        <v>97546</v>
+        <v>91529</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221941</v>
+        <v>1108</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583850</v>
+        <v>583800</v>
       </c>
       <c r="R72" t="n">
-        <v>7212515</v>
+        <v>7212769</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8649,22 +8649,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128998122</v>
+        <v>128997038</v>
       </c>
       <c r="B73" t="n">
-        <v>105717</v>
+        <v>97546</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8672,34 +8672,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221725</v>
+        <v>221941</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583934</v>
+        <v>583850</v>
       </c>
       <c r="R73" t="n">
-        <v>7212490</v>
+        <v>7212515</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8746,57 +8746,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129000183</v>
+        <v>128998122</v>
       </c>
       <c r="B74" t="n">
-        <v>79039</v>
+        <v>105717</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>584220</v>
+        <v>583934</v>
       </c>
       <c r="R74" t="n">
-        <v>7211664</v>
+        <v>7212490</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8843,12 +8843,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -11298,45 +11298,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128998132</v>
+        <v>129000150</v>
       </c>
       <c r="B100" t="n">
-        <v>57722</v>
+        <v>91903</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>583834</v>
+        <v>583951</v>
       </c>
       <c r="R100" t="n">
-        <v>7212585</v>
+        <v>7211500</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11363,12 +11363,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11383,22 +11383,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128998136</v>
+        <v>129000107</v>
       </c>
       <c r="B101" t="n">
-        <v>80180</v>
+        <v>92233</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11406,34 +11406,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>583838</v>
+        <v>583938</v>
       </c>
       <c r="R101" t="n">
-        <v>7212502</v>
+        <v>7211643</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11480,57 +11480,57 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129000150</v>
+        <v>128998136</v>
       </c>
       <c r="B102" t="n">
-        <v>91903</v>
+        <v>80180</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1506</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>583951</v>
+        <v>583838</v>
       </c>
       <c r="R102" t="n">
-        <v>7211500</v>
+        <v>7212502</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11557,12 +11557,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11577,57 +11577,57 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129000107</v>
+        <v>128998132</v>
       </c>
       <c r="B103" t="n">
-        <v>92233</v>
+        <v>57722</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>583938</v>
+        <v>583834</v>
       </c>
       <c r="R103" t="n">
-        <v>7211643</v>
+        <v>7212585</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11654,12 +11654,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11674,44 +11674,44 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129000130</v>
+        <v>129000147</v>
       </c>
       <c r="B104" t="n">
-        <v>57725</v>
+        <v>97546</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11721,10 +11721,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>584350</v>
+        <v>584141</v>
       </c>
       <c r="R104" t="n">
-        <v>7211690</v>
+        <v>7211590</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11757,11 +11757,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11788,45 +11783,53 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129000147</v>
+        <v>128998250</v>
       </c>
       <c r="B105" t="n">
-        <v>97546</v>
+        <v>57725</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>584141</v>
+        <v>583752</v>
       </c>
       <c r="R105" t="n">
-        <v>7211590</v>
+        <v>7212679</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11853,12 +11856,17 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11873,22 +11881,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128998250</v>
+        <v>129000126</v>
       </c>
       <c r="B106" t="n">
-        <v>57725</v>
+        <v>83020</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11896,42 +11904,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>583752</v>
+        <v>583693</v>
       </c>
       <c r="R106" t="n">
-        <v>7212679</v>
+        <v>7211591</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11958,17 +11958,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11983,22 +11978,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128997039</v>
+        <v>129000130</v>
       </c>
       <c r="B107" t="n">
-        <v>91529</v>
+        <v>57725</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12006,21 +12001,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12030,10 +12025,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>583807</v>
+        <v>584350</v>
       </c>
       <c r="R107" t="n">
-        <v>7212750</v>
+        <v>7211690</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12060,12 +12055,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12080,22 +12080,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129000126</v>
+        <v>128997039</v>
       </c>
       <c r="B108" t="n">
-        <v>83020</v>
+        <v>91529</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12103,21 +12103,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12127,10 +12127,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>583693</v>
+        <v>583807</v>
       </c>
       <c r="R108" t="n">
-        <v>7211591</v>
+        <v>7212750</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12157,12 +12157,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12177,12 +12177,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -12291,32 +12291,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129000157</v>
+        <v>129000187</v>
       </c>
       <c r="B110" t="n">
-        <v>57829</v>
+        <v>88930</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103031</v>
+        <v>510</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12326,10 +12326,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>583712</v>
+        <v>583966</v>
       </c>
       <c r="R110" t="n">
-        <v>7211576</v>
+        <v>7211510</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12388,32 +12388,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128998126</v>
+        <v>128998149</v>
       </c>
       <c r="B111" t="n">
-        <v>92233</v>
+        <v>79039</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12423,10 +12423,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>583748</v>
+        <v>584059</v>
       </c>
       <c r="R111" t="n">
-        <v>7212869</v>
+        <v>7212428</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12485,45 +12485,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129000187</v>
+        <v>128998126</v>
       </c>
       <c r="B112" t="n">
-        <v>88930</v>
+        <v>92233</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>510</v>
+        <v>3298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>583966</v>
+        <v>583748</v>
       </c>
       <c r="R112" t="n">
-        <v>7211510</v>
+        <v>7212869</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12550,12 +12550,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12570,57 +12570,57 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128998149</v>
+        <v>129000157</v>
       </c>
       <c r="B113" t="n">
-        <v>79039</v>
+        <v>57829</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>584059</v>
+        <v>583712</v>
       </c>
       <c r="R113" t="n">
-        <v>7212428</v>
+        <v>7211576</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12647,12 +12647,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12667,12 +12667,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -12873,32 +12873,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129000182</v>
+        <v>129000119</v>
       </c>
       <c r="B116" t="n">
-        <v>79039</v>
+        <v>83013</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12908,10 +12908,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>584124</v>
+        <v>583763</v>
       </c>
       <c r="R116" t="n">
-        <v>7211556</v>
+        <v>7211568</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12970,10 +12970,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129000097</v>
+        <v>129000182</v>
       </c>
       <c r="B117" t="n">
-        <v>83015</v>
+        <v>79039</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12981,21 +12981,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13005,10 +13005,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>584170</v>
+        <v>584124</v>
       </c>
       <c r="R117" t="n">
-        <v>7211600</v>
+        <v>7211556</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13067,10 +13067,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129000135</v>
+        <v>129000097</v>
       </c>
       <c r="B118" t="n">
-        <v>57725</v>
+        <v>83015</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13078,21 +13078,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13102,10 +13102,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>584139</v>
+        <v>584170</v>
       </c>
       <c r="R118" t="n">
-        <v>7211559</v>
+        <v>7211600</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13138,11 +13138,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13169,32 +13164,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129000119</v>
+        <v>129000135</v>
       </c>
       <c r="B119" t="n">
-        <v>83013</v>
+        <v>57725</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13204,10 +13199,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>583763</v>
+        <v>584139</v>
       </c>
       <c r="R119" t="n">
-        <v>7211568</v>
+        <v>7211559</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13240,6 +13235,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -16315,48 +16315,48 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129085088</v>
+        <v>129000178</v>
       </c>
       <c r="B151" t="n">
-        <v>97540</v>
+        <v>79039</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>583895</v>
+        <v>583707</v>
       </c>
       <c r="R151" t="n">
-        <v>7212319</v>
+        <v>7212347</v>
       </c>
       <c r="S151" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16400,60 +16400,60 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129000178</v>
+        <v>129085088</v>
       </c>
       <c r="B152" t="n">
-        <v>79039</v>
+        <v>97540</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>583707</v>
+        <v>583895</v>
       </c>
       <c r="R152" t="n">
-        <v>7212347</v>
+        <v>7212319</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16497,12 +16497,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -18080,7 +18080,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129085078</v>
+        <v>129000104</v>
       </c>
       <c r="B169" t="n">
         <v>91533</v>
@@ -18111,17 +18111,17 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>583677</v>
+        <v>584023</v>
       </c>
       <c r="R169" t="n">
-        <v>7212815</v>
+        <v>7212353</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18165,19 +18165,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129000104</v>
+        <v>129085078</v>
       </c>
       <c r="B170" t="n">
         <v>91533</v>
@@ -18208,17 +18208,17 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>584023</v>
+        <v>583677</v>
       </c>
       <c r="R170" t="n">
-        <v>7212353</v>
+        <v>7212815</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18262,12 +18262,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -20228,32 +20228,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129000154</v>
+        <v>129000162</v>
       </c>
       <c r="B191" t="n">
-        <v>80180</v>
+        <v>91529</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20263,10 +20263,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>583832</v>
+        <v>583583</v>
       </c>
       <c r="R191" t="n">
-        <v>7212853</v>
+        <v>7212676</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20325,32 +20325,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129000162</v>
+        <v>129000154</v>
       </c>
       <c r="B192" t="n">
-        <v>91529</v>
+        <v>80180</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20360,10 +20360,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>583583</v>
+        <v>583832</v>
       </c>
       <c r="R192" t="n">
-        <v>7212676</v>
+        <v>7212853</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>

--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -8171,10 +8171,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129000140</v>
+        <v>128998140</v>
       </c>
       <c r="B68" t="n">
-        <v>57725</v>
+        <v>91536</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8182,34 +8182,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>584092</v>
+        <v>583855</v>
       </c>
       <c r="R68" t="n">
-        <v>7211517</v>
+        <v>7213081</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8236,17 +8236,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8261,12 +8256,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8276,7 +8271,7 @@
         <v>128998144</v>
       </c>
       <c r="B69" t="n">
-        <v>82998</v>
+        <v>82988</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8370,10 +8365,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128998140</v>
+        <v>129000140</v>
       </c>
       <c r="B70" t="n">
-        <v>91529</v>
+        <v>57725</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8381,34 +8376,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583855</v>
+        <v>584092</v>
       </c>
       <c r="R70" t="n">
-        <v>7213081</v>
+        <v>7211517</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8435,12 +8430,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8455,12 +8455,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8567,7 +8567,7 @@
         <v>128998142</v>
       </c>
       <c r="B72" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>128997038</v>
       </c>
       <c r="B73" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>128998122</v>
       </c>
       <c r="B74" t="n">
-        <v>105717</v>
+        <v>105724</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8855,45 +8855,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129000152</v>
+        <v>128998128</v>
       </c>
       <c r="B75" t="n">
-        <v>80172</v>
+        <v>57885</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>584338</v>
+        <v>583799</v>
       </c>
       <c r="R75" t="n">
-        <v>7211689</v>
+        <v>7212748</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8940,57 +8940,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128998128</v>
+        <v>129000152</v>
       </c>
       <c r="B76" t="n">
-        <v>57885</v>
+        <v>80172</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583799</v>
+        <v>584338</v>
       </c>
       <c r="R76" t="n">
-        <v>7212748</v>
+        <v>7211689</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9017,12 +9017,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9037,12 +9037,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9146,32 +9146,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128998124</v>
+        <v>128998135</v>
       </c>
       <c r="B78" t="n">
-        <v>91533</v>
+        <v>91910</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>1506</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>583784</v>
+        <v>583778</v>
       </c>
       <c r="R78" t="n">
-        <v>7212884</v>
+        <v>7212890</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9243,32 +9243,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128998135</v>
+        <v>128998124</v>
       </c>
       <c r="B79" t="n">
-        <v>91903</v>
+        <v>91540</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583778</v>
+        <v>583784</v>
       </c>
       <c r="R79" t="n">
-        <v>7212890</v>
+        <v>7212884</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9343,7 +9343,7 @@
         <v>129000163</v>
       </c>
       <c r="B80" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>128998147</v>
       </c>
       <c r="B82" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>129000141</v>
       </c>
       <c r="B83" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9728,10 +9728,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129000115</v>
+        <v>128998153</v>
       </c>
       <c r="B84" t="n">
-        <v>80173</v>
+        <v>80179</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9739,34 +9739,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>583856</v>
+        <v>583842</v>
       </c>
       <c r="R84" t="n">
-        <v>7212374</v>
+        <v>7212492</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9813,12 +9813,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9922,45 +9922,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128998133</v>
+        <v>129000115</v>
       </c>
       <c r="B86" t="n">
-        <v>80145</v>
+        <v>80173</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>583743</v>
+        <v>583856</v>
       </c>
       <c r="R86" t="n">
-        <v>7212862</v>
+        <v>7212374</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10007,44 +10007,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128998153</v>
+        <v>128998133</v>
       </c>
       <c r="B87" t="n">
-        <v>80179</v>
+        <v>80145</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10054,10 +10054,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>583842</v>
+        <v>583743</v>
       </c>
       <c r="R87" t="n">
-        <v>7212492</v>
+        <v>7212862</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10119,7 +10119,7 @@
         <v>128998134</v>
       </c>
       <c r="B88" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128998152</v>
+        <v>128998127</v>
       </c>
       <c r="B89" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10224,34 +10224,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>583744</v>
+        <v>583792</v>
       </c>
       <c r="R89" t="n">
-        <v>7212703</v>
+        <v>7212761</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10284,6 +10292,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färskt bohål som sannolikt är från tretåig hackspett pga storleken på bohålet (ca 5 cm)</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10310,10 +10323,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128998127</v>
+        <v>128998152</v>
       </c>
       <c r="B90" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10321,42 +10334,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>583792</v>
+        <v>583744</v>
       </c>
       <c r="R90" t="n">
-        <v>7212761</v>
+        <v>7212703</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10389,11 +10394,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Färskt bohål som sannolikt är från tretåig hackspett pga storleken på bohålet (ca 5 cm)</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10420,10 +10420,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129000165</v>
+        <v>128997040</v>
       </c>
       <c r="B91" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>583888</v>
+        <v>583800</v>
       </c>
       <c r="R91" t="n">
-        <v>7211663</v>
+        <v>7212621</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10485,12 +10485,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10505,57 +10505,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129000116</v>
+        <v>128998130</v>
       </c>
       <c r="B92" t="n">
-        <v>57722</v>
+        <v>80173</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>584099</v>
+        <v>583781</v>
       </c>
       <c r="R92" t="n">
-        <v>7211521</v>
+        <v>7212767</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10582,17 +10582,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Spillkråkehack på låga</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10607,57 +10602,57 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128998130</v>
+        <v>129000165</v>
       </c>
       <c r="B93" t="n">
-        <v>80173</v>
+        <v>91536</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>583781</v>
+        <v>583888</v>
       </c>
       <c r="R93" t="n">
-        <v>7212767</v>
+        <v>7211663</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10684,12 +10679,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10704,22 +10699,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128997040</v>
+        <v>129000116</v>
       </c>
       <c r="B94" t="n">
-        <v>91529</v>
+        <v>57722</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10727,21 +10722,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10751,10 +10746,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>583800</v>
+        <v>584099</v>
       </c>
       <c r="R94" t="n">
-        <v>7212621</v>
+        <v>7211521</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10781,12 +10776,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Spillkråkehack på låga</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10801,12 +10801,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10913,7 +10913,7 @@
         <v>129000175</v>
       </c>
       <c r="B96" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>128998146</v>
       </c>
       <c r="B98" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11298,32 +11298,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129000150</v>
+        <v>129000107</v>
       </c>
       <c r="B100" t="n">
-        <v>91903</v>
+        <v>92240</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1506</v>
+        <v>3298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11333,10 +11333,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>583951</v>
+        <v>583938</v>
       </c>
       <c r="R100" t="n">
-        <v>7211500</v>
+        <v>7211643</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11395,45 +11395,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129000107</v>
+        <v>128998132</v>
       </c>
       <c r="B101" t="n">
-        <v>92233</v>
+        <v>57722</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>583938</v>
+        <v>583834</v>
       </c>
       <c r="R101" t="n">
-        <v>7211643</v>
+        <v>7212585</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11480,12 +11480,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -11589,45 +11589,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128998132</v>
+        <v>129000150</v>
       </c>
       <c r="B103" t="n">
-        <v>57722</v>
+        <v>91910</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>583834</v>
+        <v>583951</v>
       </c>
       <c r="R103" t="n">
-        <v>7212585</v>
+        <v>7211500</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11654,12 +11654,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11674,44 +11674,44 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129000147</v>
+        <v>129000126</v>
       </c>
       <c r="B104" t="n">
-        <v>97546</v>
+        <v>83010</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221941</v>
+        <v>1467</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11721,10 +11721,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>584141</v>
+        <v>583693</v>
       </c>
       <c r="R104" t="n">
-        <v>7211590</v>
+        <v>7211591</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11783,7 +11783,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128998250</v>
+        <v>129000130</v>
       </c>
       <c r="B105" t="n">
         <v>57725</v>
@@ -11812,24 +11812,16 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>583752</v>
+        <v>584350</v>
       </c>
       <c r="R105" t="n">
-        <v>7212679</v>
+        <v>7211690</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11856,17 +11848,17 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
+          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11881,44 +11873,44 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129000126</v>
+        <v>129000147</v>
       </c>
       <c r="B106" t="n">
-        <v>83020</v>
+        <v>97553</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1467</v>
+        <v>221941</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11928,10 +11920,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>583693</v>
+        <v>584141</v>
       </c>
       <c r="R106" t="n">
-        <v>7211591</v>
+        <v>7211590</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11990,10 +11982,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129000130</v>
+        <v>128997039</v>
       </c>
       <c r="B107" t="n">
-        <v>57725</v>
+        <v>91536</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12001,21 +11993,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12025,10 +12017,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>584350</v>
+        <v>583807</v>
       </c>
       <c r="R107" t="n">
-        <v>7211690</v>
+        <v>7212750</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12055,17 +12047,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Äldre och färska ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12080,22 +12067,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128997039</v>
+        <v>128998250</v>
       </c>
       <c r="B108" t="n">
-        <v>91529</v>
+        <v>57725</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12103,34 +12090,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>583807</v>
+        <v>583752</v>
       </c>
       <c r="R108" t="n">
-        <v>7212750</v>
+        <v>7212679</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12165,6 +12160,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -12177,39 +12177,39 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129000146</v>
+        <v>129000157</v>
       </c>
       <c r="B109" t="n">
-        <v>57725</v>
+        <v>57829</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -12224,10 +12224,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>583819</v>
+        <v>583712</v>
       </c>
       <c r="R109" t="n">
-        <v>7211689</v>
+        <v>7211576</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12260,11 +12260,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12294,7 +12289,7 @@
         <v>129000187</v>
       </c>
       <c r="B110" t="n">
-        <v>88930</v>
+        <v>88937</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12388,10 +12383,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128998149</v>
+        <v>129000146</v>
       </c>
       <c r="B111" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12399,34 +12394,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>584059</v>
+        <v>583819</v>
       </c>
       <c r="R111" t="n">
-        <v>7212428</v>
+        <v>7211689</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12453,12 +12448,17 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12473,12 +12473,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -12488,7 +12488,7 @@
         <v>128998126</v>
       </c>
       <c r="B112" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12582,45 +12582,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129000157</v>
+        <v>128998149</v>
       </c>
       <c r="B113" t="n">
-        <v>57829</v>
+        <v>79039</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>583712</v>
+        <v>584059</v>
       </c>
       <c r="R113" t="n">
-        <v>7211576</v>
+        <v>7212428</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12647,12 +12647,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12667,57 +12667,57 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129000173</v>
+        <v>128998138</v>
       </c>
       <c r="B114" t="n">
-        <v>91551</v>
+        <v>80180</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>583879</v>
+        <v>583742</v>
       </c>
       <c r="R114" t="n">
-        <v>7211699</v>
+        <v>7213116</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12744,12 +12744,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12764,57 +12764,57 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128998138</v>
+        <v>129000173</v>
       </c>
       <c r="B115" t="n">
-        <v>80180</v>
+        <v>91558</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>583742</v>
+        <v>583879</v>
       </c>
       <c r="R115" t="n">
-        <v>7213116</v>
+        <v>7211699</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12841,12 +12841,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12861,44 +12861,44 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129000119</v>
+        <v>129000182</v>
       </c>
       <c r="B116" t="n">
-        <v>83013</v>
+        <v>79039</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12908,10 +12908,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>583763</v>
+        <v>584124</v>
       </c>
       <c r="R116" t="n">
-        <v>7211568</v>
+        <v>7211556</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12970,10 +12970,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129000182</v>
+        <v>129000097</v>
       </c>
       <c r="B117" t="n">
-        <v>79039</v>
+        <v>83005</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12981,21 +12981,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13005,10 +13005,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>584124</v>
+        <v>584170</v>
       </c>
       <c r="R117" t="n">
-        <v>7211556</v>
+        <v>7211600</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13067,32 +13067,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129000097</v>
+        <v>129000119</v>
       </c>
       <c r="B118" t="n">
-        <v>83015</v>
+        <v>83003</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6440</v>
+        <v>6486</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13102,10 +13102,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>584170</v>
+        <v>583763</v>
       </c>
       <c r="R118" t="n">
-        <v>7211600</v>
+        <v>7211568</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13269,7 +13269,7 @@
         <v>129000169</v>
       </c>
       <c r="B120" t="n">
-        <v>82998</v>
+        <v>82988</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13465,32 +13465,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128998129</v>
+        <v>128998148</v>
       </c>
       <c r="B122" t="n">
-        <v>80173</v>
+        <v>91558</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>583743</v>
+        <v>583764</v>
       </c>
       <c r="R122" t="n">
-        <v>7212862</v>
+        <v>7212875</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13562,27 +13562,27 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128998154</v>
+        <v>128998151</v>
       </c>
       <c r="B123" t="n">
-        <v>80179</v>
+        <v>79039</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13597,10 +13597,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>583743</v>
+        <v>583830</v>
       </c>
       <c r="R123" t="n">
-        <v>7212862</v>
+        <v>7212605</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13659,32 +13659,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128998151</v>
+        <v>128998129</v>
       </c>
       <c r="B124" t="n">
-        <v>79039</v>
+        <v>80173</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13694,10 +13694,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>583830</v>
+        <v>583743</v>
       </c>
       <c r="R124" t="n">
-        <v>7212605</v>
+        <v>7212862</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13756,32 +13756,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128998148</v>
+        <v>128998154</v>
       </c>
       <c r="B125" t="n">
-        <v>91551</v>
+        <v>80179</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13791,10 +13791,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>583764</v>
+        <v>583743</v>
       </c>
       <c r="R125" t="n">
-        <v>7212875</v>
+        <v>7212862</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14055,7 +14055,7 @@
         <v>128998141</v>
       </c>
       <c r="B128" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14149,10 +14149,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129000166</v>
+        <v>129000168</v>
       </c>
       <c r="B129" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14184,10 +14184,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>583796</v>
+        <v>584331</v>
       </c>
       <c r="R129" t="n">
-        <v>7211546</v>
+        <v>7211693</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14246,10 +14246,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129000168</v>
+        <v>129000166</v>
       </c>
       <c r="B130" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>584331</v>
+        <v>583796</v>
       </c>
       <c r="R130" t="n">
-        <v>7211693</v>
+        <v>7211546</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14443,7 +14443,7 @@
         <v>129000185</v>
       </c>
       <c r="B132" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14541,10 +14541,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129000138</v>
+        <v>129000167</v>
       </c>
       <c r="B133" t="n">
-        <v>57725</v>
+        <v>91536</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14552,21 +14552,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14576,10 +14576,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>583805</v>
+        <v>584144</v>
       </c>
       <c r="R133" t="n">
-        <v>7211693</v>
+        <v>7211566</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14612,11 +14612,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14643,10 +14638,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129000167</v>
+        <v>129000138</v>
       </c>
       <c r="B134" t="n">
-        <v>91529</v>
+        <v>57725</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14654,21 +14649,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14678,10 +14673,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>584144</v>
+        <v>583805</v>
       </c>
       <c r="R134" t="n">
-        <v>7211566</v>
+        <v>7211693</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14714,6 +14709,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14743,7 +14743,7 @@
         <v>129000174</v>
       </c>
       <c r="B135" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>129012557</v>
       </c>
       <c r="B136" t="n">
-        <v>88930</v>
+        <v>88937</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>129012558</v>
       </c>
       <c r="B137" t="n">
-        <v>92206</v>
+        <v>92213</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>129012556</v>
       </c>
       <c r="B138" t="n">
-        <v>91892</v>
+        <v>91899</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>129000128</v>
       </c>
       <c r="B139" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15733,10 +15733,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129085080</v>
+        <v>129085077</v>
       </c>
       <c r="B145" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>583726</v>
+        <v>583874</v>
       </c>
       <c r="R145" t="n">
-        <v>7212315</v>
+        <v>7212775</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15830,10 +15830,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129085077</v>
+        <v>129085080</v>
       </c>
       <c r="B146" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15865,10 +15865,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>583874</v>
+        <v>583726</v>
       </c>
       <c r="R146" t="n">
-        <v>7212775</v>
+        <v>7212315</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -15927,10 +15927,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129000171</v>
+        <v>129085094</v>
       </c>
       <c r="B147" t="n">
-        <v>91551</v>
+        <v>91536</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15938,37 +15938,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>583882</v>
+        <v>583526</v>
       </c>
       <c r="R147" t="n">
-        <v>7212369</v>
+        <v>7212468</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16012,22 +16012,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129000159</v>
+        <v>129000171</v>
       </c>
       <c r="B148" t="n">
-        <v>56906</v>
+        <v>91558</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16035,21 +16035,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16059,10 +16059,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>583817</v>
+        <v>583882</v>
       </c>
       <c r="R148" t="n">
-        <v>7212328</v>
+        <v>7212369</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16121,10 +16121,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129085094</v>
+        <v>129000159</v>
       </c>
       <c r="B149" t="n">
-        <v>91529</v>
+        <v>56906</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16132,37 +16132,37 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>583526</v>
+        <v>583817</v>
       </c>
       <c r="R149" t="n">
-        <v>7212468</v>
+        <v>7212328</v>
       </c>
       <c r="S149" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16206,12 +16206,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
@@ -16221,7 +16221,7 @@
         <v>129000106</v>
       </c>
       <c r="B150" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>129085088</v>
       </c>
       <c r="B152" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>129000103</v>
       </c>
       <c r="B153" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16703,10 +16703,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129085076</v>
+        <v>129000149</v>
       </c>
       <c r="B155" t="n">
-        <v>91497</v>
+        <v>97553</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16714,37 +16714,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>583540</v>
+        <v>583660</v>
       </c>
       <c r="R155" t="n">
-        <v>7212450</v>
+        <v>7212365</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16788,22 +16788,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129000149</v>
+        <v>129085076</v>
       </c>
       <c r="B156" t="n">
-        <v>97546</v>
+        <v>91504</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16811,37 +16811,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>583660</v>
+        <v>583540</v>
       </c>
       <c r="R156" t="n">
-        <v>7212365</v>
+        <v>7212450</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16885,22 +16885,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129085096</v>
+        <v>129000110</v>
       </c>
       <c r="B157" t="n">
-        <v>91551</v>
+        <v>57885</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16908,37 +16908,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>583522</v>
+        <v>583842</v>
       </c>
       <c r="R157" t="n">
-        <v>7212551</v>
+        <v>7212868</v>
       </c>
       <c r="S157" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16982,44 +16982,44 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129000188</v>
+        <v>129000094</v>
       </c>
       <c r="B158" t="n">
-        <v>80179</v>
+        <v>83005</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17029,10 +17029,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>583606</v>
+        <v>583585</v>
       </c>
       <c r="R158" t="n">
-        <v>7212484</v>
+        <v>7212671</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17091,32 +17091,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129000094</v>
+        <v>129000188</v>
       </c>
       <c r="B159" t="n">
-        <v>83015</v>
+        <v>80179</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17126,10 +17126,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>583585</v>
+        <v>583606</v>
       </c>
       <c r="R159" t="n">
-        <v>7212671</v>
+        <v>7212484</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17188,10 +17188,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129000110</v>
+        <v>129085096</v>
       </c>
       <c r="B160" t="n">
-        <v>57885</v>
+        <v>91558</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17199,37 +17199,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>583842</v>
+        <v>583522</v>
       </c>
       <c r="R160" t="n">
-        <v>7212868</v>
+        <v>7212551</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17273,12 +17273,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17288,7 +17288,7 @@
         <v>129000100</v>
       </c>
       <c r="B161" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>129000096</v>
       </c>
       <c r="B162" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>129073200</v>
       </c>
       <c r="B163" t="n">
-        <v>91708</v>
+        <v>91715</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17576,10 +17576,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129000153</v>
+        <v>129000177</v>
       </c>
       <c r="B164" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17587,37 +17587,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>583768</v>
+        <v>583609</v>
       </c>
       <c r="R164" t="n">
-        <v>7212826</v>
+        <v>7212495</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17658,24 +17655,8 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
@@ -17692,10 +17673,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129000177</v>
+        <v>129000153</v>
       </c>
       <c r="B165" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17703,34 +17684,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>583609</v>
+        <v>583768</v>
       </c>
       <c r="R165" t="n">
-        <v>7212495</v>
+        <v>7212826</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17771,8 +17755,24 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
@@ -17889,7 +17889,7 @@
         <v>129085074</v>
       </c>
       <c r="B167" t="n">
-        <v>105717</v>
+        <v>105724</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>129085075</v>
       </c>
       <c r="B168" t="n">
-        <v>105717</v>
+        <v>105724</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18080,10 +18080,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129000104</v>
+        <v>129085078</v>
       </c>
       <c r="B169" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18111,17 +18111,17 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>584023</v>
+        <v>583677</v>
       </c>
       <c r="R169" t="n">
-        <v>7212353</v>
+        <v>7212815</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18165,22 +18165,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129085078</v>
+        <v>129000104</v>
       </c>
       <c r="B170" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18208,17 +18208,17 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>583677</v>
+        <v>584023</v>
       </c>
       <c r="R170" t="n">
-        <v>7212815</v>
+        <v>7212353</v>
       </c>
       <c r="S170" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18262,22 +18262,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129085099</v>
+        <v>129000122</v>
       </c>
       <c r="B171" t="n">
-        <v>79039</v>
+        <v>80145</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18285,37 +18285,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>583975</v>
+        <v>583833</v>
       </c>
       <c r="R171" t="n">
-        <v>7212333</v>
+        <v>7212856</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18359,12 +18359,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
         <v>129000170</v>
       </c>
       <c r="B172" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18468,10 +18468,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129000122</v>
+        <v>129085099</v>
       </c>
       <c r="B173" t="n">
-        <v>80145</v>
+        <v>79039</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18479,37 +18479,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>583833</v>
+        <v>583975</v>
       </c>
       <c r="R173" t="n">
-        <v>7212856</v>
+        <v>7212333</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18553,12 +18553,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -18662,10 +18662,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129085097</v>
+        <v>129000172</v>
       </c>
       <c r="B175" t="n">
-        <v>79039</v>
+        <v>91558</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18673,37 +18673,37 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>583788</v>
+        <v>583719</v>
       </c>
       <c r="R175" t="n">
-        <v>7212781</v>
+        <v>7212791</v>
       </c>
       <c r="S175" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18747,60 +18747,60 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129085083</v>
+        <v>129000124</v>
       </c>
       <c r="B176" t="n">
-        <v>80173</v>
+        <v>83010</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>583520</v>
+        <v>583770</v>
       </c>
       <c r="R176" t="n">
-        <v>7212517</v>
+        <v>7212830</v>
       </c>
       <c r="S176" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -18844,60 +18844,60 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129000124</v>
+        <v>129085083</v>
       </c>
       <c r="B177" t="n">
-        <v>83020</v>
+        <v>80173</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>583770</v>
+        <v>583520</v>
       </c>
       <c r="R177" t="n">
-        <v>7212830</v>
+        <v>7212517</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -18941,22 +18941,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129000172</v>
+        <v>129085097</v>
       </c>
       <c r="B178" t="n">
-        <v>91551</v>
+        <v>79039</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18964,37 +18964,37 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>583719</v>
+        <v>583788</v>
       </c>
       <c r="R178" t="n">
-        <v>7212791</v>
+        <v>7212781</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19038,12 +19038,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
@@ -19053,7 +19053,7 @@
         <v>129085079</v>
       </c>
       <c r="B179" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19147,10 +19147,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129000129</v>
+        <v>129000101</v>
       </c>
       <c r="B180" t="n">
-        <v>91818</v>
+        <v>91540</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19158,21 +19158,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19182,10 +19182,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>583810</v>
+        <v>583663</v>
       </c>
       <c r="R180" t="n">
-        <v>7212852</v>
+        <v>7212429</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19244,32 +19244,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129073201</v>
+        <v>129000129</v>
       </c>
       <c r="B181" t="n">
-        <v>92323</v>
+        <v>91825</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>918</v>
+        <v>658</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19279,10 +19279,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>583599</v>
+        <v>583810</v>
       </c>
       <c r="R181" t="n">
-        <v>7212710</v>
+        <v>7212852</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19334,55 +19334,55 @@
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129085095</v>
+        <v>129073202</v>
       </c>
       <c r="B182" t="n">
-        <v>91551</v>
+        <v>95526</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5432</v>
+        <v>2387</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>583378</v>
+        <v>584165</v>
       </c>
       <c r="R182" t="n">
-        <v>7212728</v>
+        <v>7211601</v>
       </c>
       <c r="S182" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19406,12 +19406,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19426,44 +19426,44 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129000101</v>
+        <v>129073201</v>
       </c>
       <c r="B183" t="n">
-        <v>91533</v>
+        <v>92330</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1202</v>
+        <v>918</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19473,10 +19473,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>583663</v>
+        <v>583599</v>
       </c>
       <c r="R183" t="n">
-        <v>7212429</v>
+        <v>7212710</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19528,55 +19528,55 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129073202</v>
+        <v>129085095</v>
       </c>
       <c r="B184" t="n">
-        <v>95519</v>
+        <v>91558</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2387</v>
+        <v>5432</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>584165</v>
+        <v>583378</v>
       </c>
       <c r="R184" t="n">
-        <v>7211601</v>
+        <v>7212728</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19600,12 +19600,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19620,60 +19620,60 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129085082</v>
+        <v>129000121</v>
       </c>
       <c r="B185" t="n">
-        <v>80173</v>
+        <v>80145</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>583926</v>
+        <v>583770</v>
       </c>
       <c r="R185" t="n">
-        <v>7212799</v>
+        <v>7212825</v>
       </c>
       <c r="S185" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19717,60 +19717,60 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129000121</v>
+        <v>129085082</v>
       </c>
       <c r="B186" t="n">
-        <v>80145</v>
+        <v>80173</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>583770</v>
+        <v>583926</v>
       </c>
       <c r="R186" t="n">
-        <v>7212825</v>
+        <v>7212799</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19814,22 +19814,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129000160</v>
+        <v>129085086</v>
       </c>
       <c r="B187" t="n">
-        <v>91529</v>
+        <v>57725</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19837,37 +19837,41 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>583674</v>
+        <v>583569</v>
       </c>
       <c r="R187" t="n">
-        <v>7212755</v>
+        <v>7212757</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19897,6 +19901,11 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19911,39 +19920,39 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129000132</v>
+        <v>129085092</v>
       </c>
       <c r="B188" t="n">
-        <v>57725</v>
+        <v>58095</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -19954,17 +19963,17 @@
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>583968</v>
+        <v>584017</v>
       </c>
       <c r="R188" t="n">
-        <v>7212362</v>
+        <v>7212353</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19994,11 +20003,6 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20013,22 +20017,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129085086</v>
+        <v>129000160</v>
       </c>
       <c r="B189" t="n">
-        <v>57725</v>
+        <v>91536</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20036,41 +20040,37 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>583569</v>
+        <v>583674</v>
       </c>
       <c r="R189" t="n">
-        <v>7212757</v>
+        <v>7212755</v>
       </c>
       <c r="S189" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20100,11 +20100,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20119,39 +20114,39 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129085092</v>
+        <v>129000132</v>
       </c>
       <c r="B190" t="n">
-        <v>58095</v>
+        <v>57725</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -20162,17 +20157,17 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>584017</v>
+        <v>583968</v>
       </c>
       <c r="R190" t="n">
-        <v>7212353</v>
+        <v>7212362</v>
       </c>
       <c r="S190" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20202,6 +20197,11 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20216,12 +20216,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
@@ -20231,7 +20231,7 @@
         <v>129000162</v>
       </c>
       <c r="B191" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -8171,32 +8171,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128998140</v>
+        <v>128998144</v>
       </c>
       <c r="B68" t="n">
-        <v>91536</v>
+        <v>82990</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1108</v>
+        <v>6439</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8206,10 +8206,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583855</v>
+        <v>583765</v>
       </c>
       <c r="R68" t="n">
-        <v>7213081</v>
+        <v>7212611</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8268,32 +8268,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128998144</v>
+        <v>128998140</v>
       </c>
       <c r="B69" t="n">
-        <v>82988</v>
+        <v>91538</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6439</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>583765</v>
+        <v>583855</v>
       </c>
       <c r="R69" t="n">
-        <v>7212611</v>
+        <v>7213081</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8368,7 +8368,7 @@
         <v>129000140</v>
       </c>
       <c r="B70" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8467,10 +8467,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129000183</v>
+        <v>128998142</v>
       </c>
       <c r="B71" t="n">
-        <v>79039</v>
+        <v>91538</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8478,34 +8478,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>584220</v>
+        <v>583800</v>
       </c>
       <c r="R71" t="n">
-        <v>7211664</v>
+        <v>7212769</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8532,12 +8532,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8552,57 +8552,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128998142</v>
+        <v>128997038</v>
       </c>
       <c r="B72" t="n">
-        <v>91536</v>
+        <v>97555</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1108</v>
+        <v>221941</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583800</v>
+        <v>583850</v>
       </c>
       <c r="R72" t="n">
-        <v>7212769</v>
+        <v>7212515</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8649,22 +8649,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128997038</v>
+        <v>128998122</v>
       </c>
       <c r="B73" t="n">
-        <v>97553</v>
+        <v>105726</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8672,34 +8672,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583850</v>
+        <v>583934</v>
       </c>
       <c r="R73" t="n">
-        <v>7212515</v>
+        <v>7212490</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8746,57 +8746,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128998122</v>
+        <v>129000183</v>
       </c>
       <c r="B74" t="n">
-        <v>105724</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583934</v>
+        <v>584220</v>
       </c>
       <c r="R74" t="n">
-        <v>7212490</v>
+        <v>7211664</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8843,57 +8843,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128998128</v>
+        <v>129000152</v>
       </c>
       <c r="B75" t="n">
-        <v>57885</v>
+        <v>80174</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583799</v>
+        <v>584338</v>
       </c>
       <c r="R75" t="n">
-        <v>7212748</v>
+        <v>7211689</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8940,57 +8940,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129000152</v>
+        <v>128998128</v>
       </c>
       <c r="B76" t="n">
-        <v>80172</v>
+        <v>57887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>584338</v>
+        <v>583799</v>
       </c>
       <c r="R76" t="n">
-        <v>7211689</v>
+        <v>7212748</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9017,12 +9017,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9037,44 +9037,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128998131</v>
+        <v>128998135</v>
       </c>
       <c r="B77" t="n">
-        <v>57722</v>
+        <v>91912</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>584025</v>
+        <v>583778</v>
       </c>
       <c r="R77" t="n">
-        <v>7212370</v>
+        <v>7212890</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9146,32 +9146,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128998135</v>
+        <v>128998124</v>
       </c>
       <c r="B78" t="n">
-        <v>91910</v>
+        <v>91542</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>583778</v>
+        <v>583784</v>
       </c>
       <c r="R78" t="n">
-        <v>7212890</v>
+        <v>7212884</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9243,10 +9243,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128998124</v>
+        <v>128998131</v>
       </c>
       <c r="B79" t="n">
-        <v>91540</v>
+        <v>57724</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9254,21 +9254,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583784</v>
+        <v>584025</v>
       </c>
       <c r="R79" t="n">
-        <v>7212884</v>
+        <v>7212370</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9340,10 +9340,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129000163</v>
+        <v>128998147</v>
       </c>
       <c r="B80" t="n">
-        <v>91536</v>
+        <v>91560</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9351,34 +9351,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>584005</v>
+        <v>583732</v>
       </c>
       <c r="R80" t="n">
-        <v>7211652</v>
+        <v>7212858</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9425,12 +9425,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9440,7 +9440,7 @@
         <v>129000181</v>
       </c>
       <c r="B81" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9534,10 +9534,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128998147</v>
+        <v>129000163</v>
       </c>
       <c r="B82" t="n">
-        <v>91558</v>
+        <v>91538</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9545,34 +9545,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>583732</v>
+        <v>584005</v>
       </c>
       <c r="R82" t="n">
-        <v>7212858</v>
+        <v>7211652</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9599,12 +9599,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9619,12 +9619,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9634,7 +9634,7 @@
         <v>129000141</v>
       </c>
       <c r="B83" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9728,32 +9728,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128998153</v>
+        <v>128998133</v>
       </c>
       <c r="B84" t="n">
-        <v>80179</v>
+        <v>80147</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9763,10 +9763,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>583842</v>
+        <v>583743</v>
       </c>
       <c r="R84" t="n">
-        <v>7212492</v>
+        <v>7212862</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9825,32 +9825,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129000145</v>
+        <v>129000115</v>
       </c>
       <c r="B85" t="n">
-        <v>57725</v>
+        <v>80175</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>583826</v>
+        <v>583856</v>
       </c>
       <c r="R85" t="n">
-        <v>7211682</v>
+        <v>7212374</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9890,12 +9890,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9922,32 +9922,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129000115</v>
+        <v>129000145</v>
       </c>
       <c r="B86" t="n">
-        <v>80173</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9957,10 +9957,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>583856</v>
+        <v>583826</v>
       </c>
       <c r="R86" t="n">
-        <v>7212374</v>
+        <v>7211682</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9987,12 +9987,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10019,32 +10019,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128998133</v>
+        <v>128998153</v>
       </c>
       <c r="B87" t="n">
-        <v>80145</v>
+        <v>80181</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10054,10 +10054,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>583743</v>
+        <v>583842</v>
       </c>
       <c r="R87" t="n">
-        <v>7212862</v>
+        <v>7212492</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10119,7 +10119,7 @@
         <v>128998134</v>
       </c>
       <c r="B88" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>128998127</v>
       </c>
       <c r="B89" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>128998152</v>
       </c>
       <c r="B90" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10420,45 +10420,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128997040</v>
+        <v>128998130</v>
       </c>
       <c r="B91" t="n">
-        <v>91536</v>
+        <v>80175</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>583800</v>
+        <v>583781</v>
       </c>
       <c r="R91" t="n">
-        <v>7212621</v>
+        <v>7212767</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10505,57 +10505,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128998130</v>
+        <v>128997035</v>
       </c>
       <c r="B92" t="n">
-        <v>80173</v>
+        <v>57887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>583781</v>
+        <v>583868</v>
       </c>
       <c r="R92" t="n">
-        <v>7212767</v>
+        <v>7212926</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10602,22 +10602,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129000165</v>
+        <v>128997040</v>
       </c>
       <c r="B93" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10649,10 +10649,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>583888</v>
+        <v>583800</v>
       </c>
       <c r="R93" t="n">
-        <v>7211663</v>
+        <v>7212621</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10679,12 +10679,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10699,22 +10699,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129000116</v>
+        <v>129000165</v>
       </c>
       <c r="B94" t="n">
-        <v>57722</v>
+        <v>91538</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10722,21 +10722,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10746,10 +10746,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>584099</v>
+        <v>583888</v>
       </c>
       <c r="R94" t="n">
-        <v>7211521</v>
+        <v>7211663</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10782,11 +10782,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Spillkråkehack på låga</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10813,10 +10808,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128997035</v>
+        <v>129000116</v>
       </c>
       <c r="B95" t="n">
-        <v>57885</v>
+        <v>57724</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10824,21 +10819,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10848,10 +10843,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>583868</v>
+        <v>584099</v>
       </c>
       <c r="R95" t="n">
-        <v>7212926</v>
+        <v>7211521</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10878,12 +10873,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Spillkråkehack på låga</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10898,22 +10898,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129000175</v>
+        <v>128998150</v>
       </c>
       <c r="B96" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10921,34 +10921,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>583975</v>
+        <v>583862</v>
       </c>
       <c r="R96" t="n">
-        <v>7211530</v>
+        <v>7212466</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10975,12 +10975,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10995,44 +10995,44 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128998155</v>
+        <v>128998146</v>
       </c>
       <c r="B97" t="n">
-        <v>80179</v>
+        <v>91560</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11042,10 +11042,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>583778</v>
+        <v>583700</v>
       </c>
       <c r="R97" t="n">
-        <v>7212766</v>
+        <v>7212870</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11104,32 +11104,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128998146</v>
+        <v>128998155</v>
       </c>
       <c r="B98" t="n">
-        <v>91558</v>
+        <v>80181</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11139,10 +11139,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>583700</v>
+        <v>583778</v>
       </c>
       <c r="R98" t="n">
-        <v>7212870</v>
+        <v>7212766</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11201,10 +11201,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128998150</v>
+        <v>129000175</v>
       </c>
       <c r="B99" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11212,34 +11212,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>583862</v>
+        <v>583975</v>
       </c>
       <c r="R99" t="n">
-        <v>7212466</v>
+        <v>7211530</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11266,12 +11266,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11286,57 +11286,57 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129000107</v>
+        <v>128998132</v>
       </c>
       <c r="B100" t="n">
-        <v>92240</v>
+        <v>57724</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>583938</v>
+        <v>583834</v>
       </c>
       <c r="R100" t="n">
-        <v>7211643</v>
+        <v>7212585</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11363,12 +11363,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11383,44 +11383,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128998132</v>
+        <v>128998136</v>
       </c>
       <c r="B101" t="n">
-        <v>57722</v>
+        <v>80182</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11430,10 +11430,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>583834</v>
+        <v>583838</v>
       </c>
       <c r="R101" t="n">
-        <v>7212585</v>
+        <v>7212502</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11492,10 +11492,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128998136</v>
+        <v>129000107</v>
       </c>
       <c r="B102" t="n">
-        <v>80180</v>
+        <v>92242</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11503,34 +11503,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>583838</v>
+        <v>583938</v>
       </c>
       <c r="R102" t="n">
-        <v>7212502</v>
+        <v>7211643</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11557,12 +11557,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11577,12 +11577,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11592,7 +11592,7 @@
         <v>129000150</v>
       </c>
       <c r="B103" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11686,10 +11686,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129000126</v>
+        <v>128998250</v>
       </c>
       <c r="B104" t="n">
-        <v>83010</v>
+        <v>57727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11697,34 +11697,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>583693</v>
+        <v>583752</v>
       </c>
       <c r="R104" t="n">
-        <v>7211591</v>
+        <v>7212679</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11751,12 +11759,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11771,22 +11784,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129000130</v>
+        <v>128997039</v>
       </c>
       <c r="B105" t="n">
-        <v>57725</v>
+        <v>91538</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11794,21 +11807,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11818,10 +11831,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>584350</v>
+        <v>583807</v>
       </c>
       <c r="R105" t="n">
-        <v>7211690</v>
+        <v>7212750</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11848,17 +11861,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Äldre och färska ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11873,44 +11881,44 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129000147</v>
+        <v>129000126</v>
       </c>
       <c r="B106" t="n">
-        <v>97553</v>
+        <v>83012</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221941</v>
+        <v>1467</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11920,10 +11928,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>584141</v>
+        <v>583693</v>
       </c>
       <c r="R106" t="n">
-        <v>7211590</v>
+        <v>7211591</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11982,10 +11990,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128997039</v>
+        <v>129000130</v>
       </c>
       <c r="B107" t="n">
-        <v>91536</v>
+        <v>57727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11993,21 +12001,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12017,10 +12025,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>583807</v>
+        <v>584350</v>
       </c>
       <c r="R107" t="n">
-        <v>7212750</v>
+        <v>7211690</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12047,12 +12055,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12067,65 +12080,57 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128998250</v>
+        <v>129000147</v>
       </c>
       <c r="B108" t="n">
-        <v>57725</v>
+        <v>97555</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>583752</v>
+        <v>584141</v>
       </c>
       <c r="R108" t="n">
-        <v>7212679</v>
+        <v>7211590</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12152,17 +12157,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12177,39 +12177,39 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129000157</v>
+        <v>129000146</v>
       </c>
       <c r="B109" t="n">
-        <v>57829</v>
+        <v>57727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -12224,10 +12224,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>583712</v>
+        <v>583819</v>
       </c>
       <c r="R109" t="n">
-        <v>7211576</v>
+        <v>7211689</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12260,6 +12260,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12286,45 +12291,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129000187</v>
+        <v>128998126</v>
       </c>
       <c r="B110" t="n">
-        <v>88937</v>
+        <v>92242</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>510</v>
+        <v>3298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>583966</v>
+        <v>583748</v>
       </c>
       <c r="R110" t="n">
-        <v>7211510</v>
+        <v>7212869</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12351,12 +12356,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12371,22 +12376,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129000146</v>
+        <v>128998149</v>
       </c>
       <c r="B111" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12394,34 +12399,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>583819</v>
+        <v>584059</v>
       </c>
       <c r="R111" t="n">
-        <v>7211689</v>
+        <v>7212428</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12448,17 +12453,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12473,57 +12473,57 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128998126</v>
+        <v>129000187</v>
       </c>
       <c r="B112" t="n">
-        <v>92240</v>
+        <v>88939</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3298</v>
+        <v>510</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>583748</v>
+        <v>583966</v>
       </c>
       <c r="R112" t="n">
-        <v>7212869</v>
+        <v>7211510</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12550,12 +12550,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12570,57 +12570,57 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128998149</v>
+        <v>129000157</v>
       </c>
       <c r="B113" t="n">
-        <v>79039</v>
+        <v>57831</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>584059</v>
+        <v>583712</v>
       </c>
       <c r="R113" t="n">
-        <v>7212428</v>
+        <v>7211576</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12647,12 +12647,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12667,12 +12667,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -12682,7 +12682,7 @@
         <v>128998138</v>
       </c>
       <c r="B114" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>129000173</v>
       </c>
       <c r="B115" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>129000182</v>
       </c>
       <c r="B116" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>129000097</v>
       </c>
       <c r="B117" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13067,32 +13067,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129000119</v>
+        <v>129000135</v>
       </c>
       <c r="B118" t="n">
-        <v>83003</v>
+        <v>57727</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13102,10 +13102,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>583763</v>
+        <v>584139</v>
       </c>
       <c r="R118" t="n">
-        <v>7211568</v>
+        <v>7211559</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13138,6 +13138,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13164,32 +13169,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129000135</v>
+        <v>129000119</v>
       </c>
       <c r="B119" t="n">
-        <v>57725</v>
+        <v>83005</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13199,10 +13204,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>584139</v>
+        <v>583763</v>
       </c>
       <c r="R119" t="n">
-        <v>7211559</v>
+        <v>7211568</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13235,11 +13240,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13266,45 +13266,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129000169</v>
+        <v>128998148</v>
       </c>
       <c r="B120" t="n">
-        <v>82988</v>
+        <v>91560</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>583695</v>
+        <v>583764</v>
       </c>
       <c r="R120" t="n">
-        <v>7211591</v>
+        <v>7212875</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13331,12 +13331,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13351,44 +13351,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129000144</v>
+        <v>129000169</v>
       </c>
       <c r="B121" t="n">
-        <v>57725</v>
+        <v>82990</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13398,10 +13398,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>583832</v>
+        <v>583695</v>
       </c>
       <c r="R121" t="n">
-        <v>7211693</v>
+        <v>7211591</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13434,11 +13434,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13465,10 +13460,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128998148</v>
+        <v>129000144</v>
       </c>
       <c r="B122" t="n">
-        <v>91558</v>
+        <v>57727</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13476,34 +13471,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>583764</v>
+        <v>583832</v>
       </c>
       <c r="R122" t="n">
-        <v>7212875</v>
+        <v>7211693</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13530,12 +13525,17 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13550,12 +13550,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -13565,7 +13565,7 @@
         <v>128998151</v>
       </c>
       <c r="B123" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>128998129</v>
       </c>
       <c r="B124" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>128998154</v>
       </c>
       <c r="B125" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13853,10 +13853,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129000180</v>
+        <v>128998141</v>
       </c>
       <c r="B126" t="n">
-        <v>79039</v>
+        <v>91538</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13864,34 +13864,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>583695</v>
+        <v>583789</v>
       </c>
       <c r="R126" t="n">
-        <v>7211621</v>
+        <v>7213129</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13918,12 +13918,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13938,22 +13938,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129000142</v>
+        <v>129000180</v>
       </c>
       <c r="B127" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13961,21 +13961,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13985,10 +13985,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>583922</v>
+        <v>583695</v>
       </c>
       <c r="R127" t="n">
-        <v>7211662</v>
+        <v>7211621</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14021,11 +14021,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14052,10 +14047,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128998141</v>
+        <v>129000142</v>
       </c>
       <c r="B128" t="n">
-        <v>91536</v>
+        <v>57727</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14063,34 +14058,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>583789</v>
+        <v>583922</v>
       </c>
       <c r="R128" t="n">
-        <v>7213129</v>
+        <v>7211662</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14117,12 +14112,17 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14137,22 +14137,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129000168</v>
+        <v>129000184</v>
       </c>
       <c r="B129" t="n">
-        <v>91536</v>
+        <v>79041</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14160,21 +14160,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14184,10 +14184,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>584331</v>
+        <v>584333</v>
       </c>
       <c r="R129" t="n">
-        <v>7211693</v>
+        <v>7211688</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14246,45 +14246,48 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129000166</v>
+        <v>129000185</v>
       </c>
       <c r="B130" t="n">
-        <v>91536</v>
+        <v>92871</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1108</v>
+        <v>5964</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>583796</v>
+        <v>584074</v>
       </c>
       <c r="R130" t="n">
-        <v>7211546</v>
+        <v>7211675</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14325,6 +14328,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14343,10 +14347,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129000184</v>
+        <v>129000166</v>
       </c>
       <c r="B131" t="n">
-        <v>79039</v>
+        <v>91538</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14354,21 +14358,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14378,10 +14382,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>584333</v>
+        <v>583796</v>
       </c>
       <c r="R131" t="n">
-        <v>7211688</v>
+        <v>7211546</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14440,48 +14444,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129000185</v>
+        <v>129000168</v>
       </c>
       <c r="B132" t="n">
-        <v>92869</v>
+        <v>91538</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5964</v>
+        <v>1108</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>584074</v>
+        <v>584331</v>
       </c>
       <c r="R132" t="n">
-        <v>7211675</v>
+        <v>7211693</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14522,7 +14523,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14541,10 +14541,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129000167</v>
+        <v>129000174</v>
       </c>
       <c r="B133" t="n">
-        <v>91536</v>
+        <v>91560</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14552,21 +14552,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14576,10 +14576,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>584144</v>
+        <v>583934</v>
       </c>
       <c r="R133" t="n">
-        <v>7211566</v>
+        <v>7211520</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14638,10 +14638,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129000138</v>
+        <v>129000167</v>
       </c>
       <c r="B134" t="n">
-        <v>57725</v>
+        <v>91538</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14649,21 +14649,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14673,10 +14673,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>583805</v>
+        <v>584144</v>
       </c>
       <c r="R134" t="n">
-        <v>7211693</v>
+        <v>7211566</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14709,11 +14709,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14740,10 +14735,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129000174</v>
+        <v>129000138</v>
       </c>
       <c r="B135" t="n">
-        <v>91558</v>
+        <v>57727</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14751,21 +14746,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14775,10 +14770,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>583934</v>
+        <v>583805</v>
       </c>
       <c r="R135" t="n">
-        <v>7211520</v>
+        <v>7211693</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14811,6 +14806,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14840,7 +14840,7 @@
         <v>129012557</v>
       </c>
       <c r="B136" t="n">
-        <v>88937</v>
+        <v>88939</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>129012558</v>
       </c>
       <c r="B137" t="n">
-        <v>92213</v>
+        <v>92215</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>129012556</v>
       </c>
       <c r="B138" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15132,32 +15132,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129000128</v>
+        <v>129000179</v>
       </c>
       <c r="B139" t="n">
-        <v>91995</v>
+        <v>79041</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15167,10 +15167,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>583804</v>
+        <v>583976</v>
       </c>
       <c r="R139" t="n">
-        <v>7212351</v>
+        <v>7212366</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15229,32 +15229,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129000179</v>
+        <v>129000128</v>
       </c>
       <c r="B140" t="n">
-        <v>79039</v>
+        <v>91997</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15264,10 +15264,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>583976</v>
+        <v>583804</v>
       </c>
       <c r="R140" t="n">
-        <v>7212366</v>
+        <v>7212351</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15329,7 +15329,7 @@
         <v>129000136</v>
       </c>
       <c r="B141" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>129085087</v>
       </c>
       <c r="B142" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>129085098</v>
       </c>
       <c r="B143" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15631,10 +15631,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129000137</v>
+        <v>129085077</v>
       </c>
       <c r="B144" t="n">
-        <v>57725</v>
+        <v>91542</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15642,37 +15642,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>583784</v>
+        <v>583874</v>
       </c>
       <c r="R144" t="n">
-        <v>7212338</v>
+        <v>7212775</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15702,11 +15702,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15721,22 +15716,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129085077</v>
+        <v>129085080</v>
       </c>
       <c r="B145" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15768,10 +15763,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>583874</v>
+        <v>583726</v>
       </c>
       <c r="R145" t="n">
-        <v>7212775</v>
+        <v>7212315</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15830,10 +15825,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129085080</v>
+        <v>129000137</v>
       </c>
       <c r="B146" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15841,37 +15836,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>583726</v>
+        <v>583784</v>
       </c>
       <c r="R146" t="n">
-        <v>7212315</v>
+        <v>7212338</v>
       </c>
       <c r="S146" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15901,6 +15896,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15915,12 +15915,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -15930,7 +15930,7 @@
         <v>129085094</v>
       </c>
       <c r="B147" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>129000171</v>
       </c>
       <c r="B148" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>129000159</v>
       </c>
       <c r="B149" t="n">
-        <v>56906</v>
+        <v>56908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>129000106</v>
       </c>
       <c r="B150" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16315,48 +16315,48 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129000178</v>
+        <v>129085088</v>
       </c>
       <c r="B151" t="n">
-        <v>79039</v>
+        <v>97549</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>583707</v>
+        <v>583895</v>
       </c>
       <c r="R151" t="n">
-        <v>7212347</v>
+        <v>7212319</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16400,60 +16400,60 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129085088</v>
+        <v>129000178</v>
       </c>
       <c r="B152" t="n">
-        <v>97547</v>
+        <v>79041</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>583895</v>
+        <v>583707</v>
       </c>
       <c r="R152" t="n">
-        <v>7212319</v>
+        <v>7212347</v>
       </c>
       <c r="S152" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16497,60 +16497,60 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129000103</v>
+        <v>129085076</v>
       </c>
       <c r="B153" t="n">
-        <v>91540</v>
+        <v>91506</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>583841</v>
+        <v>583540</v>
       </c>
       <c r="R153" t="n">
-        <v>7212355</v>
+        <v>7212450</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16594,44 +16594,44 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129000189</v>
+        <v>129000103</v>
       </c>
       <c r="B154" t="n">
-        <v>80179</v>
+        <v>91542</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16641,10 +16641,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>583856</v>
+        <v>583841</v>
       </c>
       <c r="R154" t="n">
-        <v>7212375</v>
+        <v>7212355</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16706,7 +16706,7 @@
         <v>129000149</v>
       </c>
       <c r="B155" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16800,10 +16800,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129085076</v>
+        <v>129000189</v>
       </c>
       <c r="B156" t="n">
-        <v>91504</v>
+        <v>80181</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16811,37 +16811,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>583540</v>
+        <v>583856</v>
       </c>
       <c r="R156" t="n">
-        <v>7212450</v>
+        <v>7212375</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16885,22 +16885,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129000110</v>
+        <v>129085096</v>
       </c>
       <c r="B157" t="n">
-        <v>57885</v>
+        <v>91560</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16908,37 +16908,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>583842</v>
+        <v>583522</v>
       </c>
       <c r="R157" t="n">
-        <v>7212868</v>
+        <v>7212551</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16982,12 +16982,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -16997,7 +16997,7 @@
         <v>129000094</v>
       </c>
       <c r="B158" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>129000188</v>
       </c>
       <c r="B159" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17188,10 +17188,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129085096</v>
+        <v>129000110</v>
       </c>
       <c r="B160" t="n">
-        <v>91558</v>
+        <v>57887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17199,37 +17199,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>583522</v>
+        <v>583842</v>
       </c>
       <c r="R160" t="n">
-        <v>7212551</v>
+        <v>7212868</v>
       </c>
       <c r="S160" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17273,44 +17273,44 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129000100</v>
+        <v>129073200</v>
       </c>
       <c r="B161" t="n">
-        <v>91504</v>
+        <v>91717</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5447</v>
+        <v>1588</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17320,10 +17320,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>583841</v>
+        <v>583712</v>
       </c>
       <c r="R161" t="n">
-        <v>7212873</v>
+        <v>7211578</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17350,12 +17350,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17375,7 +17375,7 @@
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
@@ -17385,7 +17385,7 @@
         <v>129000096</v>
       </c>
       <c r="B162" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17479,32 +17479,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129073200</v>
+        <v>129000100</v>
       </c>
       <c r="B163" t="n">
-        <v>91715</v>
+        <v>91506</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1588</v>
+        <v>5447</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17514,10 +17514,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>583712</v>
+        <v>583841</v>
       </c>
       <c r="R163" t="n">
-        <v>7211578</v>
+        <v>7212873</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17544,12 +17544,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17569,17 +17569,17 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129000177</v>
+        <v>129000153</v>
       </c>
       <c r="B164" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17587,34 +17587,37 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>583609</v>
+        <v>583768</v>
       </c>
       <c r="R164" t="n">
-        <v>7212495</v>
+        <v>7212826</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17655,8 +17658,24 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
@@ -17673,10 +17692,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129000153</v>
+        <v>129000177</v>
       </c>
       <c r="B165" t="n">
-        <v>80144</v>
+        <v>79041</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17684,37 +17703,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>583768</v>
+        <v>583609</v>
       </c>
       <c r="R165" t="n">
-        <v>7212826</v>
+        <v>7212495</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17755,24 +17771,8 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
@@ -17789,10 +17789,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129000114</v>
+        <v>129085074</v>
       </c>
       <c r="B166" t="n">
-        <v>80173</v>
+        <v>105726</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17800,37 +17800,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>583606</v>
+        <v>583517</v>
       </c>
       <c r="R166" t="n">
-        <v>7212483</v>
+        <v>7212494</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17874,22 +17874,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129085074</v>
+        <v>129085075</v>
       </c>
       <c r="B167" t="n">
-        <v>105724</v>
+        <v>105726</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17921,10 +17921,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>583517</v>
+        <v>583896</v>
       </c>
       <c r="R167" t="n">
-        <v>7212494</v>
+        <v>7212322</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -17983,10 +17983,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129085075</v>
+        <v>129000114</v>
       </c>
       <c r="B168" t="n">
-        <v>105724</v>
+        <v>80175</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17994,37 +17994,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>583896</v>
+        <v>583606</v>
       </c>
       <c r="R168" t="n">
-        <v>7212322</v>
+        <v>7212483</v>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18068,12 +18068,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
@@ -18083,7 +18083,7 @@
         <v>129085078</v>
       </c>
       <c r="B169" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>129000104</v>
       </c>
       <c r="B170" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18274,10 +18274,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129000122</v>
+        <v>129085099</v>
       </c>
       <c r="B171" t="n">
-        <v>80145</v>
+        <v>79041</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18285,37 +18285,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>583833</v>
+        <v>583975</v>
       </c>
       <c r="R171" t="n">
-        <v>7212856</v>
+        <v>7212333</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18359,12 +18359,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
         <v>129000170</v>
       </c>
       <c r="B172" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18468,10 +18468,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129085099</v>
+        <v>129000122</v>
       </c>
       <c r="B173" t="n">
-        <v>79039</v>
+        <v>80147</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18479,37 +18479,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>583975</v>
+        <v>583833</v>
       </c>
       <c r="R173" t="n">
-        <v>7212333</v>
+        <v>7212856</v>
       </c>
       <c r="S173" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18553,12 +18553,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -18568,7 +18568,7 @@
         <v>129000176</v>
       </c>
       <c r="B174" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18662,48 +18662,48 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129000172</v>
+        <v>129085083</v>
       </c>
       <c r="B175" t="n">
-        <v>91558</v>
+        <v>80175</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>583719</v>
+        <v>583520</v>
       </c>
       <c r="R175" t="n">
-        <v>7212791</v>
+        <v>7212517</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18747,22 +18747,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129000124</v>
+        <v>129085097</v>
       </c>
       <c r="B176" t="n">
-        <v>83010</v>
+        <v>79041</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18770,37 +18770,37 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>583770</v>
+        <v>583788</v>
       </c>
       <c r="R176" t="n">
-        <v>7212830</v>
+        <v>7212781</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -18844,60 +18844,60 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129085083</v>
+        <v>129000124</v>
       </c>
       <c r="B177" t="n">
-        <v>80173</v>
+        <v>83012</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>583520</v>
+        <v>583770</v>
       </c>
       <c r="R177" t="n">
-        <v>7212517</v>
+        <v>7212830</v>
       </c>
       <c r="S177" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -18941,22 +18941,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129085097</v>
+        <v>129000172</v>
       </c>
       <c r="B178" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18964,37 +18964,37 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>583788</v>
+        <v>583719</v>
       </c>
       <c r="R178" t="n">
-        <v>7212781</v>
+        <v>7212791</v>
       </c>
       <c r="S178" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19038,12 +19038,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
@@ -19053,7 +19053,7 @@
         <v>129085079</v>
       </c>
       <c r="B179" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19147,10 +19147,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129000101</v>
+        <v>129085095</v>
       </c>
       <c r="B180" t="n">
-        <v>91540</v>
+        <v>91560</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19158,37 +19158,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>583663</v>
+        <v>583378</v>
       </c>
       <c r="R180" t="n">
-        <v>7212429</v>
+        <v>7212728</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19232,44 +19232,44 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129000129</v>
+        <v>129073201</v>
       </c>
       <c r="B181" t="n">
-        <v>91825</v>
+        <v>92332</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>658</v>
+        <v>918</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19279,10 +19279,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>583810</v>
+        <v>583599</v>
       </c>
       <c r="R181" t="n">
-        <v>7212852</v>
+        <v>7212710</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
@@ -19344,7 +19344,7 @@
         <v>129073202</v>
       </c>
       <c r="B182" t="n">
-        <v>95526</v>
+        <v>95528</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19438,32 +19438,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129073201</v>
+        <v>129000101</v>
       </c>
       <c r="B183" t="n">
-        <v>92330</v>
+        <v>91542</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>918</v>
+        <v>1202</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19473,10 +19473,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>583599</v>
+        <v>583663</v>
       </c>
       <c r="R183" t="n">
-        <v>7212710</v>
+        <v>7212429</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19528,17 +19528,17 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129085095</v>
+        <v>129000129</v>
       </c>
       <c r="B184" t="n">
-        <v>91558</v>
+        <v>91827</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19546,37 +19546,37 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>583378</v>
+        <v>583810</v>
       </c>
       <c r="R184" t="n">
-        <v>7212728</v>
+        <v>7212852</v>
       </c>
       <c r="S184" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19620,22 +19620,22 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129000121</v>
+        <v>129085086</v>
       </c>
       <c r="B185" t="n">
-        <v>80145</v>
+        <v>57727</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19643,37 +19643,41 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>583770</v>
+        <v>583569</v>
       </c>
       <c r="R185" t="n">
-        <v>7212825</v>
+        <v>7212757</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19703,6 +19707,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19717,60 +19726,60 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129085082</v>
+        <v>129000160</v>
       </c>
       <c r="B186" t="n">
-        <v>80173</v>
+        <v>91538</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>583926</v>
+        <v>583674</v>
       </c>
       <c r="R186" t="n">
-        <v>7212799</v>
+        <v>7212755</v>
       </c>
       <c r="S186" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19814,22 +19823,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129085086</v>
+        <v>129000121</v>
       </c>
       <c r="B187" t="n">
-        <v>57725</v>
+        <v>80147</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19837,41 +19846,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>583569</v>
+        <v>583770</v>
       </c>
       <c r="R187" t="n">
-        <v>7212757</v>
+        <v>7212825</v>
       </c>
       <c r="S187" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19901,11 +19906,6 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19920,22 +19920,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129085092</v>
+        <v>129085082</v>
       </c>
       <c r="B188" t="n">
-        <v>58095</v>
+        <v>80175</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19943,21 +19943,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19967,10 +19967,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>584017</v>
+        <v>583926</v>
       </c>
       <c r="R188" t="n">
-        <v>7212353</v>
+        <v>7212799</v>
       </c>
       <c r="S188" t="n">
         <v>15</v>
@@ -20022,55 +20022,55 @@
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129000160</v>
+        <v>129085092</v>
       </c>
       <c r="B189" t="n">
-        <v>91536</v>
+        <v>58097</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>583674</v>
+        <v>584017</v>
       </c>
       <c r="R189" t="n">
-        <v>7212755</v>
+        <v>7212353</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20114,12 +20114,12 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
@@ -20129,7 +20129,7 @@
         <v>129000132</v>
       </c>
       <c r="B190" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20228,32 +20228,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129000162</v>
+        <v>129000154</v>
       </c>
       <c r="B191" t="n">
-        <v>91536</v>
+        <v>80182</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20263,10 +20263,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>583583</v>
+        <v>583832</v>
       </c>
       <c r="R191" t="n">
-        <v>7212676</v>
+        <v>7212853</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20325,32 +20325,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129000154</v>
+        <v>129000162</v>
       </c>
       <c r="B192" t="n">
-        <v>80180</v>
+        <v>91538</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20360,10 +20360,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>583832</v>
+        <v>583583</v>
       </c>
       <c r="R192" t="n">
-        <v>7212853</v>
+        <v>7212676</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>

--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -8171,45 +8171,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128998144</v>
+        <v>129000140</v>
       </c>
       <c r="B68" t="n">
-        <v>82990</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583765</v>
+        <v>584092</v>
       </c>
       <c r="R68" t="n">
-        <v>7212611</v>
+        <v>7211517</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8236,12 +8236,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8256,12 +8261,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8365,45 +8370,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129000140</v>
+        <v>128998144</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>82990</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>584092</v>
+        <v>583765</v>
       </c>
       <c r="R70" t="n">
-        <v>7211517</v>
+        <v>7212611</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8430,17 +8435,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8455,12 +8455,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8564,32 +8564,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128997038</v>
+        <v>129000183</v>
       </c>
       <c r="B72" t="n">
-        <v>97555</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8599,10 +8599,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583850</v>
+        <v>584220</v>
       </c>
       <c r="R72" t="n">
-        <v>7212515</v>
+        <v>7211664</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8629,12 +8629,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8649,22 +8649,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128998122</v>
+        <v>128997038</v>
       </c>
       <c r="B73" t="n">
-        <v>105726</v>
+        <v>97555</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8672,34 +8672,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221725</v>
+        <v>221941</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583934</v>
+        <v>583850</v>
       </c>
       <c r="R73" t="n">
-        <v>7212490</v>
+        <v>7212515</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8746,57 +8746,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129000183</v>
+        <v>128998122</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>105726</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>584220</v>
+        <v>583934</v>
       </c>
       <c r="R74" t="n">
-        <v>7211664</v>
+        <v>7212490</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8843,12 +8843,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9049,32 +9049,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128998135</v>
+        <v>128998124</v>
       </c>
       <c r="B77" t="n">
-        <v>91912</v>
+        <v>91542</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583778</v>
+        <v>583784</v>
       </c>
       <c r="R77" t="n">
-        <v>7212890</v>
+        <v>7212884</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9146,32 +9146,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128998124</v>
+        <v>128998135</v>
       </c>
       <c r="B78" t="n">
-        <v>91542</v>
+        <v>91912</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>1506</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>583784</v>
+        <v>583778</v>
       </c>
       <c r="R78" t="n">
-        <v>7212884</v>
+        <v>7212890</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9825,32 +9825,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129000115</v>
+        <v>129000145</v>
       </c>
       <c r="B85" t="n">
-        <v>80175</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>583856</v>
+        <v>583826</v>
       </c>
       <c r="R85" t="n">
-        <v>7212374</v>
+        <v>7211682</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9890,12 +9890,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9922,45 +9922,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129000145</v>
+        <v>128998153</v>
       </c>
       <c r="B86" t="n">
-        <v>57727</v>
+        <v>80181</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>583826</v>
+        <v>583842</v>
       </c>
       <c r="R86" t="n">
-        <v>7211682</v>
+        <v>7212492</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9987,12 +9987,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10007,22 +10007,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128998153</v>
+        <v>129000115</v>
       </c>
       <c r="B87" t="n">
-        <v>80181</v>
+        <v>80175</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10030,34 +10030,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>583842</v>
+        <v>583856</v>
       </c>
       <c r="R87" t="n">
-        <v>7212492</v>
+        <v>7212374</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10104,12 +10104,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128998127</v>
+        <v>128998152</v>
       </c>
       <c r="B89" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10224,42 +10224,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>583792</v>
+        <v>583744</v>
       </c>
       <c r="R89" t="n">
-        <v>7212761</v>
+        <v>7212703</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10292,11 +10284,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färskt bohål som sannolikt är från tretåig hackspett pga storleken på bohålet (ca 5 cm)</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10323,10 +10310,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128998152</v>
+        <v>128998127</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10334,34 +10321,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>583744</v>
+        <v>583792</v>
       </c>
       <c r="R90" t="n">
-        <v>7212703</v>
+        <v>7212761</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10394,6 +10389,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färskt bohål som sannolikt är från tretåig hackspett pga storleken på bohålet (ca 5 cm)</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10420,45 +10420,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128998130</v>
+        <v>129000116</v>
       </c>
       <c r="B91" t="n">
-        <v>80175</v>
+        <v>57724</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>583781</v>
+        <v>584099</v>
       </c>
       <c r="R91" t="n">
-        <v>7212767</v>
+        <v>7211521</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10485,12 +10485,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Spillkråkehack på låga</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10505,22 +10510,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128997035</v>
+        <v>129000165</v>
       </c>
       <c r="B92" t="n">
-        <v>57887</v>
+        <v>91538</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10528,21 +10533,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10552,10 +10557,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>583868</v>
+        <v>583888</v>
       </c>
       <c r="R92" t="n">
-        <v>7212926</v>
+        <v>7211663</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10582,12 +10587,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10602,12 +10607,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10711,10 +10716,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129000165</v>
+        <v>128997035</v>
       </c>
       <c r="B94" t="n">
-        <v>91538</v>
+        <v>57887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10722,21 +10727,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10746,10 +10751,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>583888</v>
+        <v>583868</v>
       </c>
       <c r="R94" t="n">
-        <v>7211663</v>
+        <v>7212926</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10776,12 +10781,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10796,57 +10801,57 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129000116</v>
+        <v>128998130</v>
       </c>
       <c r="B95" t="n">
-        <v>57724</v>
+        <v>80175</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>584099</v>
+        <v>583781</v>
       </c>
       <c r="R95" t="n">
-        <v>7211521</v>
+        <v>7212767</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10873,17 +10878,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Spillkråkehack på låga</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10898,22 +10898,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128998150</v>
+        <v>128998146</v>
       </c>
       <c r="B96" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10921,21 +10921,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10945,10 +10945,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>583862</v>
+        <v>583700</v>
       </c>
       <c r="R96" t="n">
-        <v>7212466</v>
+        <v>7212870</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11007,7 +11007,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128998146</v>
+        <v>129000175</v>
       </c>
       <c r="B97" t="n">
         <v>91560</v>
@@ -11038,14 +11038,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>583700</v>
+        <v>583975</v>
       </c>
       <c r="R97" t="n">
-        <v>7212870</v>
+        <v>7211530</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11072,12 +11072,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11092,12 +11092,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -11201,10 +11201,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129000175</v>
+        <v>128998150</v>
       </c>
       <c r="B99" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11212,34 +11212,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>583975</v>
+        <v>583862</v>
       </c>
       <c r="R99" t="n">
-        <v>7211530</v>
+        <v>7212466</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11266,12 +11266,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11286,44 +11286,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128998132</v>
+        <v>128998136</v>
       </c>
       <c r="B100" t="n">
-        <v>57724</v>
+        <v>80182</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11333,10 +11333,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>583834</v>
+        <v>583838</v>
       </c>
       <c r="R100" t="n">
-        <v>7212585</v>
+        <v>7212502</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11395,32 +11395,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128998136</v>
+        <v>128998132</v>
       </c>
       <c r="B101" t="n">
-        <v>80182</v>
+        <v>57724</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11430,10 +11430,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>583838</v>
+        <v>583834</v>
       </c>
       <c r="R101" t="n">
-        <v>7212502</v>
+        <v>7212585</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11492,32 +11492,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129000107</v>
+        <v>129000150</v>
       </c>
       <c r="B102" t="n">
-        <v>92242</v>
+        <v>91912</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>3298</v>
+        <v>1506</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11527,10 +11527,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>583938</v>
+        <v>583951</v>
       </c>
       <c r="R102" t="n">
-        <v>7211643</v>
+        <v>7211500</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11589,32 +11589,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129000150</v>
+        <v>129000107</v>
       </c>
       <c r="B103" t="n">
-        <v>91912</v>
+        <v>92242</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1506</v>
+        <v>3298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11624,10 +11624,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>583951</v>
+        <v>583938</v>
       </c>
       <c r="R103" t="n">
-        <v>7211500</v>
+        <v>7211643</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11686,10 +11686,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128998250</v>
+        <v>129000126</v>
       </c>
       <c r="B104" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11697,42 +11697,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>583752</v>
+        <v>583693</v>
       </c>
       <c r="R104" t="n">
-        <v>7212679</v>
+        <v>7211591</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11759,17 +11751,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11784,22 +11771,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128997039</v>
+        <v>129000130</v>
       </c>
       <c r="B105" t="n">
-        <v>91538</v>
+        <v>57727</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11807,21 +11794,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11831,10 +11818,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>583807</v>
+        <v>584350</v>
       </c>
       <c r="R105" t="n">
-        <v>7212750</v>
+        <v>7211690</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11861,12 +11848,17 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11881,22 +11873,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129000126</v>
+        <v>128997039</v>
       </c>
       <c r="B106" t="n">
-        <v>83012</v>
+        <v>91538</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11904,21 +11896,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11928,10 +11920,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>583693</v>
+        <v>583807</v>
       </c>
       <c r="R106" t="n">
-        <v>7211591</v>
+        <v>7212750</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11958,12 +11950,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11978,19 +11970,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129000130</v>
+        <v>128998250</v>
       </c>
       <c r="B107" t="n">
         <v>57727</v>
@@ -12019,16 +12011,24 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>584350</v>
+        <v>583752</v>
       </c>
       <c r="R107" t="n">
-        <v>7211690</v>
+        <v>7212679</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12055,17 +12055,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Äldre och färska ringhack</t>
+          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12080,12 +12080,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12189,45 +12189,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129000146</v>
+        <v>128998126</v>
       </c>
       <c r="B109" t="n">
-        <v>57727</v>
+        <v>92242</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>583819</v>
+        <v>583748</v>
       </c>
       <c r="R109" t="n">
-        <v>7211689</v>
+        <v>7212869</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12254,17 +12254,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12279,22 +12274,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128998126</v>
+        <v>129000157</v>
       </c>
       <c r="B110" t="n">
-        <v>92242</v>
+        <v>57831</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12302,34 +12297,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3298</v>
+        <v>103031</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>583748</v>
+        <v>583712</v>
       </c>
       <c r="R110" t="n">
-        <v>7212869</v>
+        <v>7211576</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12356,12 +12351,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12376,22 +12371,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128998149</v>
+        <v>129000146</v>
       </c>
       <c r="B111" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12399,34 +12394,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>584059</v>
+        <v>583819</v>
       </c>
       <c r="R111" t="n">
-        <v>7212428</v>
+        <v>7211689</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12453,12 +12448,17 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12473,22 +12473,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129000187</v>
+        <v>128998149</v>
       </c>
       <c r="B112" t="n">
-        <v>88939</v>
+        <v>79041</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12496,34 +12496,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>583966</v>
+        <v>584059</v>
       </c>
       <c r="R112" t="n">
-        <v>7211510</v>
+        <v>7212428</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12550,12 +12550,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12570,44 +12570,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129000157</v>
+        <v>129000187</v>
       </c>
       <c r="B113" t="n">
-        <v>57831</v>
+        <v>88939</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103031</v>
+        <v>510</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>583712</v>
+        <v>583966</v>
       </c>
       <c r="R113" t="n">
-        <v>7211576</v>
+        <v>7211510</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13067,32 +13067,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129000135</v>
+        <v>129000119</v>
       </c>
       <c r="B118" t="n">
-        <v>57727</v>
+        <v>83005</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13102,10 +13102,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>584139</v>
+        <v>583763</v>
       </c>
       <c r="R118" t="n">
-        <v>7211559</v>
+        <v>7211568</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13138,11 +13138,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13169,32 +13164,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129000119</v>
+        <v>129000135</v>
       </c>
       <c r="B119" t="n">
-        <v>83005</v>
+        <v>57727</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13204,10 +13199,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>583763</v>
+        <v>584139</v>
       </c>
       <c r="R119" t="n">
-        <v>7211568</v>
+        <v>7211559</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13240,6 +13235,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13266,45 +13266,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128998148</v>
+        <v>129000169</v>
       </c>
       <c r="B120" t="n">
-        <v>91560</v>
+        <v>82990</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>583764</v>
+        <v>583695</v>
       </c>
       <c r="R120" t="n">
-        <v>7212875</v>
+        <v>7211591</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13331,12 +13331,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13351,44 +13351,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129000169</v>
+        <v>129000144</v>
       </c>
       <c r="B121" t="n">
-        <v>82990</v>
+        <v>57727</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13398,10 +13398,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>583695</v>
+        <v>583832</v>
       </c>
       <c r="R121" t="n">
-        <v>7211591</v>
+        <v>7211693</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13434,6 +13434,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13460,10 +13465,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129000144</v>
+        <v>128998148</v>
       </c>
       <c r="B122" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13471,34 +13476,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>583832</v>
+        <v>583764</v>
       </c>
       <c r="R122" t="n">
-        <v>7211693</v>
+        <v>7212875</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13525,17 +13530,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13550,44 +13550,44 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128998151</v>
+        <v>128998129</v>
       </c>
       <c r="B123" t="n">
-        <v>79041</v>
+        <v>80175</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13597,10 +13597,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>583830</v>
+        <v>583743</v>
       </c>
       <c r="R123" t="n">
-        <v>7212605</v>
+        <v>7212862</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13659,10 +13659,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128998129</v>
+        <v>128998154</v>
       </c>
       <c r="B124" t="n">
-        <v>80175</v>
+        <v>80181</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13670,21 +13670,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13756,27 +13756,27 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128998154</v>
+        <v>128998151</v>
       </c>
       <c r="B125" t="n">
-        <v>80181</v>
+        <v>79041</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -13791,10 +13791,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>583743</v>
+        <v>583830</v>
       </c>
       <c r="R125" t="n">
-        <v>7212862</v>
+        <v>7212605</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13853,10 +13853,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128998141</v>
+        <v>129000180</v>
       </c>
       <c r="B126" t="n">
-        <v>91538</v>
+        <v>79041</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13864,34 +13864,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>583789</v>
+        <v>583695</v>
       </c>
       <c r="R126" t="n">
-        <v>7213129</v>
+        <v>7211621</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13918,12 +13918,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13938,22 +13938,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129000180</v>
+        <v>129000142</v>
       </c>
       <c r="B127" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13961,21 +13961,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13985,10 +13985,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>583695</v>
+        <v>583922</v>
       </c>
       <c r="R127" t="n">
-        <v>7211621</v>
+        <v>7211662</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14021,6 +14021,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14047,10 +14052,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129000142</v>
+        <v>128998141</v>
       </c>
       <c r="B128" t="n">
-        <v>57727</v>
+        <v>91538</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14058,34 +14063,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>583922</v>
+        <v>583789</v>
       </c>
       <c r="R128" t="n">
-        <v>7211662</v>
+        <v>7213129</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14112,17 +14117,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14137,22 +14137,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129000184</v>
+        <v>129000166</v>
       </c>
       <c r="B129" t="n">
-        <v>79041</v>
+        <v>91538</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14160,21 +14160,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14184,10 +14184,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>584333</v>
+        <v>583796</v>
       </c>
       <c r="R129" t="n">
-        <v>7211688</v>
+        <v>7211546</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14246,48 +14246,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129000185</v>
+        <v>129000168</v>
       </c>
       <c r="B130" t="n">
-        <v>92871</v>
+        <v>91538</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5964</v>
+        <v>1108</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>584074</v>
+        <v>584331</v>
       </c>
       <c r="R130" t="n">
-        <v>7211675</v>
+        <v>7211693</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14328,7 +14325,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14347,10 +14343,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129000166</v>
+        <v>129000184</v>
       </c>
       <c r="B131" t="n">
-        <v>91538</v>
+        <v>79041</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14358,21 +14354,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14382,10 +14378,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>583796</v>
+        <v>584333</v>
       </c>
       <c r="R131" t="n">
-        <v>7211546</v>
+        <v>7211688</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14444,45 +14440,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129000168</v>
+        <v>129000185</v>
       </c>
       <c r="B132" t="n">
-        <v>91538</v>
+        <v>92871</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1108</v>
+        <v>5964</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>584331</v>
+        <v>584074</v>
       </c>
       <c r="R132" t="n">
-        <v>7211693</v>
+        <v>7211675</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14523,6 +14522,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -15631,7 +15631,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129085077</v>
+        <v>129085080</v>
       </c>
       <c r="B144" t="n">
         <v>91542</v>
@@ -15666,10 +15666,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>583874</v>
+        <v>583726</v>
       </c>
       <c r="R144" t="n">
-        <v>7212775</v>
+        <v>7212315</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -15728,7 +15728,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129085080</v>
+        <v>129085077</v>
       </c>
       <c r="B145" t="n">
         <v>91542</v>
@@ -15763,10 +15763,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>583726</v>
+        <v>583874</v>
       </c>
       <c r="R145" t="n">
-        <v>7212315</v>
+        <v>7212775</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -16121,32 +16121,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129000159</v>
+        <v>129000106</v>
       </c>
       <c r="B149" t="n">
-        <v>56908</v>
+        <v>92242</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>102612</v>
+        <v>3298</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16156,10 +16156,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>583817</v>
+        <v>583634</v>
       </c>
       <c r="R149" t="n">
-        <v>7212328</v>
+        <v>7212397</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16218,32 +16218,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129000106</v>
+        <v>129000159</v>
       </c>
       <c r="B150" t="n">
-        <v>92242</v>
+        <v>56908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3298</v>
+        <v>102612</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16253,10 +16253,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>583634</v>
+        <v>583817</v>
       </c>
       <c r="R150" t="n">
-        <v>7212397</v>
+        <v>7212328</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16315,48 +16315,48 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129085088</v>
+        <v>129000178</v>
       </c>
       <c r="B151" t="n">
-        <v>97549</v>
+        <v>79041</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>583895</v>
+        <v>583707</v>
       </c>
       <c r="R151" t="n">
-        <v>7212319</v>
+        <v>7212347</v>
       </c>
       <c r="S151" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16400,60 +16400,60 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129000178</v>
+        <v>129085088</v>
       </c>
       <c r="B152" t="n">
-        <v>79041</v>
+        <v>97549</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>583707</v>
+        <v>583895</v>
       </c>
       <c r="R152" t="n">
-        <v>7212347</v>
+        <v>7212319</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16497,12 +16497,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16703,10 +16703,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129000149</v>
+        <v>129000189</v>
       </c>
       <c r="B155" t="n">
-        <v>97555</v>
+        <v>80181</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16714,21 +16714,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16738,10 +16738,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>583660</v>
+        <v>583856</v>
       </c>
       <c r="R155" t="n">
-        <v>7212365</v>
+        <v>7212375</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16800,10 +16800,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129000189</v>
+        <v>129000149</v>
       </c>
       <c r="B156" t="n">
-        <v>80181</v>
+        <v>97555</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16811,21 +16811,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6463</v>
+        <v>221941</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16835,10 +16835,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>583856</v>
+        <v>583660</v>
       </c>
       <c r="R156" t="n">
-        <v>7212375</v>
+        <v>7212365</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16897,10 +16897,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129085096</v>
+        <v>129000094</v>
       </c>
       <c r="B157" t="n">
-        <v>91560</v>
+        <v>83007</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16908,37 +16908,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>583522</v>
+        <v>583585</v>
       </c>
       <c r="R157" t="n">
-        <v>7212551</v>
+        <v>7212671</v>
       </c>
       <c r="S157" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16982,44 +16982,44 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129000094</v>
+        <v>129000188</v>
       </c>
       <c r="B158" t="n">
-        <v>83007</v>
+        <v>80181</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17029,10 +17029,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>583585</v>
+        <v>583606</v>
       </c>
       <c r="R158" t="n">
-        <v>7212671</v>
+        <v>7212484</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17091,32 +17091,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129000188</v>
+        <v>129000110</v>
       </c>
       <c r="B159" t="n">
-        <v>80181</v>
+        <v>57887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17126,10 +17126,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>583606</v>
+        <v>583842</v>
       </c>
       <c r="R159" t="n">
-        <v>7212484</v>
+        <v>7212868</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17188,10 +17188,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129000110</v>
+        <v>129085096</v>
       </c>
       <c r="B160" t="n">
-        <v>57887</v>
+        <v>91560</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17199,37 +17199,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>583842</v>
+        <v>583522</v>
       </c>
       <c r="R160" t="n">
-        <v>7212868</v>
+        <v>7212551</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17273,12 +17273,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17576,10 +17576,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129000153</v>
+        <v>129000177</v>
       </c>
       <c r="B164" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17587,37 +17587,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>583768</v>
+        <v>583609</v>
       </c>
       <c r="R164" t="n">
-        <v>7212826</v>
+        <v>7212495</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17658,24 +17655,8 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
@@ -17692,10 +17673,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129000177</v>
+        <v>129000153</v>
       </c>
       <c r="B165" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17703,34 +17684,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>583609</v>
+        <v>583768</v>
       </c>
       <c r="R165" t="n">
-        <v>7212495</v>
+        <v>7212826</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17771,8 +17755,24 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
@@ -17789,10 +17789,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129085074</v>
+        <v>129000114</v>
       </c>
       <c r="B166" t="n">
-        <v>105726</v>
+        <v>80175</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17800,37 +17800,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>583517</v>
+        <v>583606</v>
       </c>
       <c r="R166" t="n">
-        <v>7212494</v>
+        <v>7212483</v>
       </c>
       <c r="S166" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17874,19 +17874,19 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129085075</v>
+        <v>129085074</v>
       </c>
       <c r="B167" t="n">
         <v>105726</v>
@@ -17921,10 +17921,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>583896</v>
+        <v>583517</v>
       </c>
       <c r="R167" t="n">
-        <v>7212322</v>
+        <v>7212494</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -17983,10 +17983,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129000114</v>
+        <v>129085075</v>
       </c>
       <c r="B168" t="n">
-        <v>80175</v>
+        <v>105726</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17994,37 +17994,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>583606</v>
+        <v>583896</v>
       </c>
       <c r="R168" t="n">
-        <v>7212483</v>
+        <v>7212322</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18068,19 +18068,19 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129085078</v>
+        <v>129000104</v>
       </c>
       <c r="B169" t="n">
         <v>91542</v>
@@ -18111,17 +18111,17 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>583677</v>
+        <v>584023</v>
       </c>
       <c r="R169" t="n">
-        <v>7212815</v>
+        <v>7212353</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18165,19 +18165,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129000104</v>
+        <v>129085078</v>
       </c>
       <c r="B170" t="n">
         <v>91542</v>
@@ -18208,17 +18208,17 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>584023</v>
+        <v>583677</v>
       </c>
       <c r="R170" t="n">
-        <v>7212353</v>
+        <v>7212815</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18262,22 +18262,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129085099</v>
+        <v>129000170</v>
       </c>
       <c r="B171" t="n">
-        <v>79041</v>
+        <v>91556</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18285,37 +18285,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>583975</v>
+        <v>583844</v>
       </c>
       <c r="R171" t="n">
-        <v>7212333</v>
+        <v>7212348</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18359,22 +18359,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129000170</v>
+        <v>129000122</v>
       </c>
       <c r="B172" t="n">
-        <v>91556</v>
+        <v>80147</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18382,21 +18382,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18406,10 +18406,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>583844</v>
+        <v>583833</v>
       </c>
       <c r="R172" t="n">
-        <v>7212348</v>
+        <v>7212856</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18468,10 +18468,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129000122</v>
+        <v>129085099</v>
       </c>
       <c r="B173" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18479,37 +18479,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>583833</v>
+        <v>583975</v>
       </c>
       <c r="R173" t="n">
-        <v>7212856</v>
+        <v>7212333</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18553,12 +18553,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -18662,48 +18662,48 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129085083</v>
+        <v>129000124</v>
       </c>
       <c r="B175" t="n">
-        <v>80175</v>
+        <v>83012</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>583520</v>
+        <v>583770</v>
       </c>
       <c r="R175" t="n">
-        <v>7212517</v>
+        <v>7212830</v>
       </c>
       <c r="S175" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18747,22 +18747,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129085097</v>
+        <v>129000172</v>
       </c>
       <c r="B176" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18770,37 +18770,37 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>583788</v>
+        <v>583719</v>
       </c>
       <c r="R176" t="n">
-        <v>7212781</v>
+        <v>7212791</v>
       </c>
       <c r="S176" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -18844,22 +18844,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129000124</v>
+        <v>129085097</v>
       </c>
       <c r="B177" t="n">
-        <v>83012</v>
+        <v>79041</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18867,37 +18867,37 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>583770</v>
+        <v>583788</v>
       </c>
       <c r="R177" t="n">
-        <v>7212830</v>
+        <v>7212781</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -18941,60 +18941,60 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129000172</v>
+        <v>129085083</v>
       </c>
       <c r="B178" t="n">
-        <v>91560</v>
+        <v>80175</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>583719</v>
+        <v>583520</v>
       </c>
       <c r="R178" t="n">
-        <v>7212791</v>
+        <v>7212517</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19038,12 +19038,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
@@ -19147,48 +19147,48 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129085095</v>
+        <v>129073202</v>
       </c>
       <c r="B180" t="n">
-        <v>91560</v>
+        <v>95528</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5432</v>
+        <v>2387</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>583378</v>
+        <v>584165</v>
       </c>
       <c r="R180" t="n">
-        <v>7212728</v>
+        <v>7211601</v>
       </c>
       <c r="S180" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19212,12 +19212,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19232,60 +19232,60 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129073201</v>
+        <v>129085095</v>
       </c>
       <c r="B181" t="n">
-        <v>92332</v>
+        <v>91560</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>918</v>
+        <v>5432</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>583599</v>
+        <v>583378</v>
       </c>
       <c r="R181" t="n">
-        <v>7212710</v>
+        <v>7212728</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19329,44 +19329,44 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129073202</v>
+        <v>129000101</v>
       </c>
       <c r="B182" t="n">
-        <v>95528</v>
+        <v>91542</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2387</v>
+        <v>1202</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19376,10 +19376,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>584165</v>
+        <v>583663</v>
       </c>
       <c r="R182" t="n">
-        <v>7211601</v>
+        <v>7212429</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19406,12 +19406,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19431,17 +19431,17 @@
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129000101</v>
+        <v>129000129</v>
       </c>
       <c r="B183" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19449,21 +19449,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19473,10 +19473,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>583663</v>
+        <v>583810</v>
       </c>
       <c r="R183" t="n">
-        <v>7212429</v>
+        <v>7212852</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19535,32 +19535,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129000129</v>
+        <v>129073201</v>
       </c>
       <c r="B184" t="n">
-        <v>91827</v>
+        <v>92332</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>658</v>
+        <v>918</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19570,10 +19570,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>583810</v>
+        <v>583599</v>
       </c>
       <c r="R184" t="n">
-        <v>7212852</v>
+        <v>7212710</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19625,17 +19625,17 @@
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129085086</v>
+        <v>129000121</v>
       </c>
       <c r="B185" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19643,41 +19643,37 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>583569</v>
+        <v>583770</v>
       </c>
       <c r="R185" t="n">
-        <v>7212757</v>
+        <v>7212825</v>
       </c>
       <c r="S185" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19707,11 +19703,6 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19726,12 +19717,12 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
@@ -19835,48 +19826,48 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129000121</v>
+        <v>129085082</v>
       </c>
       <c r="B187" t="n">
-        <v>80147</v>
+        <v>80175</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>583770</v>
+        <v>583926</v>
       </c>
       <c r="R187" t="n">
-        <v>7212825</v>
+        <v>7212799</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19920,60 +19911,60 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129085082</v>
+        <v>129000132</v>
       </c>
       <c r="B188" t="n">
-        <v>80175</v>
+        <v>57727</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>583926</v>
+        <v>583968</v>
       </c>
       <c r="R188" t="n">
-        <v>7212799</v>
+        <v>7212362</v>
       </c>
       <c r="S188" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20003,6 +19994,11 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20017,39 +20013,39 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129085092</v>
+        <v>129085086</v>
       </c>
       <c r="B189" t="n">
-        <v>58097</v>
+        <v>57727</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -20058,16 +20054,20 @@
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>584017</v>
+        <v>583569</v>
       </c>
       <c r="R189" t="n">
-        <v>7212353</v>
+        <v>7212757</v>
       </c>
       <c r="S189" t="n">
         <v>15</v>
@@ -20102,6 +20102,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD189" t="b">
         <v>0</v>
       </c>
@@ -20119,34 +20124,34 @@
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129000132</v>
+        <v>129085092</v>
       </c>
       <c r="B190" t="n">
-        <v>57727</v>
+        <v>58097</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -20157,17 +20162,17 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>583968</v>
+        <v>584017</v>
       </c>
       <c r="R190" t="n">
-        <v>7212362</v>
+        <v>7212353</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20197,11 +20202,6 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20216,44 +20216,44 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129000154</v>
+        <v>129000162</v>
       </c>
       <c r="B191" t="n">
-        <v>80182</v>
+        <v>91538</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20263,10 +20263,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>583832</v>
+        <v>583583</v>
       </c>
       <c r="R191" t="n">
-        <v>7212853</v>
+        <v>7212676</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20325,32 +20325,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129000162</v>
+        <v>129000154</v>
       </c>
       <c r="B192" t="n">
-        <v>91538</v>
+        <v>80182</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20360,10 +20360,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>583583</v>
+        <v>583832</v>
       </c>
       <c r="R192" t="n">
-        <v>7212676</v>
+        <v>7212853</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>

--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -9728,32 +9728,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128998133</v>
+        <v>128998153</v>
       </c>
       <c r="B84" t="n">
-        <v>80147</v>
+        <v>80181</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9763,10 +9763,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>583743</v>
+        <v>583842</v>
       </c>
       <c r="R84" t="n">
-        <v>7212862</v>
+        <v>7212492</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9825,10 +9825,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129000145</v>
+        <v>128998133</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9836,34 +9836,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>583826</v>
+        <v>583743</v>
       </c>
       <c r="R85" t="n">
-        <v>7211682</v>
+        <v>7212862</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9890,12 +9890,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9910,57 +9910,57 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128998153</v>
+        <v>129000145</v>
       </c>
       <c r="B86" t="n">
-        <v>80181</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>583842</v>
+        <v>583826</v>
       </c>
       <c r="R86" t="n">
-        <v>7212492</v>
+        <v>7211682</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9987,12 +9987,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10007,12 +10007,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10910,7 +10910,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128998146</v>
+        <v>129000175</v>
       </c>
       <c r="B96" t="n">
         <v>91560</v>
@@ -10941,14 +10941,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>583700</v>
+        <v>583975</v>
       </c>
       <c r="R96" t="n">
-        <v>7212870</v>
+        <v>7211530</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10975,12 +10975,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10995,19 +10995,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129000175</v>
+        <v>128998146</v>
       </c>
       <c r="B97" t="n">
         <v>91560</v>
@@ -11038,14 +11038,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>583975</v>
+        <v>583700</v>
       </c>
       <c r="R97" t="n">
-        <v>7211530</v>
+        <v>7212870</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11072,12 +11072,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11092,12 +11092,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -11298,45 +11298,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128998136</v>
+        <v>129000150</v>
       </c>
       <c r="B100" t="n">
-        <v>80182</v>
+        <v>91912</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6464</v>
+        <v>1506</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>583838</v>
+        <v>583951</v>
       </c>
       <c r="R100" t="n">
-        <v>7212502</v>
+        <v>7211500</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11363,12 +11363,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11383,12 +11383,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11492,45 +11492,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129000150</v>
+        <v>128998136</v>
       </c>
       <c r="B102" t="n">
-        <v>91912</v>
+        <v>80182</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1506</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>583951</v>
+        <v>583838</v>
       </c>
       <c r="R102" t="n">
-        <v>7211500</v>
+        <v>7212502</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11557,12 +11557,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11577,12 +11577,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -13266,10 +13266,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129000169</v>
+        <v>128998129</v>
       </c>
       <c r="B120" t="n">
-        <v>82990</v>
+        <v>80175</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13277,34 +13277,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6439</v>
+        <v>6462</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>583695</v>
+        <v>583743</v>
       </c>
       <c r="R120" t="n">
-        <v>7211591</v>
+        <v>7212862</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13331,12 +13331,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13351,57 +13351,57 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129000144</v>
+        <v>128998154</v>
       </c>
       <c r="B121" t="n">
-        <v>57727</v>
+        <v>80181</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>583832</v>
+        <v>583743</v>
       </c>
       <c r="R121" t="n">
-        <v>7211693</v>
+        <v>7212862</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13428,17 +13428,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13453,12 +13448,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -13562,32 +13557,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128998129</v>
+        <v>128998151</v>
       </c>
       <c r="B123" t="n">
-        <v>80175</v>
+        <v>79041</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13597,10 +13592,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>583743</v>
+        <v>583830</v>
       </c>
       <c r="R123" t="n">
-        <v>7212862</v>
+        <v>7212605</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13659,10 +13654,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128998154</v>
+        <v>129000169</v>
       </c>
       <c r="B124" t="n">
-        <v>80181</v>
+        <v>82990</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13670,34 +13665,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6463</v>
+        <v>6439</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>583743</v>
+        <v>583695</v>
       </c>
       <c r="R124" t="n">
-        <v>7212862</v>
+        <v>7211591</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13724,12 +13719,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13744,22 +13739,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128998151</v>
+        <v>129000144</v>
       </c>
       <c r="B125" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13767,34 +13762,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>583830</v>
+        <v>583832</v>
       </c>
       <c r="R125" t="n">
-        <v>7212605</v>
+        <v>7211693</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13821,12 +13816,17 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13841,22 +13841,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129000180</v>
+        <v>129000142</v>
       </c>
       <c r="B126" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13864,21 +13864,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13888,10 +13888,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>583695</v>
+        <v>583922</v>
       </c>
       <c r="R126" t="n">
-        <v>7211621</v>
+        <v>7211662</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13924,6 +13924,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13950,10 +13955,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129000142</v>
+        <v>129000180</v>
       </c>
       <c r="B127" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13961,21 +13966,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13985,10 +13990,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>583922</v>
+        <v>583695</v>
       </c>
       <c r="R127" t="n">
-        <v>7211662</v>
+        <v>7211621</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14021,11 +14026,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14343,45 +14343,48 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129000184</v>
+        <v>129000185</v>
       </c>
       <c r="B131" t="n">
-        <v>79041</v>
+        <v>92871</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>584333</v>
+        <v>584074</v>
       </c>
       <c r="R131" t="n">
-        <v>7211688</v>
+        <v>7211675</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14422,6 +14425,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14440,48 +14444,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129000185</v>
+        <v>129000184</v>
       </c>
       <c r="B132" t="n">
-        <v>92871</v>
+        <v>79041</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>584074</v>
+        <v>584333</v>
       </c>
       <c r="R132" t="n">
-        <v>7211675</v>
+        <v>7211688</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14522,7 +14523,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -15132,32 +15132,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129000179</v>
+        <v>129000128</v>
       </c>
       <c r="B139" t="n">
-        <v>79041</v>
+        <v>91997</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15167,10 +15167,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>583976</v>
+        <v>583804</v>
       </c>
       <c r="R139" t="n">
-        <v>7212366</v>
+        <v>7212351</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15229,32 +15229,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129000128</v>
+        <v>129000179</v>
       </c>
       <c r="B140" t="n">
-        <v>91997</v>
+        <v>79041</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15264,10 +15264,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>583804</v>
+        <v>583976</v>
       </c>
       <c r="R140" t="n">
-        <v>7212351</v>
+        <v>7212366</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16315,48 +16315,48 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129000178</v>
+        <v>129085088</v>
       </c>
       <c r="B151" t="n">
-        <v>79041</v>
+        <v>97549</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>583707</v>
+        <v>583895</v>
       </c>
       <c r="R151" t="n">
-        <v>7212347</v>
+        <v>7212319</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16400,60 +16400,60 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129085088</v>
+        <v>129000178</v>
       </c>
       <c r="B152" t="n">
-        <v>97549</v>
+        <v>79041</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>583895</v>
+        <v>583707</v>
       </c>
       <c r="R152" t="n">
-        <v>7212319</v>
+        <v>7212347</v>
       </c>
       <c r="S152" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16497,60 +16497,60 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129085076</v>
+        <v>129000103</v>
       </c>
       <c r="B153" t="n">
-        <v>91506</v>
+        <v>91542</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>583540</v>
+        <v>583841</v>
       </c>
       <c r="R153" t="n">
-        <v>7212450</v>
+        <v>7212355</v>
       </c>
       <c r="S153" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16594,60 +16594,60 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129000103</v>
+        <v>129085076</v>
       </c>
       <c r="B154" t="n">
-        <v>91542</v>
+        <v>91506</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>583841</v>
+        <v>583540</v>
       </c>
       <c r="R154" t="n">
-        <v>7212355</v>
+        <v>7212450</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16691,12 +16691,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
@@ -16897,10 +16897,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129000094</v>
+        <v>129085096</v>
       </c>
       <c r="B157" t="n">
-        <v>83007</v>
+        <v>91560</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16908,37 +16908,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>583585</v>
+        <v>583522</v>
       </c>
       <c r="R157" t="n">
-        <v>7212671</v>
+        <v>7212551</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16982,44 +16982,44 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129000188</v>
+        <v>129000094</v>
       </c>
       <c r="B158" t="n">
-        <v>80181</v>
+        <v>83007</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17029,10 +17029,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>583606</v>
+        <v>583585</v>
       </c>
       <c r="R158" t="n">
-        <v>7212484</v>
+        <v>7212671</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17091,32 +17091,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129000110</v>
+        <v>129000188</v>
       </c>
       <c r="B159" t="n">
-        <v>57887</v>
+        <v>80181</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17126,10 +17126,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>583842</v>
+        <v>583606</v>
       </c>
       <c r="R159" t="n">
-        <v>7212868</v>
+        <v>7212484</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17188,10 +17188,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129085096</v>
+        <v>129000110</v>
       </c>
       <c r="B160" t="n">
-        <v>91560</v>
+        <v>57887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17199,37 +17199,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>583522</v>
+        <v>583842</v>
       </c>
       <c r="R160" t="n">
-        <v>7212551</v>
+        <v>7212868</v>
       </c>
       <c r="S160" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17273,12 +17273,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17789,10 +17789,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129000114</v>
+        <v>129085074</v>
       </c>
       <c r="B166" t="n">
-        <v>80175</v>
+        <v>105726</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17800,37 +17800,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>583606</v>
+        <v>583517</v>
       </c>
       <c r="R166" t="n">
-        <v>7212483</v>
+        <v>7212494</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17874,19 +17874,19 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129085074</v>
+        <v>129085075</v>
       </c>
       <c r="B167" t="n">
         <v>105726</v>
@@ -17921,10 +17921,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>583517</v>
+        <v>583896</v>
       </c>
       <c r="R167" t="n">
-        <v>7212494</v>
+        <v>7212322</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -17983,10 +17983,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129085075</v>
+        <v>129000114</v>
       </c>
       <c r="B168" t="n">
-        <v>105726</v>
+        <v>80175</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17994,37 +17994,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>583896</v>
+        <v>583606</v>
       </c>
       <c r="R168" t="n">
-        <v>7212322</v>
+        <v>7212483</v>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18068,12 +18068,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
@@ -18662,10 +18662,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129000124</v>
+        <v>129085097</v>
       </c>
       <c r="B175" t="n">
-        <v>83012</v>
+        <v>79041</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18673,37 +18673,37 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>583770</v>
+        <v>583788</v>
       </c>
       <c r="R175" t="n">
-        <v>7212830</v>
+        <v>7212781</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18747,60 +18747,60 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129000172</v>
+        <v>129085083</v>
       </c>
       <c r="B176" t="n">
-        <v>91560</v>
+        <v>80175</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>583719</v>
+        <v>583520</v>
       </c>
       <c r="R176" t="n">
-        <v>7212791</v>
+        <v>7212517</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -18844,22 +18844,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129085097</v>
+        <v>129000124</v>
       </c>
       <c r="B177" t="n">
-        <v>79041</v>
+        <v>83012</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18867,37 +18867,37 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>583788</v>
+        <v>583770</v>
       </c>
       <c r="R177" t="n">
-        <v>7212781</v>
+        <v>7212830</v>
       </c>
       <c r="S177" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -18941,60 +18941,60 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129085083</v>
+        <v>129000172</v>
       </c>
       <c r="B178" t="n">
-        <v>80175</v>
+        <v>91560</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>583520</v>
+        <v>583719</v>
       </c>
       <c r="R178" t="n">
-        <v>7212517</v>
+        <v>7212791</v>
       </c>
       <c r="S178" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19038,12 +19038,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
@@ -19341,32 +19341,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129000101</v>
+        <v>129073201</v>
       </c>
       <c r="B182" t="n">
-        <v>91542</v>
+        <v>92332</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1202</v>
+        <v>918</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19376,10 +19376,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>583663</v>
+        <v>583599</v>
       </c>
       <c r="R182" t="n">
-        <v>7212429</v>
+        <v>7212710</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19431,17 +19431,17 @@
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129000129</v>
+        <v>129000101</v>
       </c>
       <c r="B183" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19449,21 +19449,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19473,10 +19473,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>583810</v>
+        <v>583663</v>
       </c>
       <c r="R183" t="n">
-        <v>7212852</v>
+        <v>7212429</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19535,32 +19535,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129073201</v>
+        <v>129000129</v>
       </c>
       <c r="B184" t="n">
-        <v>92332</v>
+        <v>91827</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>918</v>
+        <v>658</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19570,10 +19570,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>583599</v>
+        <v>583810</v>
       </c>
       <c r="R184" t="n">
-        <v>7212710</v>
+        <v>7212852</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19625,7 +19625,7 @@
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>

--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -8276,7 +8276,7 @@
         <v>128998140</v>
       </c>
       <c r="B69" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8467,45 +8467,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128998142</v>
+        <v>128997038</v>
       </c>
       <c r="B71" t="n">
-        <v>91538</v>
+        <v>97581</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1108</v>
+        <v>221941</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>583800</v>
+        <v>583850</v>
       </c>
       <c r="R71" t="n">
-        <v>7212769</v>
+        <v>7212515</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8552,57 +8552,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129000183</v>
+        <v>128998122</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>105752</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>584220</v>
+        <v>583934</v>
       </c>
       <c r="R72" t="n">
-        <v>7211664</v>
+        <v>7212490</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8629,12 +8629,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8649,44 +8649,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128997038</v>
+        <v>129000183</v>
       </c>
       <c r="B73" t="n">
-        <v>97555</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8696,10 +8696,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583850</v>
+        <v>584220</v>
       </c>
       <c r="R73" t="n">
-        <v>7212515</v>
+        <v>7211664</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8726,12 +8726,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8746,44 +8746,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128998122</v>
+        <v>128998142</v>
       </c>
       <c r="B74" t="n">
-        <v>105726</v>
+        <v>91536</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221725</v>
+        <v>1108</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8793,10 +8793,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583934</v>
+        <v>583800</v>
       </c>
       <c r="R74" t="n">
-        <v>7212490</v>
+        <v>7212769</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8855,45 +8855,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129000152</v>
+        <v>128998128</v>
       </c>
       <c r="B75" t="n">
-        <v>80174</v>
+        <v>57887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>584338</v>
+        <v>583799</v>
       </c>
       <c r="R75" t="n">
-        <v>7211689</v>
+        <v>7212748</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8940,57 +8940,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128998128</v>
+        <v>129000152</v>
       </c>
       <c r="B76" t="n">
-        <v>57887</v>
+        <v>80174</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583799</v>
+        <v>584338</v>
       </c>
       <c r="R76" t="n">
-        <v>7212748</v>
+        <v>7211689</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9017,12 +9017,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9037,12 +9037,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9052,7 +9052,7 @@
         <v>128998124</v>
       </c>
       <c r="B77" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>128998135</v>
       </c>
       <c r="B78" t="n">
-        <v>91912</v>
+        <v>91921</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9340,10 +9340,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128998147</v>
+        <v>129000163</v>
       </c>
       <c r="B80" t="n">
-        <v>91560</v>
+        <v>91536</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9351,34 +9351,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583732</v>
+        <v>584005</v>
       </c>
       <c r="R80" t="n">
-        <v>7212858</v>
+        <v>7211652</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9425,12 +9425,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9534,10 +9534,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129000163</v>
+        <v>128998147</v>
       </c>
       <c r="B82" t="n">
-        <v>91538</v>
+        <v>91558</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9545,34 +9545,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>584005</v>
+        <v>583732</v>
       </c>
       <c r="R82" t="n">
-        <v>7211652</v>
+        <v>7212858</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9599,12 +9599,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9619,12 +9619,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9634,7 +9634,7 @@
         <v>129000141</v>
       </c>
       <c r="B83" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9728,10 +9728,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128998153</v>
+        <v>129000115</v>
       </c>
       <c r="B84" t="n">
-        <v>80181</v>
+        <v>80175</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9739,34 +9739,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>583842</v>
+        <v>583856</v>
       </c>
       <c r="R84" t="n">
-        <v>7212492</v>
+        <v>7212374</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9813,22 +9813,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128998133</v>
+        <v>129000145</v>
       </c>
       <c r="B85" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9836,34 +9836,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>583743</v>
+        <v>583826</v>
       </c>
       <c r="R85" t="n">
-        <v>7212862</v>
+        <v>7211682</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9890,12 +9890,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9910,22 +9910,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129000145</v>
+        <v>128998133</v>
       </c>
       <c r="B86" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9933,34 +9933,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>583826</v>
+        <v>583743</v>
       </c>
       <c r="R86" t="n">
-        <v>7211682</v>
+        <v>7212862</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9987,12 +9987,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10007,22 +10007,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129000115</v>
+        <v>128998153</v>
       </c>
       <c r="B87" t="n">
-        <v>80175</v>
+        <v>80181</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10030,34 +10030,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>583856</v>
+        <v>583842</v>
       </c>
       <c r="R87" t="n">
-        <v>7212374</v>
+        <v>7212492</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10104,12 +10104,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10119,7 +10119,7 @@
         <v>128998134</v>
       </c>
       <c r="B88" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10420,10 +10420,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129000116</v>
+        <v>128997040</v>
       </c>
       <c r="B91" t="n">
-        <v>57724</v>
+        <v>91536</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10431,21 +10431,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>584099</v>
+        <v>583800</v>
       </c>
       <c r="R91" t="n">
-        <v>7211521</v>
+        <v>7212621</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10485,17 +10485,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Spillkråkehack på låga</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10510,22 +10505,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129000165</v>
+        <v>128997035</v>
       </c>
       <c r="B92" t="n">
-        <v>91538</v>
+        <v>57887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10533,21 +10528,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10557,10 +10552,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>583888</v>
+        <v>583868</v>
       </c>
       <c r="R92" t="n">
-        <v>7211663</v>
+        <v>7212926</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10587,12 +10582,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10607,22 +10602,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128997040</v>
+        <v>129000165</v>
       </c>
       <c r="B93" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10654,10 +10649,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>583800</v>
+        <v>583888</v>
       </c>
       <c r="R93" t="n">
-        <v>7212621</v>
+        <v>7211663</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10684,12 +10679,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10704,57 +10699,57 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128997035</v>
+        <v>128998130</v>
       </c>
       <c r="B94" t="n">
-        <v>57887</v>
+        <v>80175</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>583868</v>
+        <v>583781</v>
       </c>
       <c r="R94" t="n">
-        <v>7212926</v>
+        <v>7212767</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10801,57 +10796,57 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128998130</v>
+        <v>129000116</v>
       </c>
       <c r="B95" t="n">
-        <v>80175</v>
+        <v>57724</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>583781</v>
+        <v>584099</v>
       </c>
       <c r="R95" t="n">
-        <v>7212767</v>
+        <v>7211521</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10878,12 +10873,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Spillkråkehack på låga</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10898,22 +10898,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129000175</v>
+        <v>128998150</v>
       </c>
       <c r="B96" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10921,34 +10921,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>583975</v>
+        <v>583862</v>
       </c>
       <c r="R96" t="n">
-        <v>7211530</v>
+        <v>7212466</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10975,12 +10975,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10995,22 +10995,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128998146</v>
+        <v>129000175</v>
       </c>
       <c r="B97" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11038,14 +11038,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>583700</v>
+        <v>583975</v>
       </c>
       <c r="R97" t="n">
-        <v>7212870</v>
+        <v>7211530</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11072,12 +11072,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11092,44 +11092,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128998155</v>
+        <v>128998146</v>
       </c>
       <c r="B98" t="n">
-        <v>80181</v>
+        <v>91558</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11139,10 +11139,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>583778</v>
+        <v>583700</v>
       </c>
       <c r="R98" t="n">
-        <v>7212766</v>
+        <v>7212870</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11201,27 +11201,27 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128998150</v>
+        <v>128998155</v>
       </c>
       <c r="B99" t="n">
-        <v>79041</v>
+        <v>80181</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -11236,10 +11236,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>583862</v>
+        <v>583778</v>
       </c>
       <c r="R99" t="n">
-        <v>7212466</v>
+        <v>7212766</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11298,45 +11298,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129000150</v>
+        <v>128998136</v>
       </c>
       <c r="B100" t="n">
-        <v>91912</v>
+        <v>80182</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1506</v>
+        <v>6464</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>583951</v>
+        <v>583838</v>
       </c>
       <c r="R100" t="n">
-        <v>7211500</v>
+        <v>7212502</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11363,12 +11363,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11383,57 +11383,57 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128998132</v>
+        <v>129000150</v>
       </c>
       <c r="B101" t="n">
-        <v>57724</v>
+        <v>91921</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>583834</v>
+        <v>583951</v>
       </c>
       <c r="R101" t="n">
-        <v>7212585</v>
+        <v>7211500</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11480,44 +11480,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128998136</v>
+        <v>128998132</v>
       </c>
       <c r="B102" t="n">
-        <v>80182</v>
+        <v>57724</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11527,10 +11527,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>583838</v>
+        <v>583834</v>
       </c>
       <c r="R102" t="n">
-        <v>7212502</v>
+        <v>7212585</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11592,7 +11592,7 @@
         <v>129000107</v>
       </c>
       <c r="B103" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11686,10 +11686,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129000126</v>
+        <v>128997039</v>
       </c>
       <c r="B104" t="n">
-        <v>83012</v>
+        <v>91536</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11697,21 +11697,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11721,10 +11721,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>583693</v>
+        <v>583807</v>
       </c>
       <c r="R104" t="n">
-        <v>7211591</v>
+        <v>7212750</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11751,12 +11751,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11771,19 +11771,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129000130</v>
+        <v>128998250</v>
       </c>
       <c r="B105" t="n">
         <v>57727</v>
@@ -11812,16 +11812,24 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>584350</v>
+        <v>583752</v>
       </c>
       <c r="R105" t="n">
-        <v>7211690</v>
+        <v>7212679</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11848,17 +11856,17 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Äldre och färska ringhack</t>
+          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11873,22 +11881,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128997039</v>
+        <v>129000126</v>
       </c>
       <c r="B106" t="n">
-        <v>91538</v>
+        <v>83012</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11896,21 +11904,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11920,10 +11928,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>583807</v>
+        <v>583693</v>
       </c>
       <c r="R106" t="n">
-        <v>7212750</v>
+        <v>7211591</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11950,12 +11958,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11970,19 +11978,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128998250</v>
+        <v>129000130</v>
       </c>
       <c r="B107" t="n">
         <v>57727</v>
@@ -12011,24 +12019,16 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>583752</v>
+        <v>584350</v>
       </c>
       <c r="R107" t="n">
-        <v>7212679</v>
+        <v>7211690</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12055,17 +12055,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
+          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12080,12 +12080,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12095,7 +12095,7 @@
         <v>129000147</v>
       </c>
       <c r="B108" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12189,45 +12189,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128998126</v>
+        <v>129000187</v>
       </c>
       <c r="B109" t="n">
-        <v>92242</v>
+        <v>88940</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3298</v>
+        <v>510</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>583748</v>
+        <v>583966</v>
       </c>
       <c r="R109" t="n">
-        <v>7212869</v>
+        <v>7211510</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12254,12 +12254,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12274,22 +12274,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129000157</v>
+        <v>128998126</v>
       </c>
       <c r="B110" t="n">
-        <v>57831</v>
+        <v>92257</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12297,34 +12297,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103031</v>
+        <v>3298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>583712</v>
+        <v>583748</v>
       </c>
       <c r="R110" t="n">
-        <v>7211576</v>
+        <v>7212869</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12351,12 +12351,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12371,22 +12371,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129000146</v>
+        <v>128998149</v>
       </c>
       <c r="B111" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12394,34 +12394,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>583819</v>
+        <v>584059</v>
       </c>
       <c r="R111" t="n">
-        <v>7211689</v>
+        <v>7212428</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12448,17 +12448,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12473,22 +12468,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128998149</v>
+        <v>129000146</v>
       </c>
       <c r="B112" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12496,34 +12491,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>584059</v>
+        <v>583819</v>
       </c>
       <c r="R112" t="n">
-        <v>7212428</v>
+        <v>7211689</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12550,12 +12545,17 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12570,44 +12570,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129000187</v>
+        <v>129000157</v>
       </c>
       <c r="B113" t="n">
-        <v>88939</v>
+        <v>57831</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>510</v>
+        <v>103031</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>583966</v>
+        <v>583712</v>
       </c>
       <c r="R113" t="n">
-        <v>7211510</v>
+        <v>7211576</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12779,7 +12779,7 @@
         <v>129000173</v>
       </c>
       <c r="B115" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13266,32 +13266,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128998129</v>
+        <v>128998151</v>
       </c>
       <c r="B120" t="n">
-        <v>80175</v>
+        <v>79041</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13301,10 +13301,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>583743</v>
+        <v>583830</v>
       </c>
       <c r="R120" t="n">
-        <v>7212862</v>
+        <v>7212605</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13363,10 +13363,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128998154</v>
+        <v>128998129</v>
       </c>
       <c r="B121" t="n">
-        <v>80181</v>
+        <v>80175</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13374,21 +13374,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13460,32 +13460,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128998148</v>
+        <v>128998154</v>
       </c>
       <c r="B122" t="n">
-        <v>91560</v>
+        <v>80181</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13495,10 +13495,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>583764</v>
+        <v>583743</v>
       </c>
       <c r="R122" t="n">
-        <v>7212875</v>
+        <v>7212862</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13557,10 +13557,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128998151</v>
+        <v>129000144</v>
       </c>
       <c r="B123" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13568,34 +13568,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>583830</v>
+        <v>583832</v>
       </c>
       <c r="R123" t="n">
-        <v>7212605</v>
+        <v>7211693</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13622,12 +13622,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13642,57 +13647,57 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129000169</v>
+        <v>128998148</v>
       </c>
       <c r="B124" t="n">
-        <v>82990</v>
+        <v>91558</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>583695</v>
+        <v>583764</v>
       </c>
       <c r="R124" t="n">
-        <v>7211591</v>
+        <v>7212875</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13719,12 +13724,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13739,44 +13744,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129000144</v>
+        <v>129000169</v>
       </c>
       <c r="B125" t="n">
-        <v>57727</v>
+        <v>82990</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13786,10 +13791,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>583832</v>
+        <v>583695</v>
       </c>
       <c r="R125" t="n">
-        <v>7211693</v>
+        <v>7211591</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13822,11 +13827,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13853,10 +13853,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129000142</v>
+        <v>128998141</v>
       </c>
       <c r="B126" t="n">
-        <v>57727</v>
+        <v>91536</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13864,34 +13864,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>583922</v>
+        <v>583789</v>
       </c>
       <c r="R126" t="n">
-        <v>7211662</v>
+        <v>7213129</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13918,17 +13918,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13943,22 +13938,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129000180</v>
+        <v>129000142</v>
       </c>
       <c r="B127" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13966,21 +13961,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13990,10 +13985,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>583695</v>
+        <v>583922</v>
       </c>
       <c r="R127" t="n">
-        <v>7211621</v>
+        <v>7211662</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14026,6 +14021,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14052,10 +14052,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128998141</v>
+        <v>129000180</v>
       </c>
       <c r="B128" t="n">
-        <v>91538</v>
+        <v>79041</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14063,34 +14063,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>583789</v>
+        <v>583695</v>
       </c>
       <c r="R128" t="n">
-        <v>7213129</v>
+        <v>7211621</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14117,12 +14117,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14137,12 +14137,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -14152,7 +14152,7 @@
         <v>129000166</v>
       </c>
       <c r="B129" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>129000168</v>
       </c>
       <c r="B130" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>129000185</v>
       </c>
       <c r="B131" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>129000174</v>
       </c>
       <c r="B133" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>129000167</v>
       </c>
       <c r="B134" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>129012557</v>
       </c>
       <c r="B136" t="n">
-        <v>88939</v>
+        <v>88940</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>129012558</v>
       </c>
       <c r="B137" t="n">
-        <v>92215</v>
+        <v>92230</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>129012556</v>
       </c>
       <c r="B138" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>129000128</v>
       </c>
       <c r="B139" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15152,12 +15152,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15229,10 +15229,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129000179</v>
+        <v>129000136</v>
       </c>
       <c r="B140" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15240,21 +15240,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15264,10 +15264,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>583976</v>
+        <v>583699</v>
       </c>
       <c r="R140" t="n">
-        <v>7212366</v>
+        <v>7212348</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15300,6 +15300,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15326,10 +15331,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129000136</v>
+        <v>129000179</v>
       </c>
       <c r="B141" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15337,21 +15342,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15361,10 +15366,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>583699</v>
+        <v>583976</v>
       </c>
       <c r="R141" t="n">
-        <v>7212348</v>
+        <v>7212366</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15397,11 +15402,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15631,10 +15631,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129085080</v>
+        <v>129000137</v>
       </c>
       <c r="B144" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15642,37 +15642,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>583726</v>
+        <v>583784</v>
       </c>
       <c r="R144" t="n">
-        <v>7212315</v>
+        <v>7212338</v>
       </c>
       <c r="S144" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15702,6 +15702,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15716,22 +15721,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129085077</v>
+        <v>129085080</v>
       </c>
       <c r="B145" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15763,10 +15768,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>583874</v>
+        <v>583726</v>
       </c>
       <c r="R145" t="n">
-        <v>7212775</v>
+        <v>7212315</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15825,10 +15830,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129000137</v>
+        <v>129085077</v>
       </c>
       <c r="B146" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15836,37 +15841,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>583784</v>
+        <v>583874</v>
       </c>
       <c r="R146" t="n">
-        <v>7212338</v>
+        <v>7212775</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15896,11 +15901,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15915,22 +15915,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129085094</v>
+        <v>129000159</v>
       </c>
       <c r="B147" t="n">
-        <v>91538</v>
+        <v>56908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15938,37 +15938,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>583526</v>
+        <v>583817</v>
       </c>
       <c r="R147" t="n">
-        <v>7212468</v>
+        <v>7212328</v>
       </c>
       <c r="S147" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16012,22 +16012,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129000171</v>
+        <v>129085094</v>
       </c>
       <c r="B148" t="n">
-        <v>91560</v>
+        <v>91536</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16035,37 +16035,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>583882</v>
+        <v>583526</v>
       </c>
       <c r="R148" t="n">
-        <v>7212369</v>
+        <v>7212468</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16109,44 +16109,44 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129000106</v>
+        <v>129000171</v>
       </c>
       <c r="B149" t="n">
-        <v>92242</v>
+        <v>91558</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16156,10 +16156,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>583634</v>
+        <v>583882</v>
       </c>
       <c r="R149" t="n">
-        <v>7212397</v>
+        <v>7212369</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16218,32 +16218,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129000159</v>
+        <v>129000106</v>
       </c>
       <c r="B150" t="n">
-        <v>56908</v>
+        <v>92257</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>102612</v>
+        <v>3298</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16253,10 +16253,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>583817</v>
+        <v>583634</v>
       </c>
       <c r="R150" t="n">
-        <v>7212328</v>
+        <v>7212397</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16315,48 +16315,48 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129085088</v>
+        <v>129000178</v>
       </c>
       <c r="B151" t="n">
-        <v>97549</v>
+        <v>79041</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>583895</v>
+        <v>583707</v>
       </c>
       <c r="R151" t="n">
-        <v>7212319</v>
+        <v>7212347</v>
       </c>
       <c r="S151" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16400,60 +16400,60 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129000178</v>
+        <v>129085088</v>
       </c>
       <c r="B152" t="n">
-        <v>79041</v>
+        <v>97575</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>583707</v>
+        <v>583895</v>
       </c>
       <c r="R152" t="n">
-        <v>7212347</v>
+        <v>7212319</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16497,12 +16497,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -16512,7 +16512,7 @@
         <v>129000103</v>
       </c>
       <c r="B153" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16606,10 +16606,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129085076</v>
+        <v>129000189</v>
       </c>
       <c r="B154" t="n">
-        <v>91506</v>
+        <v>80181</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16617,37 +16617,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>583540</v>
+        <v>583856</v>
       </c>
       <c r="R154" t="n">
-        <v>7212450</v>
+        <v>7212375</v>
       </c>
       <c r="S154" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16691,22 +16691,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129000189</v>
+        <v>129000149</v>
       </c>
       <c r="B155" t="n">
-        <v>80181</v>
+        <v>97581</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16714,21 +16714,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6463</v>
+        <v>221941</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16738,10 +16738,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>583856</v>
+        <v>583660</v>
       </c>
       <c r="R155" t="n">
-        <v>7212375</v>
+        <v>7212365</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16800,10 +16800,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129000149</v>
+        <v>129085076</v>
       </c>
       <c r="B156" t="n">
-        <v>97555</v>
+        <v>91504</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16811,37 +16811,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>583660</v>
+        <v>583540</v>
       </c>
       <c r="R156" t="n">
-        <v>7212365</v>
+        <v>7212450</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16885,22 +16885,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129085096</v>
+        <v>129000110</v>
       </c>
       <c r="B157" t="n">
-        <v>91560</v>
+        <v>57887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16908,37 +16908,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>583522</v>
+        <v>583842</v>
       </c>
       <c r="R157" t="n">
-        <v>7212551</v>
+        <v>7212868</v>
       </c>
       <c r="S157" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16982,44 +16982,44 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129000094</v>
+        <v>129000188</v>
       </c>
       <c r="B158" t="n">
-        <v>83007</v>
+        <v>80181</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17029,10 +17029,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>583585</v>
+        <v>583606</v>
       </c>
       <c r="R158" t="n">
-        <v>7212671</v>
+        <v>7212484</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17091,32 +17091,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129000188</v>
+        <v>129000094</v>
       </c>
       <c r="B159" t="n">
-        <v>80181</v>
+        <v>83007</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17126,10 +17126,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>583606</v>
+        <v>583585</v>
       </c>
       <c r="R159" t="n">
-        <v>7212484</v>
+        <v>7212671</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17188,10 +17188,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129000110</v>
+        <v>129085096</v>
       </c>
       <c r="B160" t="n">
-        <v>57887</v>
+        <v>91558</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17199,37 +17199,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>583842</v>
+        <v>583522</v>
       </c>
       <c r="R160" t="n">
-        <v>7212868</v>
+        <v>7212551</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17273,44 +17273,44 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129073200</v>
+        <v>129000100</v>
       </c>
       <c r="B161" t="n">
-        <v>91717</v>
+        <v>91504</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1588</v>
+        <v>5447</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17320,10 +17320,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>583712</v>
+        <v>583841</v>
       </c>
       <c r="R161" t="n">
-        <v>7211578</v>
+        <v>7212873</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17350,12 +17350,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17375,7 +17375,7 @@
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
@@ -17479,32 +17479,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129000100</v>
+        <v>129073200</v>
       </c>
       <c r="B163" t="n">
-        <v>91506</v>
+        <v>91726</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5447</v>
+        <v>1588</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17514,10 +17514,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>583841</v>
+        <v>583712</v>
       </c>
       <c r="R163" t="n">
-        <v>7212873</v>
+        <v>7211578</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17544,12 +17544,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17569,7 +17569,7 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
@@ -17789,10 +17789,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129085074</v>
+        <v>129000114</v>
       </c>
       <c r="B166" t="n">
-        <v>105726</v>
+        <v>80175</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17800,37 +17800,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>583517</v>
+        <v>583606</v>
       </c>
       <c r="R166" t="n">
-        <v>7212494</v>
+        <v>7212483</v>
       </c>
       <c r="S166" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17874,22 +17874,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129085075</v>
+        <v>129085074</v>
       </c>
       <c r="B167" t="n">
-        <v>105726</v>
+        <v>105752</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17921,10 +17921,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>583896</v>
+        <v>583517</v>
       </c>
       <c r="R167" t="n">
-        <v>7212322</v>
+        <v>7212494</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -17983,10 +17983,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129000114</v>
+        <v>129085075</v>
       </c>
       <c r="B168" t="n">
-        <v>80175</v>
+        <v>105752</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17994,37 +17994,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>583606</v>
+        <v>583896</v>
       </c>
       <c r="R168" t="n">
-        <v>7212483</v>
+        <v>7212322</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18068,12 +18068,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
@@ -18083,7 +18083,7 @@
         <v>129000104</v>
       </c>
       <c r="B169" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>129085078</v>
       </c>
       <c r="B170" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18274,10 +18274,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129000170</v>
+        <v>129000122</v>
       </c>
       <c r="B171" t="n">
-        <v>91556</v>
+        <v>80147</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18285,21 +18285,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>583844</v>
+        <v>583833</v>
       </c>
       <c r="R171" t="n">
-        <v>7212348</v>
+        <v>7212856</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18371,10 +18371,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129000122</v>
+        <v>129000170</v>
       </c>
       <c r="B172" t="n">
-        <v>80147</v>
+        <v>91554</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18382,21 +18382,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18406,10 +18406,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>583833</v>
+        <v>583844</v>
       </c>
       <c r="R172" t="n">
-        <v>7212856</v>
+        <v>7212348</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18662,10 +18662,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129085097</v>
+        <v>129000124</v>
       </c>
       <c r="B175" t="n">
-        <v>79041</v>
+        <v>83012</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18673,37 +18673,37 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>583788</v>
+        <v>583770</v>
       </c>
       <c r="R175" t="n">
-        <v>7212781</v>
+        <v>7212830</v>
       </c>
       <c r="S175" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18747,60 +18747,60 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129085083</v>
+        <v>129000172</v>
       </c>
       <c r="B176" t="n">
-        <v>80175</v>
+        <v>91558</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>583520</v>
+        <v>583719</v>
       </c>
       <c r="R176" t="n">
-        <v>7212517</v>
+        <v>7212791</v>
       </c>
       <c r="S176" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -18844,22 +18844,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129000124</v>
+        <v>129085097</v>
       </c>
       <c r="B177" t="n">
-        <v>83012</v>
+        <v>79041</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18867,37 +18867,37 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>583770</v>
+        <v>583788</v>
       </c>
       <c r="R177" t="n">
-        <v>7212830</v>
+        <v>7212781</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -18941,60 +18941,60 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129000172</v>
+        <v>129085083</v>
       </c>
       <c r="B178" t="n">
-        <v>91560</v>
+        <v>80175</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>583719</v>
+        <v>583520</v>
       </c>
       <c r="R178" t="n">
-        <v>7212791</v>
+        <v>7212517</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19038,12 +19038,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
@@ -19053,7 +19053,7 @@
         <v>129085079</v>
       </c>
       <c r="B179" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19147,32 +19147,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129073202</v>
+        <v>129000101</v>
       </c>
       <c r="B180" t="n">
-        <v>95528</v>
+        <v>91540</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>2387</v>
+        <v>1202</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19182,10 +19182,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>584165</v>
+        <v>583663</v>
       </c>
       <c r="R180" t="n">
-        <v>7211601</v>
+        <v>7212429</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19212,12 +19212,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19237,17 +19237,17 @@
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129085095</v>
+        <v>129000129</v>
       </c>
       <c r="B181" t="n">
-        <v>91560</v>
+        <v>91837</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19255,37 +19255,37 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>583378</v>
+        <v>583810</v>
       </c>
       <c r="R181" t="n">
-        <v>7212728</v>
+        <v>7212852</v>
       </c>
       <c r="S181" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19329,12 +19329,12 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
@@ -19344,7 +19344,7 @@
         <v>129073201</v>
       </c>
       <c r="B182" t="n">
-        <v>92332</v>
+        <v>92346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19438,32 +19438,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129000101</v>
+        <v>129073202</v>
       </c>
       <c r="B183" t="n">
-        <v>91542</v>
+        <v>95554</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1202</v>
+        <v>2387</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19473,10 +19473,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>583663</v>
+        <v>584165</v>
       </c>
       <c r="R183" t="n">
-        <v>7212429</v>
+        <v>7211601</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19503,12 +19503,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19528,17 +19528,17 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129000129</v>
+        <v>129085095</v>
       </c>
       <c r="B184" t="n">
-        <v>91827</v>
+        <v>91558</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19546,37 +19546,37 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>583810</v>
+        <v>583378</v>
       </c>
       <c r="R184" t="n">
-        <v>7212852</v>
+        <v>7212728</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19620,22 +19620,22 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129000121</v>
+        <v>129085086</v>
       </c>
       <c r="B185" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19643,37 +19643,41 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>583770</v>
+        <v>583569</v>
       </c>
       <c r="R185" t="n">
-        <v>7212825</v>
+        <v>7212757</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19703,6 +19707,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19717,60 +19726,60 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129000160</v>
+        <v>129085082</v>
       </c>
       <c r="B186" t="n">
-        <v>91538</v>
+        <v>80175</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>583674</v>
+        <v>583926</v>
       </c>
       <c r="R186" t="n">
-        <v>7212755</v>
+        <v>7212799</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19814,22 +19823,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129085082</v>
+        <v>129085092</v>
       </c>
       <c r="B187" t="n">
-        <v>80175</v>
+        <v>58097</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19837,21 +19846,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6462</v>
+        <v>103015</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19861,10 +19870,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>583926</v>
+        <v>584017</v>
       </c>
       <c r="R187" t="n">
-        <v>7212799</v>
+        <v>7212353</v>
       </c>
       <c r="S187" t="n">
         <v>15</v>
@@ -19916,7 +19925,7 @@
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
@@ -20025,10 +20034,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129085086</v>
+        <v>129000121</v>
       </c>
       <c r="B189" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20036,41 +20045,37 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>583569</v>
+        <v>583770</v>
       </c>
       <c r="R189" t="n">
-        <v>7212757</v>
+        <v>7212825</v>
       </c>
       <c r="S189" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20100,11 +20105,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20119,60 +20119,60 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129085092</v>
+        <v>129000160</v>
       </c>
       <c r="B190" t="n">
-        <v>58097</v>
+        <v>91536</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>584017</v>
+        <v>583674</v>
       </c>
       <c r="R190" t="n">
-        <v>7212353</v>
+        <v>7212755</v>
       </c>
       <c r="S190" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20216,44 +20216,44 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129000162</v>
+        <v>129000154</v>
       </c>
       <c r="B191" t="n">
-        <v>91538</v>
+        <v>80182</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20263,10 +20263,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>583583</v>
+        <v>583832</v>
       </c>
       <c r="R191" t="n">
-        <v>7212676</v>
+        <v>7212853</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20325,32 +20325,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129000154</v>
+        <v>129000162</v>
       </c>
       <c r="B192" t="n">
-        <v>80182</v>
+        <v>91536</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20360,10 +20360,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>583832</v>
+        <v>583583</v>
       </c>
       <c r="R192" t="n">
-        <v>7212853</v>
+        <v>7212676</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>

--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -8171,45 +8171,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129000140</v>
+        <v>128998144</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>82990</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>584092</v>
+        <v>583765</v>
       </c>
       <c r="R68" t="n">
-        <v>7211517</v>
+        <v>7212611</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8236,17 +8236,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8261,22 +8256,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128998140</v>
+        <v>129000140</v>
       </c>
       <c r="B69" t="n">
-        <v>91536</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8284,34 +8279,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>583855</v>
+        <v>584092</v>
       </c>
       <c r="R69" t="n">
-        <v>7213081</v>
+        <v>7211517</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8338,12 +8333,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8358,44 +8358,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128998144</v>
+        <v>128998140</v>
       </c>
       <c r="B70" t="n">
-        <v>82990</v>
+        <v>91536</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6439</v>
+        <v>1108</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583765</v>
+        <v>583855</v>
       </c>
       <c r="R70" t="n">
-        <v>7212611</v>
+        <v>7213081</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8467,32 +8467,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128997038</v>
+        <v>129000183</v>
       </c>
       <c r="B71" t="n">
-        <v>97581</v>
+        <v>79041</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>583850</v>
+        <v>584220</v>
       </c>
       <c r="R71" t="n">
-        <v>7212515</v>
+        <v>7211664</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8532,12 +8532,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8552,44 +8552,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128998122</v>
+        <v>128998142</v>
       </c>
       <c r="B72" t="n">
-        <v>105752</v>
+        <v>91536</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>1108</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8599,10 +8599,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583934</v>
+        <v>583800</v>
       </c>
       <c r="R72" t="n">
-        <v>7212490</v>
+        <v>7212769</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8661,32 +8661,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129000183</v>
+        <v>128997038</v>
       </c>
       <c r="B73" t="n">
-        <v>79041</v>
+        <v>97582</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8696,10 +8696,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>584220</v>
+        <v>583850</v>
       </c>
       <c r="R73" t="n">
-        <v>7211664</v>
+        <v>7212515</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8726,12 +8726,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8746,44 +8746,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128998142</v>
+        <v>128998122</v>
       </c>
       <c r="B74" t="n">
-        <v>91536</v>
+        <v>105754</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1108</v>
+        <v>221725</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8793,10 +8793,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583800</v>
+        <v>583934</v>
       </c>
       <c r="R74" t="n">
-        <v>7212769</v>
+        <v>7212490</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9049,10 +9049,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128998124</v>
+        <v>128998131</v>
       </c>
       <c r="B77" t="n">
-        <v>91540</v>
+        <v>57724</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9060,21 +9060,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583784</v>
+        <v>584025</v>
       </c>
       <c r="R77" t="n">
-        <v>7212884</v>
+        <v>7212370</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9146,32 +9146,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128998135</v>
+        <v>128998124</v>
       </c>
       <c r="B78" t="n">
-        <v>91921</v>
+        <v>91540</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>583778</v>
+        <v>583784</v>
       </c>
       <c r="R78" t="n">
-        <v>7212890</v>
+        <v>7212884</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9243,32 +9243,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128998131</v>
+        <v>128998135</v>
       </c>
       <c r="B79" t="n">
-        <v>57724</v>
+        <v>91922</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>584025</v>
+        <v>583778</v>
       </c>
       <c r="R79" t="n">
-        <v>7212370</v>
+        <v>7212890</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9340,10 +9340,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129000163</v>
+        <v>128998147</v>
       </c>
       <c r="B80" t="n">
-        <v>91536</v>
+        <v>91560</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9351,34 +9351,30 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>584005</v>
+        <v>583732</v>
       </c>
       <c r="R80" t="n">
-        <v>7211652</v>
+        <v>7212858</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9405,12 +9401,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9425,22 +9421,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129000181</v>
+        <v>129000163</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>91536</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9448,21 +9444,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9472,10 +9468,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583824</v>
+        <v>584005</v>
       </c>
       <c r="R81" t="n">
-        <v>7211526</v>
+        <v>7211652</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9534,10 +9530,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128998147</v>
+        <v>129000181</v>
       </c>
       <c r="B82" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9545,34 +9541,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>583732</v>
+        <v>583824</v>
       </c>
       <c r="R82" t="n">
-        <v>7212858</v>
+        <v>7211526</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9599,12 +9595,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9619,12 +9615,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9634,7 +9630,7 @@
         <v>129000141</v>
       </c>
       <c r="B83" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9728,45 +9724,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129000115</v>
+        <v>128998133</v>
       </c>
       <c r="B84" t="n">
-        <v>80175</v>
+        <v>80147</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>583856</v>
+        <v>583743</v>
       </c>
       <c r="R84" t="n">
-        <v>7212374</v>
+        <v>7212862</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9813,57 +9809,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129000145</v>
+        <v>128998153</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>80181</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>583826</v>
+        <v>583842</v>
       </c>
       <c r="R85" t="n">
-        <v>7211682</v>
+        <v>7212492</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9890,12 +9886,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9910,22 +9906,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128998133</v>
+        <v>129000145</v>
       </c>
       <c r="B86" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9933,34 +9929,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>583743</v>
+        <v>583826</v>
       </c>
       <c r="R86" t="n">
-        <v>7212862</v>
+        <v>7211682</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9987,12 +9983,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10007,22 +10003,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128998153</v>
+        <v>129000115</v>
       </c>
       <c r="B87" t="n">
-        <v>80181</v>
+        <v>80175</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10030,34 +10026,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>583842</v>
+        <v>583856</v>
       </c>
       <c r="R87" t="n">
-        <v>7212492</v>
+        <v>7212374</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10104,12 +10100,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10119,7 +10115,7 @@
         <v>128998134</v>
       </c>
       <c r="B88" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10517,45 +10513,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128997035</v>
+        <v>128998130</v>
       </c>
       <c r="B92" t="n">
-        <v>57887</v>
+        <v>80175</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>583868</v>
+        <v>583781</v>
       </c>
       <c r="R92" t="n">
-        <v>7212926</v>
+        <v>7212767</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10602,22 +10598,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129000165</v>
+        <v>128997035</v>
       </c>
       <c r="B93" t="n">
-        <v>91536</v>
+        <v>57887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10625,21 +10621,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10649,10 +10645,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>583888</v>
+        <v>583868</v>
       </c>
       <c r="R93" t="n">
-        <v>7211663</v>
+        <v>7212926</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10679,12 +10675,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10699,57 +10695,57 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128998130</v>
+        <v>129000165</v>
       </c>
       <c r="B94" t="n">
-        <v>80175</v>
+        <v>91536</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>583781</v>
+        <v>583888</v>
       </c>
       <c r="R94" t="n">
-        <v>7212767</v>
+        <v>7211663</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10776,12 +10772,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10796,12 +10792,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11007,10 +11003,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129000175</v>
+        <v>128998146</v>
       </c>
       <c r="B97" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11027,25 +11023,21 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>583975</v>
+        <v>583700</v>
       </c>
       <c r="R97" t="n">
-        <v>7211530</v>
+        <v>7212870</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11072,12 +11064,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11092,44 +11084,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128998146</v>
+        <v>128998155</v>
       </c>
       <c r="B98" t="n">
-        <v>91558</v>
+        <v>80181</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11139,10 +11131,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>583700</v>
+        <v>583778</v>
       </c>
       <c r="R98" t="n">
-        <v>7212870</v>
+        <v>7212766</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11201,45 +11193,41 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128998155</v>
+        <v>129000175</v>
       </c>
       <c r="B99" t="n">
-        <v>80181</v>
+        <v>91560</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>583778</v>
+        <v>583975</v>
       </c>
       <c r="R99" t="n">
-        <v>7212766</v>
+        <v>7211530</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11266,12 +11254,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11286,44 +11274,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128998136</v>
+        <v>128998132</v>
       </c>
       <c r="B100" t="n">
-        <v>80182</v>
+        <v>57724</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11333,10 +11321,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>583838</v>
+        <v>583834</v>
       </c>
       <c r="R100" t="n">
-        <v>7212502</v>
+        <v>7212585</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11398,7 +11386,7 @@
         <v>129000150</v>
       </c>
       <c r="B101" t="n">
-        <v>91921</v>
+        <v>91922</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11492,32 +11480,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128998132</v>
+        <v>128998136</v>
       </c>
       <c r="B102" t="n">
-        <v>57724</v>
+        <v>80182</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11527,10 +11515,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>583834</v>
+        <v>583838</v>
       </c>
       <c r="R102" t="n">
-        <v>7212585</v>
+        <v>7212502</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11592,7 +11580,7 @@
         <v>129000107</v>
       </c>
       <c r="B103" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11686,10 +11674,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128997039</v>
+        <v>129000130</v>
       </c>
       <c r="B104" t="n">
-        <v>91536</v>
+        <v>57727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11697,21 +11685,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11721,10 +11709,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>583807</v>
+        <v>584350</v>
       </c>
       <c r="R104" t="n">
-        <v>7212750</v>
+        <v>7211690</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11751,12 +11739,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11771,22 +11764,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128998250</v>
+        <v>128997039</v>
       </c>
       <c r="B105" t="n">
-        <v>57727</v>
+        <v>91536</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11794,42 +11787,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>583752</v>
+        <v>583807</v>
       </c>
       <c r="R105" t="n">
-        <v>7212679</v>
+        <v>7212750</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11864,11 +11849,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -11881,12 +11861,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11990,7 +11970,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129000130</v>
+        <v>128998250</v>
       </c>
       <c r="B107" t="n">
         <v>57727</v>
@@ -12019,16 +11999,24 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>584350</v>
+        <v>583752</v>
       </c>
       <c r="R107" t="n">
-        <v>7211690</v>
+        <v>7212679</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12055,17 +12043,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Äldre och färska ringhack</t>
+          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12080,12 +12068,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12095,7 +12083,7 @@
         <v>129000147</v>
       </c>
       <c r="B108" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12189,10 +12177,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129000187</v>
+        <v>128998149</v>
       </c>
       <c r="B109" t="n">
-        <v>88940</v>
+        <v>79041</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12200,34 +12188,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>583966</v>
+        <v>584059</v>
       </c>
       <c r="R109" t="n">
-        <v>7211510</v>
+        <v>7212428</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12254,12 +12242,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12274,12 +12262,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12289,7 +12277,7 @@
         <v>128998126</v>
       </c>
       <c r="B110" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12383,10 +12371,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128998149</v>
+        <v>129000187</v>
       </c>
       <c r="B111" t="n">
-        <v>79041</v>
+        <v>88940</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12394,34 +12382,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>584059</v>
+        <v>583966</v>
       </c>
       <c r="R111" t="n">
-        <v>7212428</v>
+        <v>7211510</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12448,12 +12436,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12468,39 +12456,39 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129000146</v>
+        <v>129000157</v>
       </c>
       <c r="B112" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -12515,10 +12503,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>583819</v>
+        <v>583712</v>
       </c>
       <c r="R112" t="n">
-        <v>7211689</v>
+        <v>7211576</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12551,11 +12539,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12582,27 +12565,27 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129000157</v>
+        <v>129000146</v>
       </c>
       <c r="B113" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -12617,10 +12600,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>583712</v>
+        <v>583819</v>
       </c>
       <c r="R113" t="n">
-        <v>7211576</v>
+        <v>7211689</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12653,6 +12636,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12779,7 +12767,7 @@
         <v>129000173</v>
       </c>
       <c r="B115" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12796,14 +12784,10 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12873,32 +12857,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129000182</v>
+        <v>129000119</v>
       </c>
       <c r="B116" t="n">
-        <v>79041</v>
+        <v>83005</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12908,10 +12892,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>584124</v>
+        <v>583763</v>
       </c>
       <c r="R116" t="n">
-        <v>7211556</v>
+        <v>7211568</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12970,10 +12954,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129000097</v>
+        <v>129000182</v>
       </c>
       <c r="B117" t="n">
-        <v>83007</v>
+        <v>79041</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12981,21 +12965,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13005,10 +12989,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>584170</v>
+        <v>584124</v>
       </c>
       <c r="R117" t="n">
-        <v>7211600</v>
+        <v>7211556</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13067,32 +13051,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129000119</v>
+        <v>129000097</v>
       </c>
       <c r="B118" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6486</v>
+        <v>6440</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13102,10 +13086,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>583763</v>
+        <v>584170</v>
       </c>
       <c r="R118" t="n">
-        <v>7211568</v>
+        <v>7211600</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13266,10 +13250,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128998151</v>
+        <v>128998148</v>
       </c>
       <c r="B120" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13277,23 +13261,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -13301,10 +13281,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>583830</v>
+        <v>583764</v>
       </c>
       <c r="R120" t="n">
-        <v>7212605</v>
+        <v>7212875</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13557,10 +13537,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129000144</v>
+        <v>128998151</v>
       </c>
       <c r="B123" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13568,34 +13548,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>583832</v>
+        <v>583830</v>
       </c>
       <c r="R123" t="n">
-        <v>7211693</v>
+        <v>7212605</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13622,17 +13602,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13647,57 +13622,57 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128998148</v>
+        <v>129000169</v>
       </c>
       <c r="B124" t="n">
-        <v>91558</v>
+        <v>82990</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>583764</v>
+        <v>583695</v>
       </c>
       <c r="R124" t="n">
-        <v>7212875</v>
+        <v>7211591</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13724,12 +13699,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13744,44 +13719,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129000169</v>
+        <v>129000144</v>
       </c>
       <c r="B125" t="n">
-        <v>82990</v>
+        <v>57727</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13791,10 +13766,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>583695</v>
+        <v>583832</v>
       </c>
       <c r="R125" t="n">
-        <v>7211591</v>
+        <v>7211693</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13827,6 +13802,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13853,10 +13833,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128998141</v>
+        <v>129000180</v>
       </c>
       <c r="B126" t="n">
-        <v>91536</v>
+        <v>79041</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13864,34 +13844,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>583789</v>
+        <v>583695</v>
       </c>
       <c r="R126" t="n">
-        <v>7213129</v>
+        <v>7211621</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13918,12 +13898,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13938,12 +13918,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -14052,10 +14032,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129000180</v>
+        <v>128998141</v>
       </c>
       <c r="B128" t="n">
-        <v>79041</v>
+        <v>91536</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14063,34 +14043,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>583695</v>
+        <v>583789</v>
       </c>
       <c r="R128" t="n">
-        <v>7211621</v>
+        <v>7213129</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14117,12 +14097,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14137,12 +14117,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -14346,7 +14326,7 @@
         <v>129000185</v>
       </c>
       <c r="B131" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14541,10 +14521,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129000174</v>
+        <v>129000167</v>
       </c>
       <c r="B133" t="n">
-        <v>91558</v>
+        <v>91536</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14552,21 +14532,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14576,10 +14556,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>583934</v>
+        <v>584144</v>
       </c>
       <c r="R133" t="n">
-        <v>7211520</v>
+        <v>7211566</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14638,10 +14618,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129000167</v>
+        <v>129000174</v>
       </c>
       <c r="B134" t="n">
-        <v>91536</v>
+        <v>91560</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14649,23 +14629,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -14673,10 +14649,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>584144</v>
+        <v>583934</v>
       </c>
       <c r="R134" t="n">
-        <v>7211566</v>
+        <v>7211520</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14937,7 +14913,7 @@
         <v>129012558</v>
       </c>
       <c r="B137" t="n">
-        <v>92230</v>
+        <v>92231</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15034,7 +15010,7 @@
         <v>129012556</v>
       </c>
       <c r="B138" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15132,32 +15108,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129000128</v>
+        <v>129000136</v>
       </c>
       <c r="B139" t="n">
-        <v>91992</v>
+        <v>57727</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15167,10 +15143,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>583804</v>
+        <v>583699</v>
       </c>
       <c r="R139" t="n">
-        <v>7212351</v>
+        <v>7212348</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15203,6 +15179,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15229,32 +15210,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129000136</v>
+        <v>129000128</v>
       </c>
       <c r="B140" t="n">
-        <v>57727</v>
+        <v>91993</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15264,10 +15245,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>583699</v>
+        <v>583804</v>
       </c>
       <c r="R140" t="n">
-        <v>7212348</v>
+        <v>7212351</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15300,11 +15281,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15927,10 +15903,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129000159</v>
+        <v>129085094</v>
       </c>
       <c r="B147" t="n">
-        <v>56908</v>
+        <v>91536</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15938,37 +15914,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>583817</v>
+        <v>583526</v>
       </c>
       <c r="R147" t="n">
-        <v>7212328</v>
+        <v>7212468</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16012,60 +15988,60 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129085094</v>
+        <v>129000106</v>
       </c>
       <c r="B148" t="n">
-        <v>91536</v>
+        <v>92258</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>583526</v>
+        <v>583634</v>
       </c>
       <c r="R148" t="n">
-        <v>7212468</v>
+        <v>7212397</v>
       </c>
       <c r="S148" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16109,12 +16085,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -16124,7 +16100,7 @@
         <v>129000171</v>
       </c>
       <c r="B149" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16141,14 +16117,10 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
@@ -16218,32 +16190,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129000106</v>
+        <v>129000159</v>
       </c>
       <c r="B150" t="n">
-        <v>92257</v>
+        <v>56908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3298</v>
+        <v>102612</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16253,10 +16225,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>583634</v>
+        <v>583817</v>
       </c>
       <c r="R150" t="n">
-        <v>7212397</v>
+        <v>7212328</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16415,7 +16387,7 @@
         <v>129085088</v>
       </c>
       <c r="B152" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16706,7 +16678,7 @@
         <v>129000149</v>
       </c>
       <c r="B155" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16994,32 +16966,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129000188</v>
+        <v>129000094</v>
       </c>
       <c r="B158" t="n">
-        <v>80181</v>
+        <v>83007</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17029,10 +17001,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>583606</v>
+        <v>583585</v>
       </c>
       <c r="R158" t="n">
-        <v>7212484</v>
+        <v>7212671</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17091,32 +17063,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129000094</v>
+        <v>129000188</v>
       </c>
       <c r="B159" t="n">
-        <v>83007</v>
+        <v>80181</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17126,10 +17098,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>583585</v>
+        <v>583606</v>
       </c>
       <c r="R159" t="n">
-        <v>7212671</v>
+        <v>7212484</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17191,7 +17163,7 @@
         <v>129085096</v>
       </c>
       <c r="B160" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17208,14 +17180,10 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
@@ -17285,32 +17253,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129000100</v>
+        <v>129073200</v>
       </c>
       <c r="B161" t="n">
-        <v>91504</v>
+        <v>91727</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5447</v>
+        <v>1588</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17320,10 +17288,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>583841</v>
+        <v>583712</v>
       </c>
       <c r="R161" t="n">
-        <v>7212873</v>
+        <v>7211578</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17350,12 +17318,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17375,39 +17343,39 @@
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129000096</v>
+        <v>129000100</v>
       </c>
       <c r="B162" t="n">
-        <v>83007</v>
+        <v>91504</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17417,10 +17385,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>583980</v>
+        <v>583841</v>
       </c>
       <c r="R162" t="n">
-        <v>7212363</v>
+        <v>7212873</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17479,10 +17447,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129073200</v>
+        <v>129000096</v>
       </c>
       <c r="B163" t="n">
-        <v>91726</v>
+        <v>83007</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17490,21 +17458,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1588</v>
+        <v>6440</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17514,10 +17482,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>583712</v>
+        <v>583980</v>
       </c>
       <c r="R163" t="n">
-        <v>7211578</v>
+        <v>7212363</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17544,12 +17512,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17569,17 +17537,17 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129000177</v>
+        <v>129000153</v>
       </c>
       <c r="B164" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17587,34 +17555,37 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>583609</v>
+        <v>583768</v>
       </c>
       <c r="R164" t="n">
-        <v>7212495</v>
+        <v>7212826</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17655,8 +17626,24 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
@@ -17673,10 +17660,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129000153</v>
+        <v>129000177</v>
       </c>
       <c r="B165" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17684,37 +17671,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>583768</v>
+        <v>583609</v>
       </c>
       <c r="R165" t="n">
-        <v>7212826</v>
+        <v>7212495</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17755,24 +17739,8 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
@@ -17889,7 +17857,7 @@
         <v>129085074</v>
       </c>
       <c r="B167" t="n">
-        <v>105752</v>
+        <v>105754</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17986,7 +17954,7 @@
         <v>129085075</v>
       </c>
       <c r="B168" t="n">
-        <v>105752</v>
+        <v>105754</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18274,10 +18242,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129000122</v>
+        <v>129000170</v>
       </c>
       <c r="B171" t="n">
-        <v>80147</v>
+        <v>91554</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18285,21 +18253,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18309,10 +18277,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>583833</v>
+        <v>583844</v>
       </c>
       <c r="R171" t="n">
-        <v>7212856</v>
+        <v>7212348</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18371,10 +18339,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129000170</v>
+        <v>129000122</v>
       </c>
       <c r="B172" t="n">
-        <v>91554</v>
+        <v>80147</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18382,21 +18350,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18406,10 +18374,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>583844</v>
+        <v>583833</v>
       </c>
       <c r="R172" t="n">
-        <v>7212348</v>
+        <v>7212856</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18662,10 +18630,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129000124</v>
+        <v>129000172</v>
       </c>
       <c r="B175" t="n">
-        <v>83012</v>
+        <v>91560</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18673,23 +18641,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
@@ -18697,10 +18661,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>583770</v>
+        <v>583719</v>
       </c>
       <c r="R175" t="n">
-        <v>7212830</v>
+        <v>7212791</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18759,10 +18723,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129000172</v>
+        <v>129000124</v>
       </c>
       <c r="B176" t="n">
-        <v>91558</v>
+        <v>83012</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18770,21 +18734,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18794,10 +18758,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>583719</v>
+        <v>583770</v>
       </c>
       <c r="R176" t="n">
-        <v>7212791</v>
+        <v>7212830</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19247,7 +19211,7 @@
         <v>129000129</v>
       </c>
       <c r="B181" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19341,48 +19305,44 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129073201</v>
+        <v>129085095</v>
       </c>
       <c r="B182" t="n">
-        <v>92346</v>
+        <v>91560</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>918</v>
+        <v>5432</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>(Burt) Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>583599</v>
+        <v>583378</v>
       </c>
       <c r="R182" t="n">
-        <v>7212710</v>
+        <v>7212728</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19426,44 +19386,44 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129073202</v>
+        <v>129073201</v>
       </c>
       <c r="B183" t="n">
-        <v>95554</v>
+        <v>92347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2387</v>
+        <v>918</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19473,10 +19433,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>584165</v>
+        <v>583599</v>
       </c>
       <c r="R183" t="n">
-        <v>7211601</v>
+        <v>7212710</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19503,12 +19463,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19535,48 +19495,48 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129085095</v>
+        <v>129073202</v>
       </c>
       <c r="B184" t="n">
-        <v>91558</v>
+        <v>95555</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5432</v>
+        <v>2387</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>583378</v>
+        <v>584165</v>
       </c>
       <c r="R184" t="n">
-        <v>7212728</v>
+        <v>7211601</v>
       </c>
       <c r="S184" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19600,12 +19560,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19620,22 +19580,22 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Magdalena Nilsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129085086</v>
+        <v>129000160</v>
       </c>
       <c r="B185" t="n">
-        <v>57727</v>
+        <v>91536</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19643,41 +19603,37 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>583569</v>
+        <v>583674</v>
       </c>
       <c r="R185" t="n">
-        <v>7212757</v>
+        <v>7212755</v>
       </c>
       <c r="S185" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19707,11 +19663,6 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19726,60 +19677,60 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129085082</v>
+        <v>129000121</v>
       </c>
       <c r="B186" t="n">
-        <v>80175</v>
+        <v>80147</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>583926</v>
+        <v>583770</v>
       </c>
       <c r="R186" t="n">
-        <v>7212799</v>
+        <v>7212825</v>
       </c>
       <c r="S186" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19823,39 +19774,39 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129085092</v>
+        <v>129000132</v>
       </c>
       <c r="B187" t="n">
-        <v>58097</v>
+        <v>57727</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -19866,17 +19817,17 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>584017</v>
+        <v>583968</v>
       </c>
       <c r="R187" t="n">
-        <v>7212353</v>
+        <v>7212362</v>
       </c>
       <c r="S187" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19906,6 +19857,11 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19920,19 +19876,19 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129000132</v>
+        <v>129085086</v>
       </c>
       <c r="B188" t="n">
         <v>57727</v>
@@ -19961,19 +19917,23 @@
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>583968</v>
+        <v>583569</v>
       </c>
       <c r="R188" t="n">
-        <v>7212362</v>
+        <v>7212757</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20007,7 +19967,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20022,60 +19982,60 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129000121</v>
+        <v>129085082</v>
       </c>
       <c r="B189" t="n">
-        <v>80147</v>
+        <v>80175</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>583770</v>
+        <v>583926</v>
       </c>
       <c r="R189" t="n">
-        <v>7212825</v>
+        <v>7212799</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20119,60 +20079,60 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129000160</v>
+        <v>129085092</v>
       </c>
       <c r="B190" t="n">
-        <v>91536</v>
+        <v>58097</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>583674</v>
+        <v>584017</v>
       </c>
       <c r="R190" t="n">
-        <v>7212755</v>
+        <v>7212353</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20216,44 +20176,44 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Embla Berg, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby, Alva Danielsson, Henny My Lindqvist, Magdalena Nilsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129000154</v>
+        <v>129000162</v>
       </c>
       <c r="B191" t="n">
-        <v>80182</v>
+        <v>91536</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20263,10 +20223,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>583832</v>
+        <v>583583</v>
       </c>
       <c r="R191" t="n">
-        <v>7212853</v>
+        <v>7212676</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20325,32 +20285,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129000162</v>
+        <v>129000154</v>
       </c>
       <c r="B192" t="n">
-        <v>91536</v>
+        <v>80182</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20360,10 +20320,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>583583</v>
+        <v>583832</v>
       </c>
       <c r="R192" t="n">
-        <v>7212676</v>
+        <v>7212853</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>

--- a/artfynd/A 50208-2023 artfynd.xlsx
+++ b/artfynd/A 50208-2023 artfynd.xlsx
@@ -8268,10 +8268,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129000140</v>
+        <v>128998140</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>91536</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8279,34 +8279,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>584092</v>
+        <v>583855</v>
       </c>
       <c r="R69" t="n">
-        <v>7211517</v>
+        <v>7213081</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8333,17 +8333,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8358,22 +8353,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128998140</v>
+        <v>129000140</v>
       </c>
       <c r="B70" t="n">
-        <v>91536</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8381,34 +8376,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583855</v>
+        <v>584092</v>
       </c>
       <c r="R70" t="n">
-        <v>7213081</v>
+        <v>7211517</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8435,12 +8430,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8455,22 +8455,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129000183</v>
+        <v>128998142</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>91536</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8478,34 +8478,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>584220</v>
+        <v>583800</v>
       </c>
       <c r="R71" t="n">
-        <v>7211664</v>
+        <v>7212769</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8532,12 +8532,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8552,22 +8552,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128998142</v>
+        <v>129000183</v>
       </c>
       <c r="B72" t="n">
-        <v>91536</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8575,34 +8575,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583800</v>
+        <v>584220</v>
       </c>
       <c r="R72" t="n">
-        <v>7212769</v>
+        <v>7211664</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8629,12 +8629,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8649,12 +8649,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8664,7 +8664,7 @@
         <v>128997038</v>
       </c>
       <c r="B73" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>128998122</v>
       </c>
       <c r="B74" t="n">
-        <v>105754</v>
+        <v>105755</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8855,45 +8855,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128998128</v>
+        <v>129000152</v>
       </c>
       <c r="B75" t="n">
-        <v>57887</v>
+        <v>80174</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583799</v>
+        <v>584338</v>
       </c>
       <c r="R75" t="n">
-        <v>7212748</v>
+        <v>7211689</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8940,57 +8940,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129000152</v>
+        <v>128998128</v>
       </c>
       <c r="B76" t="n">
-        <v>80174</v>
+        <v>57887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>584338</v>
+        <v>583799</v>
       </c>
       <c r="R76" t="n">
-        <v>7211689</v>
+        <v>7212748</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9017,12 +9017,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9037,44 +9037,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128998131</v>
+        <v>128998135</v>
       </c>
       <c r="B77" t="n">
-        <v>57724</v>
+        <v>91922</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>584025</v>
+        <v>583778</v>
       </c>
       <c r="R77" t="n">
-        <v>7212370</v>
+        <v>7212890</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9243,32 +9243,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128998135</v>
+        <v>128998131</v>
       </c>
       <c r="B79" t="n">
-        <v>91922</v>
+        <v>57724</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1506</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583778</v>
+        <v>584025</v>
       </c>
       <c r="R79" t="n">
-        <v>7212890</v>
+        <v>7212370</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9630,7 +9630,7 @@
         <v>129000141</v>
       </c>
       <c r="B83" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9918,32 +9918,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129000145</v>
+        <v>129000115</v>
       </c>
       <c r="B86" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9953,10 +9953,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>583826</v>
+        <v>583856</v>
       </c>
       <c r="R86" t="n">
-        <v>7211682</v>
+        <v>7212374</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9983,12 +9983,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10015,32 +10015,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129000115</v>
+        <v>129000145</v>
       </c>
       <c r="B87" t="n">
-        <v>80175</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10050,10 +10050,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>583856</v>
+        <v>583826</v>
       </c>
       <c r="R87" t="n">
-        <v>7212374</v>
+        <v>7211682</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10080,12 +10080,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10416,10 +10416,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128997040</v>
+        <v>129000116</v>
       </c>
       <c r="B91" t="n">
-        <v>91536</v>
+        <v>57724</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10427,21 +10427,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10451,10 +10451,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>583800</v>
+        <v>584099</v>
       </c>
       <c r="R91" t="n">
-        <v>7212621</v>
+        <v>7211521</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10481,12 +10481,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Spillkråkehack på låga</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10501,12 +10506,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10610,10 +10615,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128997035</v>
+        <v>128997040</v>
       </c>
       <c r="B93" t="n">
-        <v>57887</v>
+        <v>91536</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10621,21 +10626,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10645,10 +10650,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>583868</v>
+        <v>583800</v>
       </c>
       <c r="R93" t="n">
-        <v>7212926</v>
+        <v>7212621</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10707,10 +10712,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129000165</v>
+        <v>128997035</v>
       </c>
       <c r="B94" t="n">
-        <v>91536</v>
+        <v>57887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10718,21 +10723,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10742,10 +10747,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>583888</v>
+        <v>583868</v>
       </c>
       <c r="R94" t="n">
-        <v>7211663</v>
+        <v>7212926</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10772,12 +10777,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10792,22 +10797,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129000116</v>
+        <v>129000165</v>
       </c>
       <c r="B95" t="n">
-        <v>57724</v>
+        <v>91536</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10815,21 +10820,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10839,10 +10844,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>584099</v>
+        <v>583888</v>
       </c>
       <c r="R95" t="n">
-        <v>7211521</v>
+        <v>7211663</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10875,11 +10880,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Spillkråkehack på låga</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10906,10 +10906,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128998150</v>
+        <v>129000175</v>
       </c>
       <c r="B96" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10917,34 +10917,30 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>583862</v>
+        <v>583975</v>
       </c>
       <c r="R96" t="n">
-        <v>7212466</v>
+        <v>7211530</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10971,12 +10967,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10991,12 +10987,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11096,27 +11092,27 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128998155</v>
+        <v>128998150</v>
       </c>
       <c r="B98" t="n">
-        <v>80181</v>
+        <v>79041</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -11131,10 +11127,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>583778</v>
+        <v>583862</v>
       </c>
       <c r="R98" t="n">
-        <v>7212766</v>
+        <v>7212466</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11193,41 +11189,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129000175</v>
+        <v>128998155</v>
       </c>
       <c r="B99" t="n">
-        <v>91560</v>
+        <v>80181</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>583975</v>
+        <v>583778</v>
       </c>
       <c r="R99" t="n">
-        <v>7211530</v>
+        <v>7212766</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11254,12 +11254,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11274,44 +11274,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128998132</v>
+        <v>128998136</v>
       </c>
       <c r="B100" t="n">
-        <v>57724</v>
+        <v>80182</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11321,10 +11321,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>583834</v>
+        <v>583838</v>
       </c>
       <c r="R100" t="n">
-        <v>7212585</v>
+        <v>7212502</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11480,10 +11480,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128998136</v>
+        <v>129000107</v>
       </c>
       <c r="B102" t="n">
-        <v>80182</v>
+        <v>92258</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11491,34 +11491,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>583838</v>
+        <v>583938</v>
       </c>
       <c r="R102" t="n">
-        <v>7212502</v>
+        <v>7211643</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11545,12 +11545,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11565,57 +11565,57 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129000107</v>
+        <v>128998132</v>
       </c>
       <c r="B103" t="n">
-        <v>92258</v>
+        <v>57724</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>583938</v>
+        <v>583834</v>
       </c>
       <c r="R103" t="n">
-        <v>7211643</v>
+        <v>7212585</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11642,12 +11642,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11662,22 +11662,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129000130</v>
+        <v>128997039</v>
       </c>
       <c r="B104" t="n">
-        <v>57727</v>
+        <v>91536</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11685,21 +11685,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11709,10 +11709,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>584350</v>
+        <v>583807</v>
       </c>
       <c r="R104" t="n">
-        <v>7211690</v>
+        <v>7212750</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11739,17 +11739,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Äldre och färska ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11764,22 +11759,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128997039</v>
+        <v>129000126</v>
       </c>
       <c r="B105" t="n">
-        <v>91536</v>
+        <v>83012</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11787,21 +11782,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11811,10 +11806,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>583807</v>
+        <v>583693</v>
       </c>
       <c r="R105" t="n">
-        <v>7212750</v>
+        <v>7211591</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11841,12 +11836,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11861,22 +11856,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129000126</v>
+        <v>128998250</v>
       </c>
       <c r="B106" t="n">
-        <v>83012</v>
+        <v>57727</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11884,34 +11879,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>583693</v>
+        <v>583752</v>
       </c>
       <c r="R106" t="n">
-        <v>7211591</v>
+        <v>7212679</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11938,12 +11941,17 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11958,19 +11966,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128998250</v>
+        <v>129000130</v>
       </c>
       <c r="B107" t="n">
         <v>57727</v>
@@ -11999,24 +12007,16 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>583752</v>
+        <v>584350</v>
       </c>
       <c r="R107" t="n">
-        <v>7212679</v>
+        <v>7211690</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12043,17 +12043,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Gammalt bohål på låga, troligen av tretåig hackspett pga av storleken på bohålet (ca 5 cm)</t>
+          <t>Äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12068,12 +12068,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12083,7 +12083,7 @@
         <v>129000147</v>
       </c>
       <c r="B108" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12177,10 +12177,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128998149</v>
+        <v>129000146</v>
       </c>
       <c r="B109" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12188,34 +12188,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>584059</v>
+        <v>583819</v>
       </c>
       <c r="R109" t="n">
-        <v>7212428</v>
+        <v>7211689</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12242,12 +12242,17 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12262,22 +12267,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128998126</v>
+        <v>129000157</v>
       </c>
       <c r="B110" t="n">
-        <v>92258</v>
+        <v>57831</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12285,34 +12290,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3298</v>
+        <v>103031</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>583748</v>
+        <v>583712</v>
       </c>
       <c r="R110" t="n">
-        <v>7212869</v>
+        <v>7211576</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12339,12 +12344,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12359,12 +12364,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -12468,45 +12473,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129000157</v>
+        <v>128998149</v>
       </c>
       <c r="B112" t="n">
-        <v>57831</v>
+        <v>79041</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>583712</v>
+        <v>584059</v>
       </c>
       <c r="R112" t="n">
-        <v>7211576</v>
+        <v>7212428</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12533,12 +12538,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12553,57 +12558,57 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129000146</v>
+        <v>128998126</v>
       </c>
       <c r="B113" t="n">
-        <v>57727</v>
+        <v>92258</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>583819</v>
+        <v>583748</v>
       </c>
       <c r="R113" t="n">
-        <v>7211689</v>
+        <v>7212869</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12630,17 +12635,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12655,12 +12655,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -12857,32 +12857,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129000119</v>
+        <v>129000135</v>
       </c>
       <c r="B116" t="n">
-        <v>83005</v>
+        <v>57727</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12892,10 +12892,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>583763</v>
+        <v>584139</v>
       </c>
       <c r="R116" t="n">
-        <v>7211568</v>
+        <v>7211559</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12928,6 +12928,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13148,32 +13153,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129000135</v>
+        <v>129000119</v>
       </c>
       <c r="B119" t="n">
-        <v>57727</v>
+        <v>83005</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13183,10 +13188,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>584139</v>
+        <v>583763</v>
       </c>
       <c r="R119" t="n">
-        <v>7211559</v>
+        <v>7211568</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13219,11 +13224,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13250,41 +13250,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128998148</v>
+        <v>129000169</v>
       </c>
       <c r="B120" t="n">
-        <v>91560</v>
+        <v>82990</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>583764</v>
+        <v>583695</v>
       </c>
       <c r="R120" t="n">
-        <v>7212875</v>
+        <v>7211591</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13311,12 +13315,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13331,57 +13335,57 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128998129</v>
+        <v>129000144</v>
       </c>
       <c r="B121" t="n">
-        <v>80175</v>
+        <v>57727</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>583743</v>
+        <v>583832</v>
       </c>
       <c r="R121" t="n">
-        <v>7212862</v>
+        <v>7211693</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13408,12 +13412,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13428,46 +13437,42 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128998154</v>
+        <v>128998148</v>
       </c>
       <c r="B122" t="n">
-        <v>80181</v>
+        <v>91560</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -13475,10 +13480,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>583743</v>
+        <v>583764</v>
       </c>
       <c r="R122" t="n">
-        <v>7212862</v>
+        <v>7212875</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13634,10 +13639,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129000169</v>
+        <v>128998129</v>
       </c>
       <c r="B124" t="n">
-        <v>82990</v>
+        <v>80175</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13645,34 +13650,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6439</v>
+        <v>6462</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>583695</v>
+        <v>583743</v>
       </c>
       <c r="R124" t="n">
-        <v>7211591</v>
+        <v>7212862</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13699,12 +13704,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13719,57 +13724,57 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129000144</v>
+        <v>128998154</v>
       </c>
       <c r="B125" t="n">
-        <v>57727</v>
+        <v>80181</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>583832</v>
+        <v>583743</v>
       </c>
       <c r="R125" t="n">
-        <v>7211693</v>
+        <v>7212862</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13796,17 +13801,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13821,12 +13821,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -14129,10 +14129,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129000166</v>
+        <v>129000184</v>
       </c>
       <c r="B129" t="n">
-        <v>91536</v>
+        <v>79041</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14140,21 +14140,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14164,10 +14164,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>583796</v>
+        <v>584333</v>
       </c>
       <c r="R129" t="n">
-        <v>7211546</v>
+        <v>7211688</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14226,45 +14226,48 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129000168</v>
+        <v>129000185</v>
       </c>
       <c r="B130" t="n">
-        <v>91536</v>
+        <v>92858</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1108</v>
+        <v>5964</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>584331</v>
+        <v>584074</v>
       </c>
       <c r="R130" t="n">
-        <v>7211693</v>
+        <v>7211675</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14305,6 +14308,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14323,48 +14327,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129000185</v>
+        <v>129000166</v>
       </c>
       <c r="B131" t="n">
-        <v>92858</v>
+        <v>91536</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5964</v>
+        <v>1108</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>584074</v>
+        <v>583796</v>
       </c>
       <c r="R131" t="n">
-        <v>7211675</v>
+        <v>7211546</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14405,7 +14406,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14424,10 +14424,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129000184</v>
+        <v>129000168</v>
       </c>
       <c r="B132" t="n">
-        <v>79041</v>
+        <v>91536</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14435,21 +14435,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14459,10 +14459,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>584333</v>
+        <v>584331</v>
       </c>
       <c r="R132" t="n">
-        <v>7211688</v>
+        <v>7211693</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14618,10 +14618,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129000174</v>
+        <v>129000138</v>
       </c>
       <c r="B134" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14629,19 +14629,23 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -14649,10 +14653,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>583934</v>
+        <v>583805</v>
       </c>
       <c r="R134" t="n">
-        <v>7211520</v>
+        <v>7211693</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14685,6 +14689,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14711,10 +14720,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129000138</v>
+        <v>129000174</v>
       </c>
       <c r="B135" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14722,23 +14731,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14746,10 +14751,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>583805</v>
+        <v>583934</v>
       </c>
       <c r="R135" t="n">
-        <v>7211693</v>
+        <v>7211520</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14782,11 +14787,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15108,32 +15108,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129000136</v>
+        <v>129000128</v>
       </c>
       <c r="B139" t="n">
-        <v>57727</v>
+        <v>91993</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15143,10 +15143,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>583699</v>
+        <v>583804</v>
       </c>
       <c r="R139" t="n">
-        <v>7212348</v>
+        <v>7212351</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15179,11 +15179,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15210,32 +15205,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129000128</v>
+        <v>129000179</v>
       </c>
       <c r="B140" t="n">
-        <v>91993</v>
+        <v>79041</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15245,10 +15240,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>583804</v>
+        <v>583976</v>
       </c>
       <c r="R140" t="n">
-        <v>7212351</v>
+        <v>7212366</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15307,10 +15302,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129000179</v>
+        <v>129000136</v>
       </c>
       <c r="B141" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15318,21 +15313,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15342,10 +15337,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>583976</v>
+        <v>583699</v>
       </c>
       <c r="R141" t="n">
-        <v>7212366</v>
+        <v>7212348</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15378,6 +15373,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+        